--- a/data/GRE_Quant_Notes_rewritten.xlsx
+++ b/data/GRE_Quant_Notes_rewritten.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Quant Notes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Quant Notes'!$A$1:$F$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Quant Notes'!$A$1:$G$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -428,15 +428,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="90" customWidth="1" min="4" max="4"/>
-    <col width="90" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,20 +453,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Prompt</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Watch out</t>
         </is>
@@ -482,23 +488,28 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Always convert units before comparing</t>
+          <t>Two quantities given in different units — first move?</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>A GRE question will happily give you one speed in kilometres per hour and another in metres per second, then ask which is greater. The numbers are not comparable until they are in the same unit, and the test writers know that the fastest way to lose a point is to compare 20 km/h against 8 m/s as if 20 &gt; 8 settled it.
-Make converting the first thing you do, not the last. Write the conversion as a fraction that cancels the unit you want to get rid of: to turn 8 m/s into km/h, multiply by `3600 s / 1 hr` and by `1 km / 1000 m`, and the seconds and metres cancel, leaving 28.8 km/h.</t>
+          <t>Convert to a common unit **before** comparing anything. Multiply by a conversion fraction arranged so the unwanted unit cancels.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Which is greater: a car at 20 km/h or a runner at 8 m/s? Convert the runner: `8 m/s x 3600 s/hr = 28,800 m/hr = 28.8 km/h`. The runner is faster, even though "20" looks bigger than "8".</t>
+          <t>A question will happily give one speed in km/h and another in m/s and ask which is greater. The numbers are not comparable until they share a unit, and the fastest way to lose a point is to treat 20 &gt; 8 as settling it.
+Write the conversion as a fraction that cancels the unit you want gone: to turn m/s into km/h, multiply by `3600 s / 1 hr` and by `1 km / 1000 m`, so seconds and metres both cancel.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The same trap appears with time (minutes vs hours), money (cents vs dollars) and area (cm² vs m²). If a question mentions two different units anywhere, convert before you do anything else.</t>
+          <t>Which is greater: a car at 20 km/h or a runner at 8 m/s? `8 x 3600 = 28,800 m/hr = 28.8 km/h`. The runner is faster, even though "20" looks bigger.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>The same trap hides in time (minutes vs hours), money (cents vs dollars) and area (cm² vs m²). If two units appear anywhere in a question, convert first.</t>
         </is>
       </c>
     </row>
@@ -513,25 +524,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Converting squared and cubed units</t>
+          <t>Converting an area or a volume between units — what happens to the factor?</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>When you convert an *area* you must square the conversion factor, and when you convert a *volume* you must cube it. A square metre is not 3.28 square feet — it is a square that is 3.28 feet on each side, so it is `3.28^2 = 10.76` square feet. Forgetting this is one of the most common unit mistakes on the test.
-The safe way is to write the conversion factor with its unit and raise the whole thing to the power you need: `(1 m / 3.28 ft)^2 = 1 m² / 10.76 ft²`. Then the units tell you whether to multiply or divide.</t>
+          <t>Square the conversion factor for an area, cube it for a volume. `1 m² = 3.28² = 10.76 ft²`, `1 m³ = 3.28³ ≈ 35.3 ft³`.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>How many square metres is 540 square feet, given 3.28 ft per metre? Square the factor first: `3.28^2 = 10.76`. Then `540 / 10.76 ≈ 50.2 square metres`. Dividing by 3.28 instead would have given ≈165, which is more than three times too big.</t>
+          <t>A square metre is not 3.28 square feet — it is a square 3.28 feet on each side, so it holds `3.28 x 3.28` square feet. Forgetting to raise the factor is the most common unit error on the test.
+Writing the factor with its unit and raising the whole thing to the power keeps you honest: `(1 m / 3.28 ft)^2 = 1 m² / 10.76 ft²`, and the units then tell you whether to multiply or divide.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Cubic units need the cube: 1 m³ = `3.28^3 ≈ 35.3` ft³. The bigger the power, the bigger the error if you skip this step.</t>
-        </is>
-      </c>
+          <t>How many square metres is 540 square feet, given 3.28 ft per metre? `3.28^2 = 10.76`, so `540 / 10.76 ≈ 50.2 m²`. Dividing by 3.28 instead gives ≈165 — more than three times too big.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -544,23 +556,28 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Quantitative Comparison: hunt for equal, then unequal</t>
+          <t>Quantitative Comparison: how do you prove the answer is D?</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>In a Quantity A / Quantity B question you are not asked for a value, you are asked whether one column is always bigger. That makes answer choice D ("cannot be determined") a genuine target rather than a last resort. The fastest route to D is to find one case where the two quantities are equal and one case where they are not — two cases is all it takes to prove the relationship is not fixed.
-Pick your cases deliberately rather than randomly. The values worth trying are 0, 1, a negative number, a fraction between 0 and 1, and a large number, because those are exactly where the usual intuitions break.</t>
+          <t>Find one case where the quantities are **equal** and one where they are **not**. Two different relationships means the relationship is not fixed, so the answer is D.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Quantity A: `x^2`. Quantity B: `x`. Try `x = 1`: both are 1, so they can be equal. Try `x = 2`: A is 4, B is 2, so A can be bigger. Two different relationships, so the answer is D. (If the question had said `x &gt; 1`, the answer would be A.)</t>
+          <t>A QC question does not ask for a value, it asks whether one column is always bigger. That makes D a target rather than a last resort, and the equal/not-equal pair is the quickest proof.
+Choose test values deliberately, not randomly. The ones that break intuition are 0, 1, a negative, a fraction between 0 and 1, and something large.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>One case is never enough. Finding that A = B once only rules out "A is always greater"; you still need a second case to choose between C and D.</t>
+          <t>Quantity A: `x^2`. Quantity B: `x`. Try `x = 1`: both equal 1. Try `x = 2`: A is 4, B is 2. Two different relationships, so **D**. (Told that `x &gt; 1`, the answer would be A.)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>One case is never enough. Finding A = B once only rules out "A is always greater"; you still need a second case to choose between C and D.</t>
         </is>
       </c>
     </row>
@@ -575,23 +592,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Do the least maths you can get away with</t>
+          <t>When you are about to do heavy arithmetic, what should you do instead?</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Every quantitative comparison and most multiple-choice questions are built so that a full calculation is possible but unnecessary. If you find yourself about to multiply four-digit numbers, stop: there is almost certainly a shortcut. Estimate, compare structure, cancel common factors, or test a convenient number instead.
-Comparing is easier than computing. To decide whether `17/33` is bigger than `1/2`, you do not need the decimal — you need to notice that half of 33 is 16.5 and 17 is more than that.</t>
+          <t>Stop and look for the shortcut: estimate, compare structure, cancel common factors, or test a convenient number. Comparing is easier than computing.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Which is greater, `47 x 52` or `48 x 51`? No multiplication needed. Both are products of pairs that sum to 99, and for a fixed sum the product is biggest when the two numbers are closest together. 48 and 51 are closer than 47 and 52, so `48 x 51` is greater.</t>
+          <t>Every comparison and most multiple-choice questions are built so a full calculation is possible but unnecessary. Four-digit multiplication is a sign you have missed the intended route.
+To decide whether `17/33` beats `1/2` you do not need the decimal — half of 33 is 16.5, and 17 is more than that.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Estimation is only safe when the quantities are far apart. If your estimate makes them look nearly equal, go back and calculate exactly.</t>
+          <t>Which is greater, `47 x 52` or `48 x 51`? Both pairs sum to 99, and for a fixed sum the product is largest when the numbers are closest together. 48 and 51 are closer, so `48 x 51` wins — no multiplication done.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Estimation is only safe when the quantities are far apart. If your estimate makes them look nearly equal, go back and compute exactly.</t>
         </is>
       </c>
     </row>
@@ -606,23 +628,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Find the repeating pattern</t>
+          <t>"What is the 50th term / the 200th digit?" — what is the question really about?</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>When a question asks for the 50th term, the 200th digit, or the remainder of a huge power, it is never asking you to grind out 50 steps. It is telling you that the thing repeats. Compute the first four or five cases by hand, spot the cycle length, and then use division to jump to the term you want.
-Once you know the cycle length `k`, the position of term `n` inside the cycle is given by the remainder of `n / k`. A remainder of 0 means you have landed on the last item of the cycle, not the first — that off-by-one is where most errors happen.</t>
+          <t>A repeating cycle. Compute the first few terms, find the cycle length `k`, then take the remainder of `n / k` to see where term `n` lands.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>What is the 50th term of 7, 4, 1, 7, 4, 1, …? The cycle is (7, 4, 1) with length 3. `50 / 3` leaves remainder 2, so the 50th term is the 2nd item of the cycle: 4.</t>
+          <t>No GRE question wants you to grind out 50 steps. Asking for a far-away term is a signal that the sequence repeats, and the whole job is finding the length of the repeat.
+Remainder 0 means you have landed on the **last** item of the cycle, not the first. That off-by-one is where most of the errors live.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Always write out enough terms to see the cycle repeat *twice*. Two identical terms in a row is not proof of a cycle.</t>
+          <t>The 50th term of 7, 4, 1, 7, 4, 1, …? The cycle is (7, 4, 1), length 3. `50 / 3` leaves remainder 2, so the 50th term is the 2nd item: **4**.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Write out enough terms to see the cycle repeat *twice*. Two equal terms in a row is not proof of a cycle.</t>
         </is>
       </c>
     </row>
@@ -637,21 +664,25 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The unit digit</t>
+          <t>Unit digit — what is it, and why does it get its own rules?</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>The unit digit is the rightmost digit of a number — the ones place. It gets its own section of GRE arithmetic because it behaves independently of everything to its left: when you add or multiply, the unit digit of the answer depends only on the unit digits of the inputs.
-That independence is what makes questions about the last digit of `7^100` answerable in seconds. You never need the other 84 digits.</t>
+          <t>The rightmost digit (the ones place). It is independent of everything to its left: when you add or multiply, the unit digit of the answer depends only on the unit digits of the inputs.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>In 3,472 the unit digit is 2. The unit digit of `3,472 x 1,238` is the unit digit of `2 x 8 = 16`, which is 6 — and you never had to do the full multiplication.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>That independence is what makes "last digit of `7^100`" answerable in seconds — the other 84 digits never matter.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>In 3,472 the unit digit is 2. The unit digit of `3,472 x 1,238` comes from `2 x 8 = 16`, so it is **6**, with no long multiplication.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -664,21 +695,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Floor of a negative number</t>
+          <t>Even and odd: what do the four operations give you?</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>The floor of a number is the greatest integer that is less than or equal to it, so flooring always moves you *left* on the number line, never right. For positive numbers that feels like "chop off the decimal", which is why negatives catch people out: chopping the decimal off -16.7 gives -16, but -16 is to the *right* of -16.7, so it cannot be the floor.
-Say it out loud as "round down, always" and the negatives take care of themselves: the floor of a negative non-integer has a *larger* absolute value than the number itself.</t>
+          <t>`even ± even = even`, `odd ± odd = even`, `even ± odd = odd`. For products, **anything times an even is even**; only `odd x odd = odd`.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>`floor(16.7) = 16` but `floor(-16.7) = -17`, because -17 is below -16.7 and -16 is above it. Likewise `floor(-3.01) = -4` and `floor(-3) = -3` (integers are already their own floor).</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>Multiplication is the lopsided one: a single even factor is enough to make the whole product even, which is why the product of consecutive integers is always even.
+Division breaks the pattern entirely — an even divided by an even can be either (`8/4 = 2`, `6/4 = 1.5`), so never assume parity survives a division.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>If `n` is odd, is `n^2 + n` odd or even? `odd x odd = odd`, and `odd + odd = even`, so it is always even. Testing `n = 3` gives 12 ✓.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0 is even, and 2 is the only even prime. Both show up in "must be true" questions.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -691,24 +731,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Quotient and remainder</t>
+          <t>Signs: what do products and powers do to them?</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Dividing one integer by another splits it into a whole-number part and a leftover. If `a` is divided by `b`, the quotient `q` is the whole part and the remainder `r` is what is left, and the three are tied together by one identity worth memorising:
-`a = bq + r`, where `0 &lt;= r &lt; b`
-That constraint on `r` is the important half. The remainder is never negative and is always strictly less than the divisor, which is why a remainder of 7 when dividing by 6 is impossible — it means you did not take out enough copies of 6.</t>
+          <t>Multiplying or dividing: same signs give positive, different signs give negative. Powers: a negative base raised to an **even** power is positive, to an **odd** power stays negative.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>`47 / 5`: the quotient is 9 and the remainder is 2, since `47 = 5 x 9 + 2` and `0 &lt;= 2 &lt; 5`. If a question says "n leaves remainder 2 when divided by 5", that means `n = 5q + 2`, so n could be 2, 7, 12, 17, …</t>
+          <t>Count the negatives in a product — an even number of them cancels out, an odd number leaves the result negative.
+The power rule is the source of endless QC traps: `x^2` is never negative, so `x^2 = 9` has two solutions while `x^3 = 27` has one.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>A remainder question is usually best answered by writing `n = bq + r` and substituting, not by trying numbers at random.</t>
+          <t>`(-2)^4 = 16` but `(-2)^3 = -8`. And `(-2)(-3)(-4) = -24`: three negatives, so the result is negative.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>`-2^4` and `(-2)^4` are different. Without brackets the power binds first, so `-2^4 = -16`.</t>
         </is>
       </c>
     </row>
@@ -723,23 +767,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Quotient and remainder with negative numbers</t>
+          <t>Absolute value — what does |x| actually mean?</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>The rule `0 &lt;= r &lt; b` also holds when the number being divided is negative, and it forces the quotient to go one step further down than you would expect. Because the remainder must be non-negative, the quotient has to be *smaller* than the naive answer — in absolute terms, one bigger.
-Concretely: the quotient of a negative number is `-(1 + |quotient of the positive equivalent|)` whenever the division is not exact.</t>
+          <t>The distance from zero on the number line, so it is never negative. `|x| = x` when `x &gt;= 0` and `|x| = -x` when `x &lt; 0`.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>`-15 / 9`. It is tempting to say the quotient is -1 with remainder -6, but remainders cannot be negative. Take the quotient down to -2: `-15 = 9 x (-2) + 3`, giving quotient -2 and remainder 3, with `0 &lt;= 3 &lt; 9`. Compare `15 / 9`, where the quotient is 1 and the remainder is 6.</t>
+          <t>Reading it as *distance* rather than "make it positive" is what makes the harder questions easy: `|x - 3|` is the distance between `x` and 3, so `|x - 3| = 5` immediately gives the two points 5 away from 3.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>This is the same idea as the floor of a negative number: the quotient *is* `floor(a/b)`, and floors of negatives always round away from zero.</t>
+          <t>`|-7| = 7` and `|7| = 7`. `|x - 3| &lt; 5` means "x is less than 5 away from 3", i.e. `-2 &lt; x &lt; 8` — no algebra needed.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>`|a + b|` is not `|a| + |b|`: take `a = 3, b = -3`. It is always less than or equal to it.</t>
         </is>
       </c>
     </row>
@@ -754,110 +802,124 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Remainders add, subtract and multiply</t>
+          <t>Floor of a negative number — which way does it go?</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>You can work with remainders the same way you work with the numbers themselves: the remainder of a sum is the remainder of the sum of the remainders, and the same is true for differences and products. That turns enormous arithmetic into single-digit arithmetic.
-The one extra step is that the result may still be too big, in which case you take the remainder again. If two numbers each leave remainder 4 on division by 6, their sum leaves remainder `8 mod 6 = 2`, not 8.</t>
+          <t>Down, always. `floor(-16.7) = -17`, not -16. The floor of a negative non-integer has a **larger** absolute value than the number.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>What is the remainder when `1,234 + 5,678` is divided by 5? `1,234` leaves 4 and `5,678` leaves 3. `4 + 3 = 7`, and `7` leaves remainder 2 on division by 5. So the answer is 2 — no need to add the numbers at all. The same works for products: `1,234 x 5,678` leaves `4 x 3 = 12`, and `12 mod 5 = 2`.</t>
+          <t>The floor is the greatest integer less than or equal to the number, so it always moves you left on the number line. For positives that looks like "chop off the decimal", which is why negatives catch people out: chopping -16.7 gives -16, which is to the right.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>This does **not** work for division: the remainder of `a/b` divided by n has no simple relationship to the remainders of a and b.</t>
-        </is>
-      </c>
+          <t>`floor(16.7) = 16`, `floor(-16.7) = -17`, `floor(-3.01) = -4`, `floor(-3) = -3` (integers are their own floor).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Unit Digits &amp; Divisibility Rules</t>
+          <t>Number Sense &amp; Strategy</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Unit digits of powers run in cycles</t>
+          <t>Quotient and remainder — what is the identity that ties them together?</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Raise any digit to higher and higher powers and its unit digit starts repeating, always within four steps. That is the whole trick behind "what is the last digit of `7^103`" questions: work out the cycle, then find where 103 lands inside it.
-The cycles worth knowing: 2 goes 2, 4, 8, 6; 3 goes 3, 9, 7, 1; 7 goes 7, 9, 3, 1; 8 goes 8, 4, 2, 6 (all length 4). 4 goes 4, 6 and 9 goes 9, 1 (length 2). 0, 1, 5 and 6 never change at all. Since every cycle length divides 4, dividing the exponent by 4 is enough for all of them.</t>
+          <t>`a = bq + r` with `0 &lt;= r &lt; b`. The quotient `q` is the whole-number part; the remainder `r` is what is left, and it is never negative and always smaller than the divisor.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Last digit of `7^103`. The cycle for 7 is (7, 9, 3, 1), length 4. `103 / 4` leaves remainder 3, so we want the 3rd entry: **3**. Check the logic on a small case: `7^3 = 343`, and 3 is indeed the 3rd entry.</t>
+          <t>The constraint on `r` is the important half. A remainder of 7 when dividing by 6 is impossible — it means you did not take out enough copies of 6.
+Most remainder questions are solved by writing the number in this form and substituting, not by trying values at random.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Remainder 0 means the *last* item of the cycle, not the first. `7^100` has remainder 0, so its unit digit is 1, the 4th entry.</t>
-        </is>
-      </c>
+          <t>`47 / 5`: quotient 9, remainder 2, since `47 = 5 x 9 + 2`. "n leaves remainder 2 when divided by 5" means `n = 5q + 2`, so n is 2, 7, 12, 17, …</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Unit Digits &amp; Divisibility Rules</t>
+          <t>Number Sense &amp; Strategy</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Only the base's unit digit matters</t>
+          <t>Quotient and remainder when the number is negative?</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>`unitdigit(a^b) = unitdigit(unitdigit(a)^b)`. Everything to the left of the base's last digit is irrelevant to the answer, because multiplying two numbers only lets the unit digits talk to each other. This is what makes the cycles above usable on monstrous numbers.
-So `1,234,567^40` has the same unit digit as `7^40`, and you can throw the other six digits away the moment you see the question.</t>
+          <t>The quotient goes one step further down, because the remainder must stay non-negative. `-15 / 9` gives quotient **-2**, remainder **3**.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Unit digit of `2,468^15`? Keep only the 8: the cycle for 8 is (8, 4, 2, 6). `15 / 4` leaves remainder 3, so the answer is the 3rd entry, **2**.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
+          <t>It is tempting to say quotient -1 remainder -6, but remainders cannot be negative. Taking the quotient down to -2 gives `-15 = 9(-2) + 3`, with `0 &lt;= 3 &lt; 9` ✓.
+This is the same idea as the floor of a negative: the quotient *is* `floor(a/b)`.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>`-15 / 9` → quotient -2, remainder 3. Compare `15 / 9` → quotient 1, remainder 6. The absolute value of the quotient went up by one.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Unit Digits &amp; Divisibility Rules</t>
+          <t>Number Sense &amp; Strategy</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Unit digit of a sum or product</t>
+          <t>Remainder of a sum or a product of huge numbers?</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>The unit digit of a sum is the unit digit of the sum of the unit digits, and the same holds for products. This is just the remainder rule for division by 10, and it lets you collapse a long expression into single digits before doing anything else.
-If the digits add to more than 9, keep only the last digit of that total and carry on.</t>
+          <t>Work with the remainders instead: the remainder of a sum is the remainder of the **sum of the remainders**, and the same holds for differences and products. Reduce again if the result is still too big.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Unit digit of `327 + 4,589 + 62`? Add only the last digits: `7 + 9 + 2 = 18`, so the unit digit is **8**. For a product, `327 x 4,589` has unit digit from `7 x 9 = 63`, so **3**.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
+          <t>This turns enormous arithmetic into single-digit arithmetic. If two numbers each leave remainder 4 on division by 6, their sum leaves `8 mod 6 = 2`, not 8.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Remainder of `1,234 + 5,678` divided by 5? They leave 4 and 3, and `4 + 3 = 7` leaves remainder **2**. For the product: `4 x 3 = 12`, and `12 mod 5 = 2`.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>This does **not** work for division — the remainder of `a/b` has no simple relationship to the remainders of `a` and `b`.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -870,22 +932,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Worked example: unit digit of a long power sum</t>
+          <t>Last digit of a large power — what do you need?</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Combine the last three ideas and a question like "what is the unit digit of `3 + 3^2 + 3^3 + ... + 3^50`?" becomes a counting exercise. Each power of 3 contributes its own unit digit from the cycle (3, 9, 7, 1), those four digits sum to 20, and 20 contributes a unit digit of 0. So every complete block of four terms adds nothing to the unit digit, and only the leftover terms matter.</t>
+          <t>The unit digit's **cycle**, which is always length 4 or shorter. Divide the exponent by 4 and use the remainder to pick the entry.
+2: 2, 4, 8, 6 · 3: 3, 9, 7, 1 · 7: 7, 9, 3, 1 · 8: 8, 4, 2, 6 · 4: 4, 6 · 9: 9, 1 · 0, 1, 5, 6 never change.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>`3 + 3^2 + ... + 3^50`: 50 terms is 12 complete blocks of 4 (48 terms, contributing unit digit 0) plus 2 leftover terms, `3^49` and `3^50`. `49 / 4` leaves remainder 1, so `3^49` ends in 3; `50 / 4` leaves remainder 2, so `3^50` ends in 9. `3 + 9 = 12`, so the unit digit of the whole sum is **2**.</t>
+          <t>Raise any digit to higher powers and its last digit starts repeating within four steps. Since every cycle length divides 4, dividing the exponent by 4 works for all of them.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Count the leftovers from the *end* of the series, and check whether the series starts at `3^1` or `3^0` — an extra first term changes the answer.</t>
+          <t>Last digit of `7^103`? The cycle for 7 is (7, 9, 3, 1). `103 / 4` leaves remainder 3, so take the 3rd entry: **3**. Check on a small case: `7^3 = 343` ✓.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Remainder 0 means the **last** entry of the cycle, not the first. `7^100` has remainder 0, so its unit digit is 1.</t>
         </is>
       </c>
     </row>
@@ -900,21 +968,25 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Remainder of a huge power</t>
+          <t>Unit digit of `1,234,567^40` — what can you throw away?</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>The same cyclicity idea works for remainders by any divisor, not just 10. To find the remainder of `a^b` divided by `n`, compute the remainders of `a^1, a^2, a^3, ...` divided by `n` until the pattern repeats, then use the exponent's position in that cycle.
-If a step of the pattern gives you a number bigger than the divisor, reduce it again. When dividing by 6, a running value of 7 is really a remainder of 1.</t>
+          <t>Everything except the base's last digit: `unitdigit(a^b) = unitdigit(unitdigit(a)^b)`. So `1,234,567^40` ends in the same digit as `7^40`.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Remainder of `4^35` divided by 6. `4^1 = 4` → 4. `4^2 = 16` → 4. `4^3 = 64` → 4. The cycle has length 1, so the answer is **4** for any positive power. A richer case: `3^20` divided by 7 gives remainders 3, 2, 6, 4, 5, 1 then repeats (length 6); `20 / 6` leaves remainder 2, so the answer is the 2nd entry, 2.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>Multiplying two numbers only lets their unit digits interact, so the digits further left can never reach the ones place. This is what makes the cycles usable on monstrous numbers.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Unit digit of `2,468^15`? Keep the 8; its cycle is (8, 4, 2, 6). `15 / 4` leaves remainder 3, so the answer is the 3rd entry, **2**.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -927,20 +999,25 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Divisibility by 2, 5 and 10</t>
+          <t>Unit digit of a sum or of a product?</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Before the clever rules, the three that come straight off the last digit: a number is divisible by 2 if its unit digit is even (0, 2, 4, 6, 8), by 5 if its unit digit is 0 or 5, and by 10 if its unit digit is 0. These are the building blocks that the composite rules below are made from.</t>
+          <t>Add or multiply just the unit digits, then keep the last digit of that result.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,938 is divisible by 2 (ends in 8) but not by 5. 4,935 is divisible by 5 but not by 2, so not by 10. 4,930 ends in 0 so it is divisible by 2, 5 and 10.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
+          <t>It is the remainder rule for division by 10, and it lets you collapse a long expression into single digits before doing anything else.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>`327 + 4,589 + 62`: add `7 + 9 + 2 = 18`, so the unit digit is **8**. For `327 x 4,589`: `7 x 9 = 63`, so **3**.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -953,21 +1030,29 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Divisibility by 3</t>
+          <t>Unit digit of `3 + 3^2 + 3^3 + ... + 3^50`?</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Add up the digits. If that sum is a multiple of 3, so is the original number — and if the sum is still too big to judge, add its digits again and repeat.
-The rule works because 10, 100, 1000 … all leave remainder 1 when divided by 3, so each digit contributes exactly its own value to the remainder.</t>
+          <t>**2.** Each block of four powers contributes `3+9+7+1 = 20`, so complete blocks add 0 to the unit digit. Only the leftover terms count.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Is 4,938 divisible by 3? `4 + 9 + 3 + 8 = 24`, and 24 is a multiple of 3, so yes. For 987,654: `9+8+7+6+5+4 = 39`, and `3+9 = 12`, a multiple of 3, so yes.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
+          <t>50 terms is 12 complete blocks of four (48 terms, unit digit 0) plus two leftovers, `3^49` and `3^50`. `49 / 4` leaves 1 so `3^49` ends in 3; `50 / 4` leaves 2 so `3^50` ends in 9. `3 + 9 = 12` → unit digit 2.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Same method on `2 + 2^2 + ... + 2^22`: the cycle (2, 4, 8, 6) sums to 20, so ignore the 20 complete-block terms; the leftovers are `2^21` (ends in 2) and `2^22` (ends in 4), giving unit digit **6**.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Count the leftovers from the **end** of the series, and check whether it starts at `3^1` or `3^0` — one extra first term changes everything.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -980,20 +1065,25 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Divisibility by 9</t>
+          <t>Remainder of `a^b` divided by a small number `n`?</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Exactly the same digit-sum test, but the sum must be a multiple of 9. Every number divisible by 9 is therefore also divisible by 3, though the reverse is not true.</t>
+          <t>Find the cycle of remainders of `a^1, a^2, a^3, ...` divided by `n`, then use `b`'s position in that cycle. Reduce any running value that grows past `n`.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,938: digits sum to 24, which is divisible by 3 but not 9, so 4,938 is a multiple of 3 and not of 9. 4,932: digits sum to 18, a multiple of 9, so it is divisible by 9 (and by 3).</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>Cyclicity is not just a base-10 trick — remainders by any divisor repeat too. Compute until the pattern comes back round, then jump.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Remainder of `4^35` divided by 6? `4, 16, 64` give remainders 4, 4, 4 — a cycle of length 1, so the answer is **4** for every positive power. Richer case: `3^n` divided by 7 gives 3, 2, 6, 4, 5, 1 (length 6); `20 / 6` leaves 2, so `3^20` leaves remainder **2**.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1006,21 +1096,25 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Divisibility by 4</t>
+          <t>Divisibility by 2, 5 and 10?</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Ignore everything except the last two digits: if the two-digit number they form is divisible by 4, so is the whole number. This works because 100 is itself a multiple of 4, so the hundreds and everything above them can never affect the answer.
-Two handy corollaries: any number ending in 00 is divisible by 4, and any even number whose tens digit is even needs only its unit digit to be 0, 4 or 8.</t>
+          <t>Read the last digit: **2** if it is even (0, 2, 4, 6, 8), **5** if it is 0 or 5, **10** only if it is 0.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Is 7,318 divisible by 4? Look at 18 — not a multiple of 4, so no. Is 7,316? Look at 16 — yes, so 7,316 is divisible by 4.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>These are the building blocks the composite rules are made from, so they are worth stating before the clever ones.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4,938 is divisible by 2 but not 5. 4,935 is divisible by 5 but not 2, so not by 10. 4,930 ends in 0, so it is divisible by all three.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1033,161 +1127,184 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Divisibility by 8</t>
+          <t>Divisibility by 3?</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Same idea one place further: check the last *three* digits, because 1,000 is a multiple of 8. If the three-digit number they form is divisible by 8, so is the original.
-Anything ending in 000 is divisible by 8, which is why questions about round numbers often collapse immediately.</t>
+          <t>Add the digits. If the sum is a multiple of 3, so is the number — and you can repeat the test on the sum.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Is 12,344 divisible by 8? Check 344: `344 / 8 = 43` exactly, so yes. Is 12,346? Check 346: `346 / 8 = 43.25`, so no. For a faster check on the three digits, halve three times: 344 → 172 → 86 → 43, all whole numbers, so it is a multiple of 8.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>It works because 10, 100, 1000 … all leave remainder 1 on division by 3, so each digit contributes exactly its own value to the remainder.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>4,938 → `4+9+3+8 = 24`, a multiple of 3, so yes. 987,654 → 39 → `3+9 = 12`, so yes.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Primes &amp; Factors</t>
+          <t>Unit Digits &amp; Divisibility Rules</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Divisibility by 6 and other composites</t>
+          <t>Divisibility by 9?</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>There is no separate digit trick for 6. Instead, split 6 into `2 x 3` and apply both rules: a number is divisible by 6 exactly when it is even *and* its digits sum to a multiple of 3. The same method builds a test for any composite number out of the tests you already know.
-The one condition is that the factors you split into must be **coprime** (share no factor). `12 = 4 x 3` works, because 4 and 3 are coprime. `12 = 2 x 6` does not, because 2 and 6 share a factor, and every multiple of 2 that is also a multiple of 6 is really just a multiple of 6.</t>
+          <t>The same digit sum, but it must be a multiple of **9**.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Is 4,938 divisible by 6? It is even, and `4+9+3+8 = 24` is a multiple of 3, so yes. Is 7,316 divisible by 12? It is divisible by 4 (last two digits 16) but `7+3+1+6 = 17` is not a multiple of 3, so no.</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+          <t>Every multiple of 9 is therefore also a multiple of 3, though the reverse fails.
+Repeating the digit sum until one digit is left gives the *digital root*, and a digital root of 9 is the same test. It is a quick way to check arithmetic: the digital roots of the inputs must match the digital root of the answer.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4,938: digits sum to 24, divisible by 3 but not 9 → multiple of 3 only. 4,932: digits sum to 18 → divisible by 9 and by 3.
+Digital root of 987,654: `39 → 12 → 3`, so it is divisible by 3 but not 9.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Primes &amp; Factors</t>
+          <t>Unit Digits &amp; Divisibility Rules</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Divisibility by 11</t>
+          <t>Divisibility by 4?</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Alternate the signs of the digits from left to right, starting with plus, then add them up. If that alternating sum is a multiple of 11 (including 0), the number is divisible by 11.
-The rule comes from the fact that 10 leaves remainder -1 on division by 11, so each place value flips sign as you move left.</t>
+          <t>Look only at the **last two digits**. If that two-digit number is a multiple of 4, so is the whole number.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Is 918,082 divisible by 11? `+9 -1 +8 -0 +8 -2 = 22`, which is a multiple of 11, so yes. Is 4,938? `+4 -9 +3 -8 = -10`, not a multiple of 11, so no.</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
+          <t>100 is itself a multiple of 4, so the hundreds and everything above them can never affect the answer. Anything ending in 00 is divisible by 4.
+A second shortcut: if the tens digit is even, the number is divisible by 4 exactly when the unit digit is 0, 4 or 8; if the tens digit is odd, the unit digit must be 2 or 6.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7,318 → 18 is not a multiple of 4, so no. 7,316 → 16 is, so yes.
+Squares are a good stress test: every even square is divisible by 4 (`14^2 = 196` → 96 ✓), and every odd square leaves remainder 1.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Primes &amp; Factors</t>
+          <t>Unit Digits &amp; Divisibility Rules</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Testing whether a number is prime</t>
+          <t>Divisibility by 8?</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>To check whether `n` is prime, try dividing by the primes up to `sqrt(n)` and stop there. You do not need to go further, because if `n` had a factor larger than its square root, it would have to be paired with one smaller than the square root, which you would already have found.
-In practice that means testing 2, 3, 5, 7, 11, 13 — enough to settle every number below 289.</t>
+          <t>Look at the **last three digits**, because 1,000 is a multiple of 8. Anything ending in 000 qualifies.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Is 191 prime? `sqrt(191) ≈ 13.8`, so test 2, 3, 5, 7, 11, 13. It is odd; digits sum to 11 so not divisible by 3; does not end in 0 or 5; `191/7 ≈ 27.3`; `191/11 ≈ 17.4`; `191/13 ≈ 14.7`. None divide it, so 191 is prime.</t>
+          <t>For a quick check on those three digits, halve three times — if you stay on whole numbers, it divides.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1 is not prime, and 2 is the only even prime — the single most common source of "all primes are odd" errors in comparison questions.</t>
-        </is>
-      </c>
+          <t>12,344 → 344, and `344 / 8 = 43` exactly, so yes. Halving: 344 → 172 → 86 → 43 ✓. 12,346 → 346 → 173 → 86.5 ✗.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Primes &amp; Factors</t>
+          <t>Unit Digits &amp; Divisibility Rules</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Prime factorization is the master key</t>
+          <t>Divisibility by 6, 12 or any composite?</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Every integer greater than 1 breaks down into a unique product of primes, and almost every factor, GCF, LCM, divisibility and root question on the GRE is really asking you to look at that breakdown. Getting into the habit of writing a number as its prime factorization before doing anything else is the highest-return habit in the quant section.
-Build it by dividing out the smallest prime repeatedly: `360 / 2 = 180 / 2 = 90 / 2 = 45 / 3 = 15 / 3 = 5 / 5 = 1`, giving `360 = 2^3 x 3^2 x 5`.</t>
+          <t>Split it into **coprime** factors and apply both rules. 6 = 2 x 3, so even **and** digit sum divisible by 3. 12 = 4 x 3, so the last two digits divide by 4 **and** the digit sum by 3.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>`60 = 2^2 x 3 x 5`. From that one line you can read off that 60 is divisible by 4 (there are two 2s), not by 8 (there is no third 2), not by 9 (only one 3), and that it has 12 factors in total.</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
+          <t>The factors must share no common factor. `12 = 2 x 6` is useless, because every number divisible by 2 and 6 is just divisible by 6.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4,938: even ✓, digits sum to 24 ✓ → divisible by 6. 7,316: last two digits 16 divide by 4 ✓, but `7+3+1+6 = 17` is not a multiple of 3 ✗ → not divisible by 12.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Primes &amp; Factors</t>
+          <t>Unit Digits &amp; Divisibility Rules</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>What three consecutive integers guarantee</t>
+          <t>Divisibility by 11?</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Consecutive integers hand you divisibility facts for free. Among any three consecutive integers exactly one is a multiple of 3, so the product is always divisible by 3; at least one is even, so the product is divisible by 2; together that makes the product always divisible by 6. Their sum is also always a multiple of 3 (it equals three times the middle number).
-There is a bonus case: if the middle number is odd, then the outer two are both even and one of them is a multiple of 4, so the product is divisible by 8 as well — and therefore by 24.
-The same reasoning extends to three consecutive *multiples* of a number: their sum is three times the middle one, and the product keeps the divisibility of the base.</t>
+          <t>Alternate the digit signs from left to right starting with plus, and add. If that alternating sum is a multiple of 11 (0 counts), so is the number.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>`5 x 6 x 7 = 210 = 6 x 35`, divisible by 6. `7 x 8 x 9 = 504`, and because the middle number 8 is even the "divisible by 8" bonus does not apply here — check instead `6 x 7 x 8 = 336 = 24 x 14`, where the middle number 7 is odd, so 336 is divisible by 8 and by 24.</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+          <t>10 leaves remainder -1 on division by 11, so each place value flips sign as you move left.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>918,082 → `+9 -1 +8 -0 +8 -2 = 22`, a multiple of 11, so yes (`918,082 / 11 = 83,462`). 4,938 → `+4 -9 +3 -8 = -10` ✗.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1195,26 +1312,34 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Primes &amp; Factors</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Writing consecutive integers algebraically</t>
+          <t>How far do you test before declaring `n` prime?</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>When a problem describes consecutive numbers, naming them properly turns the words into one equation. Three consecutive integers are `n, n+1, n+2`. Three consecutive even numbers are `2n, 2n+2, 2n+4`. Three consecutive odd numbers are `2n+1, 2n+3, 2n+5`. Three consecutive multiples of 7 are `7n, 7n+7, 7n+14`.
-Centring on the middle term is often faster still: writing them as `n-1, n, n+1` makes the sum `3n` immediately.</t>
+          <t>Divide by the primes up to `sqrt(n)` and stop. In practice 2, 3, 5, 7, 11, 13 settles everything below 289.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>The sum of three consecutive odd integers is 87; what is the largest? Write `(2n+1) + (2n+3) + (2n+5) = 87`, so `6n + 9 = 87`, `n = 13`, and the integers are 27, 29, 31. Or use the centre trick: the sum is 3 times the middle number, so the middle is 29 and the largest is 31.</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
+          <t>If `n` had a factor larger than its square root, that factor would be paired with one *smaller* than the square root — which you would already have found. So there is nothing above the square root left to check.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Is 191 prime? `sqrt(191) ≈ 13.8`. It is odd; digits sum to 11 (not a multiple of 3); it does not end in 0 or 5; `191/7 ≈ 27.3`, `191/11 ≈ 17.4`, `191/13 ≈ 14.7`. None divide, so **yes**.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1 is not prime, and 2 is the only even prime — the source of most "all primes are odd" errors.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1222,26 +1347,30 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Primes &amp; Factors</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Divisibility travels through products</t>
+          <t>Prime factorization — why is it the first move on so many questions?</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>If `a` is divisible by `p^m` and `b` is divisible by `p^n`, then `ab` is divisible by `p^(m+n)`. Factors do not disappear when you multiply; they accumulate. This is the rule behind almost every "must be divisible by" question.
-The reverse also matters: to prove a product is divisible by 12, find a 4 in one factor and a 3 in another — you do not need either factor to be divisible by 12 on its own.</t>
+          <t>Because every integer above 1 is a unique product of primes, and factor counts, GCF, LCM, divisibility and rational roots are all read straight off that product. Build it by dividing out the smallest prime repeatedly.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>If `a` is divisible by 4 (`2^2`) and `b` is divisible by 6 (`2 x 3`), then `ab` is divisible by `2^3 x 3 = 24`. So `a = 8, b = 18` gives `ab = 144`, and `144 / 24 = 6` exactly.</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+          <t>`360 / 2 = 180 / 2 = 90 / 2 = 45 / 3 = 15 / 3 = 5 / 5 = 1`, so `360 = 2^3 x 3^2 x 5`. Writing this line before doing anything else is the highest-return habit in the quant section.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>`60 = 2^2 x 3 x 5`. From that one line: divisible by 4 (two 2s), not by 8 (no third 2), not by 9 (only one 3), and it has 12 factors.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1249,29 +1378,30 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Primes &amp; Factors</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Counting the factors of a number</t>
+          <t>Which squares, cubes and roots should you know cold?</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Prime factorize, add 1 to every exponent, and multiply those results together. The rule works because building a factor means choosing how many copies of each prime to take, and for a prime with exponent `e` you have `e + 1` choices: none, one, two, …, up to `e`.</t>
+          <t>Squares to 20: 121, 144, 169, 196, 225, 256, 289, 324, 361, 400. Cubes to 6: 8, 27, 64, 125, 216. Powers of 2 to 10: 1024. And `sqrt(2) ≈ 1.41`, `sqrt(3) ≈ 1.73`, `sqrt(5) ≈ 2.24`.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>How many factors does 60 have? `60 = 2^2 x 3^1 x 5^1`, so the count is `(2+1)(1+1)(1+1) = 3 x 2 x 2 = 12`. Listing them confirms it: 1, 2, 3, 4, 5, 6, 10, 12, 15, 20, 30, 60.</t>
+          <t>Recognition is speed. Seeing that 196 is `14^2`, or that 1.73 is `sqrt(3)` in disguise, turns a 40-second question into a 5-second one, and it is what lets you estimate radical answers without a calculator.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>This counts *all* factors including 1 and the number itself. A perfect square always has an odd number of factors, because one of its exponents-plus-one pairings is the square root pairing with itself.</t>
-        </is>
-      </c>
+          <t>Simplify `sqrt(288)`. Recognising `288 = 144 x 2` gives `12sqrt(2) ≈ 16.97` at once. And a triangle side of `8.66` should immediately read as `5sqrt(3)`.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1279,25 +1409,31 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Primes &amp; Factors</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Counting the odd factors</t>
+          <t>Three consecutive integers — what is guaranteed?</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>An odd number can have no even factors, so delete the whole power of 2 from the prime factorization and apply the same exponent-plus-one rule to what is left. The 2s were the only thing making factors even, so removing them counts exactly the odd factors.</t>
+          <t>Exactly one is a multiple of 3, at least one is even, so the **product is always divisible by 6** and the **sum is always a multiple of 3**. If the middle one is odd, the product is also divisible by 8, hence by 24.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Odd factors of 60? `60 = 2^2 x 3 x 5`; drop the `2^2` to get `3 x 5`, so the count is `(1+1)(1+1) = 4`. Those are 1, 3, 5 and 15.</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
+          <t>The bonus case works because an odd middle forces both outer numbers to be even, and one of any two consecutive evens is a multiple of 4.
+The same reasoning extends to three consecutive *multiples* of a number: the sum is three times the middle one.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>`5 x 6 x 7 = 210 = 6 x 35` ✓. `6 x 7 x 8 = 336 = 24 x 14` — middle number 7 is odd, so the divisible-by-24 bonus applies.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1305,229 +1441,263 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Primes &amp; Factors</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Counting the even factors</t>
+          <t>How do you name consecutive numbers in algebra?</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Every factor is either odd or even, so the even count is simply total factors minus odd factors. (Equivalently: an even factor must contain at least one 2, so with `2^a` in the factorization you have `a` choices for the power of 2 instead of `a + 1`.)</t>
+          <t>Integers: `n, n+1, n+2`. Evens: `2n, 2n+2, 2n+4`. Odds: `2n+1, 2n+3, 2n+5`. Multiples of 7: `7n, 7n+7, 7n+14`. Or centre them: `n-1, n, n+1`, whose sum is just `3n`.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>60 has 12 factors, 4 of which are odd, so 8 are even: 2, 4, 6, 10, 12, 20, 30, 60. The other route gives the same thing: `2 x (1+1)(1+1) = 8`.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
+          <t>Naming them properly turns a sentence into one equation, and centring on the middle term usually halves the algebra.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Three consecutive odd integers sum to 87; what is the largest? `(2n+1)+(2n+3)+(2n+5) = 87` → `6n + 9 = 87` → `n = 13`, giving 27, 29, 31. Or: the sum is 3 times the middle, so the middle is 29 and the largest is **31**.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Greatest common factor from prime factorizations</t>
+          <t>`a` is divisible by `p^m` and `b` by `p^n` — what about `ab`?</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>The GCF is the largest number that divides all of them. Prime factorize every number, then for each prime that appears in *all* of them take the **lowest** power. Multiply those together and you have the GCF. A prime missing from any one number cannot appear in the GCF at all.
-Think of it as "what do they all have in common" — you can only share as many copies of a prime as the stingiest number has.</t>
+          <t>`ab` is divisible by `p^(m+n)`. Factors accumulate when you multiply; they never disappear.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>GCF of 60 and 72. `60 = 2^2 x 3 x 5` and `72 = 2^3 x 3^2`. Shared primes are 2 and 3. Lowest power of 2 is `2^2`, lowest power of 3 is `3^1`, and 5 is missing from 72 so it is out. GCF `= 4 x 3 = 12`.</t>
+          <t>This is the rule behind nearly every "must be divisible by" question. It also works in reverse: to show a product is divisible by 12, find a 4 in one factor and a 3 in another — neither factor needs to be divisible by 12 itself.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>If two numbers share no prime at all, their GCF is 1 and they are called coprime — not zero.</t>
-        </is>
-      </c>
+          <t>`a` divisible by 4 (`2^2`), `b` divisible by 6 (`2 x 3`) → `ab` divisible by `2^3 x 3 = 24`. Taking `a = 8, b = 18` gives 144, and `144 / 24 = 6` ✓.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Factors shared by a group are the factors of their GCF</t>
+          <t>How many factors does a number have?</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>"How many factors do 60 and 72 have in common?" is the same question as "how many factors does their GCF have". Build the GCF, then apply the exponent-plus-one counting rule to it. There is no need to list anything.
-This is worth internalising because it converts a vague-sounding question into two steps you already know cold.</t>
+          <t>Prime factorize, **add 1 to every exponent, and multiply**. For `60 = 2^2 x 3^1 x 5^1` that is `3 x 2 x 2 = 12`.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Common factors of 60 and 72: the GCF is `12 = 2^2 x 3`, so the count is `(2+1)(1+1) = 6`. They are 1, 2, 3, 4, 6, 12 — and you can see each one divides both 60 and 72.</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr"/>
+          <t>Building a factor means choosing how many copies of each prime to take, and a prime with exponent `e` gives you `e + 1` choices: none, one, …, up to `e`.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>60's twelve factors: 1, 2, 3, 4, 5, 6, 10, 12, 15, 20, 30, 60 ✓.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>The count includes 1 and the number itself. A perfect square always has an **odd** number of factors, since its square root pairs with itself.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Least common multiple from prime factorizations</t>
+          <t>How many **odd** factors does a number have?</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>The LCM is the smallest number all of them divide into. Prime factorize, then for each prime that appears in *any* of them take the **highest** power, and multiply. Where the GCF asks what they share, the LCM asks what is needed to satisfy everyone.</t>
+          <t>Delete the whole power of 2 from the prime factorization, then use the same exponent-plus-one rule on what is left.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>LCM of 60 and 72. `60 = 2^2 x 3 x 5`, `72 = 2^3 x 3^2`. Highest power of 2 is `2^3`, of 3 is `3^2`, of 5 is `5^1`. LCM `= 8 x 9 x 5 = 360`. Sanity check: `360/60 = 6` and `360/72 = 5`, both whole.</t>
+          <t>The 2s were the only thing capable of making a factor even, so removing them counts exactly the odd ones.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>The LCM of two numbers is never smaller than the larger of them, and the GCF is never bigger than the smaller. If your answer breaks that, you have swapped the rules.</t>
-        </is>
-      </c>
+          <t>Odd factors of 60? Drop the `2^2` from `2^2 x 3 x 5` to get `3 x 5`, giving `(1+1)(1+1) = 4`: 1, 3, 5, 15.
+Another: `360 = 2^3 x 3^2 x 5` → drop the `2^3` → `(2+1)(1+1) = 6` odd factors: 1, 3, 5, 9, 15, 45.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Divisible by a and by b means divisible by their LCM</t>
+          <t>How many **even** factors does a number have?</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>If a number is a multiple of `a` and also a multiple of `b`, then it is a multiple of `LCM(a, b)` — not necessarily of `a x b`. This is the rule people get wrong: a number divisible by 4 and by 6 must be divisible by 12, not by 24.
-Only when `a` and `b` are coprime does `LCM(a, b) = a x b`, which is why "divisible by 3 and by 5" does safely mean "divisible by 15".</t>
+          <t>Total factors minus odd factors. (Or: with `2^a` in the factorization, use `a` choices for the power of 2 instead of `a + 1`.)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>`n` is divisible by 8 and by 12. `LCM(8, 12) = 24`, so `n` must be a multiple of 24. `n = 24` works and is not a multiple of `8 x 12 = 96`, which proves the product version is wrong.</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
+          <t>Every factor is either odd or even, so the subtraction is exact.
+A number with no 2 in its factorization is odd, so it has *zero* even factors — worth checking before you start subtracting.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>60 has 12 factors and 4 odd ones, so **8** are even: 2, 4, 6, 10, 12, 20, 30, 60. The other route: `2 x (1+1)(1+1) = 8` ✓.
+For 360: 24 factors in total, 6 odd, so 18 even. The direct route agrees: `3 x (2+1)(1+1) = 18`.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>GCF times LCM equals the product</t>
+          <t>Greatest common factor of a group of numbers?</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>For any two positive integers, `GCF(a, b) x LCM(a, b) = a x b`. Every prime appears in the pair with a lower and a higher exponent, and the GCF takes the lower one while the LCM takes the higher, so between them they use up exactly the exponents in `a x b`.
-This gives you a free shortcut whenever a question hands you three of the four quantities.</t>
+          <t>Prime factorize them all, then for each prime that appears in **every** number take the **lowest** power, and multiply.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>`a = 60`, `b = 72`, `GCF = 12`. Then `LCM = (60 x 72)/12 = 4,320/12 = 360`, matching the direct computation. And if a question says two numbers multiply to 1,200 with a GCF of 10, the LCM is `1,200/10 = 120` with no factorization needed.</t>
+          <t>You can only share as many copies of a prime as the stingiest number has, and a prime missing from any one number cannot appear at all.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>This identity holds for two numbers only. For three or more it breaks down.</t>
+          <t>GCF of 60 (`2^2 x 3 x 5`) and 72 (`2^3 x 3^2`): shared primes 2 and 3, lowest powers `2^2` and `3^1`, and 5 is out. GCF `= 12`.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Numbers sharing no prime have a GCF of **1**, not 0 — they are called coprime.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Simplifying a quotient of factorials</t>
+          <t>How many factors do two numbers have in common?</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>`n!` means `n x (n-1) x (n-2) x ... x 1`, so a bigger factorial contains a smaller one whole. When you divide `m!` by `n!` with `m &gt; n`, everything up to `n!` cancels and you are left with the handful of terms in between — never compute the factorials themselves.
-`m!/n! = m x (m-1) x ... x (n+1)`.</t>
+          <t>Count the factors of their **GCF**. Build the GCF, then apply the exponent-plus-one rule to it.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>`8!/5! = (8 x 7 x 6 x 5!)/5! = 8 x 7 x 6 = 336`. Similarly `100!/98! = 100 x 99 = 9,900`, which you can do in your head, while `100!` has 158 digits.</t>
+          <t>Any number dividing both must divide their greatest common factor, so the shared factors are exactly the GCF's factors. No listing required.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>`0! = 1` by definition, which keeps formulas like `nPn = n!/0!` working.</t>
-        </is>
-      </c>
+          <t>60 and 72 have GCF `12 = 2^2 x 3`, so `(2+1)(1+1) = 6` common factors: 1, 2, 3, 4, 6, 12 ✓.
+Another: 84 (`2^2 x 3 x 7`) and 126 (`2 x 3^2 x 7`) have GCF `2 x 3 x 7 = 42`, so `(1+1)(1+1)(1+1) = 8` common factors.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>Primes, Factors &amp; GCF</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Legendre's method: the prime factorization of n!</t>
+          <t>Least common multiple of a group of numbers?</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>`n!` is far too big to factorize by multiplying out, but you can count each prime directly. For a prime `p`, count how many multiples of `p` are at or below `n`, then how many multiples of `p^2`, then `p^3`, and so on until the count reaches zero. The total is the exponent of `p` in `n!`.
-The reason for the extra rounds is that a number like 9 contributes *two* 3s to the product, so it has to be counted once as a multiple of 3 and again as a multiple of 9.</t>
+          <t>Prime factorize, then for each prime appearing in **any** of them take the **highest** power, and multiply.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Exponent of 3 in `10!`: multiples of 3 up to 10 are 3, 6, 9 → 3 of them; multiples of 9 are just 9 → 1; multiples of 27 → 0. Total `3 + 1 = 4`, so `10!` contains `3^4`. Doing the same for 2 (5 + 2 + 1 = 8), 5 (2) and 7 (1) gives `10! = 2^8 x 3^4 x 5^2 x 7`.</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
+          <t>Where the GCF asks what they share, the LCM asks what it takes to satisfy everyone.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>LCM of 60 (`2^2 x 3 x 5`) and 72 (`2^3 x 3^2`): `2^3 x 3^2 x 5 = 360`. Check: `360/60 = 6` and `360/72 = 5` ✓.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>The LCM is never smaller than the largest number and the GCF never bigger than the smallest. If that fails, you have swapped the rules.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1535,26 +1705,30 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Legendre's shortcut: keep dividing</t>
+          <t>`n` is divisible by `a` and by `b` — what else must it be divisible by?</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>You do not have to list multiples. Divide `n` by `p` and drop the decimal, then divide that result by `p` again, and keep going until you hit 0. Adding up everything you wrote down gives the exponent.
-Each division is asking the same question one level deeper, which is exactly what counting multiples of `p`, `p^2`, `p^3` does.</t>
+          <t>`LCM(a, b)` — **not** `a x b`. A number divisible by 4 and by 6 must be divisible by 12, not 24.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Exponent of 5 in `100!`: `100/5 = 20`, `20/5 = 4`, `4/5 = 0`. Total `20 + 4 = 24`. Exponent of 2 in `100!`: 50, 25, 12, 6, 3, 1, 0 → `50+25+12+6+3+1 = 97`.</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
+          <t>Only when `a` and `b` are coprime does `LCM(a, b) = a x b`, which is why "divisible by 3 and by 5" safely means "divisible by 15".</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>`n` divisible by 8 and 12 → `LCM = 24`, so `n` is a multiple of 24. And `n = 24` itself is not a multiple of `8 x 12 = 96`, which kills the product version.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1562,25 +1736,34 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>How many factors does a factorial have</t>
+          <t>What is the relationship between GCF, LCM and the numbers themselves?</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Use Legendre's method to get the prime factorization of `n!`, then apply the ordinary exponent-plus-one rule. There is no separate formula — it is the two techniques stacked.</t>
+          <t>`GCF(a, b) x LCM(a, b) = a x b` — for **two** numbers only.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>How many factors does `10!` have? From above, `10! = 2^8 x 3^4 x 5^2 x 7^1`, so the count is `(8+1)(4+1)(2+1)(1+1) = 9 x 5 x 3 x 2 = 270`.</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
+          <t>Each prime appears in the pair with a lower and a higher exponent; the GCF takes the lower, the LCM the higher, so together they use up exactly the exponents in `a x b`.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>`a = 60, b = 72, GCF = 12` → `LCM = (60 x 72)/12 = 360` ✓. If two numbers multiply to 1,200 with GCF 10, the LCM is `1,200/10 = 120` with no factorization at all.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>The identity breaks for three or more numbers.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -1588,26 +1771,34 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>How many copies of r are inside n!</t>
+          <t>`m!/n!` with `m &gt; n` — how do you simplify it?</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>If `r` is prime, run Legendre's method for `r` and you are done. If `r` is composite, factorize it first, run Legendre separately for each of its primes, then see which prime runs out first — that bottleneck is your answer.
-The bottleneck logic is the point: making one copy of `r` uses one of each of its primes, so you can only make as many copies as the scarcest ingredient allows.</t>
+          <t>Cancel the smaller factorial: `m!/n! = m x (m-1) x ... x (n+1)`. Never compute the factorials themselves.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>How many copies of 15 are inside `20!`? `15 = 3 x 5`. Exponent of 3: `20/3 = 6`, `6/3 = 2`, `2/3 = 0` → 8. Exponent of 5: `20/5 = 4`, `4/5 = 0` → 4. The 5s run out first, so `20!` contains 4 copies of 15.</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
+          <t>`n!` sits inside `m!` whole, so everything up to `n!` cancels and only the handful of terms in between survive.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>`8!/5! = (8 x 7 x 6 x 5!)/5! = 336`. And `100!/98! = 100 x 99 = 9,900` in your head, while `100!` has 158 digits.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>`0! = 1` by definition, which keeps formulas like `nPn = n!/0!` working.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -1615,30 +1806,30 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Largest power of r that divides n!</t>
+          <t>How do you find the prime factorization of `n!`?</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>This is the same machinery in its most common exam form: "if `n!/r^x` is an integer, what is the largest `x`?" Run Legendre for each prime in `r`. If a prime appears in `r` with an exponent of its own, divide that prime's Legendre total by the exponent and drop the decimal. The smallest result across all the primes is the answer.</t>
+          <t>Legendre's method: for each prime `p`, count the multiples of `p` up to `n`, then the multiples of `p^2`, then `p^3`, until the count hits 0. The total is the exponent of `p`.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>If `30!/3^x` is an integer, what is the largest `x`? Legendre for 3: `30/3 = 10`, `10/3 = 3`, `3/3 = 1`, `1/3 = 0`. Total `10 + 3 + 1 = 14`, so `x = 14`.
-Harder: if `100!/24^x` is an integer, what is the largest `x`? `24 = 2^3 x 3`. Legendre for 2 gives 97, but each 24 needs three 2s, so `97/3 = 32.3 → 32`. Legendre for 3 gives `33 + 11 + 3 + 1 = 48`, and each 24 needs one 3, so 48. The minimum is **32**.</t>
+          <t>The extra rounds exist because a number like 9 contributes *two* 3s, so it must be counted once as a multiple of 3 and again as a multiple of 9.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Take the floor *after* dividing by the exponent, and take the minimum across primes at the very end — swapping those two steps gives the wrong answer.</t>
-        </is>
-      </c>
+          <t>Exponent of 3 in `10!`: multiples of 3 are 3, 6, 9 → 3; multiples of 9 → 1; multiples of 27 → 0. Total **4**. Doing all the primes gives `10! = 2^8 x 3^4 x 5^2 x 7`.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -1646,228 +1837,256 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>GCF, LCM &amp; Factorials</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Trailing zeros of a factorial</t>
+          <t>Legendre's method without listing multiples?</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>A trailing zero comes from a factor of 10, and `10 = 2 x 5`. In any factorial the 2s vastly outnumber the 5s, so the number of trailing zeros is just the number of 5s: run Legendre for 5 and stop.</t>
+          <t>Divide `n` by `p` and drop the decimal, divide that result by `p` again, and keep going until you reach 0. Add up everything you wrote.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>How many zeros does `100!` end in? Legendre for 5: `100/5 = 20`, `20/5 = 4`, `4/5 = 0`, total **24**. Note that counting `100/5 = 20` alone is the classic mistake — 25, 50, 75 and 100 each contribute a second 5.</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
+          <t>Each division asks the same question one level deeper, which is exactly what counting multiples of `p`, `p^2`, `p^3` does.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Exponent of 5 in `100!`: `100/5 = 20`, `20/5 = 4`, `4/5 = 0` → **24**. Exponent of 2 in `100!`: 50, 25, 12, 6, 3, 1 → **97**.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Numbers that are not factors of n!</t>
+          <t>How many factors does `n!` have?</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>`n!` contains every integer from 1 to `n` as a factor, so the first number that fails to divide it must involve a prime bigger than `n`. The smallest non-factor is therefore the next prime after `n`, and the next few are that prime's multiples and the primes beyond it.</t>
+          <t>Legendre for the prime factorization, then the ordinary exponent-plus-one rule. No separate formula — two techniques stacked.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>What is the smallest integer greater than 1 that is not a factor of `10!`? Every number up to 10 divides it, and so do products built from those primes (12 = 4x3, 14 = 2x7, 15 = 3x5 all divide it). The first failure is **11**, the next prime. After that come 13, 17, 19 and 22 (= 2 x 11, which needs an 11 that `10!` does not have).</t>
+          <t>The only work is being systematic about every prime up to `n`.
+The counts grow startlingly fast, which is why these questions always name a small factorial: `10!` has 270 factors, but `15!` has 4,032.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Do not stop at "the next number after n". 11 works for `10!` only because 11 happens to be prime; for `12!` the smallest non-factor is 13, not 14 (`14 = 2 x 7`, both present).</t>
-        </is>
-      </c>
+          <t>`10! = 2^8 x 3^4 x 5^2 x 7^1`, so the count is `(8+1)(4+1)(2+1)(1+1) = 270`.
+For `6! = 720 = 2^4 x 3^2 x 5`: `(4+1)(2+1)(1+1) = 30` factors. Legendre gives the exponents: 2 → `3+1 = 4`, 3 → `2`, 5 → `1`.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Counting the integers in a range</t>
+          <t>How many copies of `r` are inside `n!`?</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>The number of integers from `a` to `b` **inclusive** is `b - a + 1`. The `+1` is there because subtraction counts the gaps between the numbers, not the numbers themselves, and there is always one more fencepost than fence. If both endpoints are excluded, the count is `b - a - 1`.</t>
+          <t>If `r` is prime, run Legendre for `r`. If `r` is composite, factorize it, run Legendre for each prime, and take the **minimum** — the scarcest prime is the bottleneck.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>How many integers from 17 to 63 inclusive? `63 - 17 + 1 = 47`. Check with something tiny: from 3 to 5 inclusive there are 3 numbers, and `5 - 3 + 1 = 3`. Strictly between 17 and 63 there are `63 - 17 - 1 = 45`.</t>
+          <t>Making one copy of `r` uses one of each of its primes, so you can build only as many as the rarest ingredient allows.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>"Between" is ambiguous in English but almost always means exclusive on the GRE; "from … to …" and "inclusive" mean both ends count.</t>
-        </is>
-      </c>
+          <t>Copies of 15 inside `20!`? `15 = 3 x 5`. 3s: `20/3 = 6`, `6/3 = 2` → 8. 5s: `20/5 = 4` → 4. The 5s run out first, so **4**.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Sum of a range of integers</t>
+          <t>If `n!/r^x` is an integer, what is the largest `x`?</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>For any evenly spaced list, the sum is the average times the number of terms, and the average of an evenly spaced list is just the midpoint of the first and last terms. So for the integers from `a` to `b`:
-`sum = ((a + b)/2) x (b - a + 1)`
-The first bracket is the average, the second is the count. This beats the `n(n+1)/2` formula whenever the list does not start at 1.</t>
+          <t>Legendre each prime of `r`; if a prime carries an exponent inside `r`, divide that prime's total by the exponent and drop the decimal; then take the **minimum** across primes.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sum of the integers from 17 to 63. Average `= (17 + 63)/2 = 40`. Count `= 63 - 17 + 1 = 47`. Sum `= 40 x 47 = 1,880`.</t>
+          <t>The floor comes *after* dividing by the exponent, and the minimum comes at the very end. Swapping those two steps gives the wrong answer.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>The count is `b - a + 1`, not `a - b + 1`. Getting the subtraction backwards gives a negative count and a nonsense answer.</t>
-        </is>
-      </c>
+          <t>`30!/3^x`: Legendre for 3 gives `10 + 3 + 1 = 14`, so **x = 14**.
+Harder — `100!/24^x`, where `24 = 2^3 x 3`. Legendre for 2 gives 97, but each 24 needs three 2s: `97/3 = 32.3 → 32`. Legendre for 3 gives `33+11+3+1 = 48`, one per 24 → 48. Minimum: **32**.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Counting multiples in a range</t>
+          <t>How many zeros does `n!` end in?</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Find the smallest multiple of `r` at or above the bottom of the range and the largest at or below the top, then count the steps between them and add one:
-`count = (last - first)/r + 1`
-Dividing by `r` converts a distance into a number of steps, and the `+1` is the same fencepost correction as before.</t>
+          <t>Count the **5s** — run Legendre for 5 and stop. A trailing zero needs a `2 x 5`, and the 2s always outnumber the 5s.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>How many multiples of 7 between 50 and 200? The first is 56 (`7 x 8`) and the last is 196 (`7 x 28`). Count `= (196 - 56)/7 + 1 = 20 + 1 = 21`. You can check it against the multiplier index: from `7 x 8` to `7 x 28` is `28 - 8 + 1 = 21` terms.</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
+          <t>The only work is remembering the higher powers: 25, 50, 75 and 100 each contribute a second 5.
+The reverse question is common too: "for which `n` does `n!` first end in 6 zeros?" Walk the counts up — `20!` has 4, `25!` has 6 (25 contributes two 5s), so the answer is 25.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>`100!` ends in `20 + 4 = 24` zeros. Answering 20 is the classic mistake.
+`50!`: `50/5 = 10`, `10/5 = 2` → 12 zeros. `200!`: `40 + 8 + 1 = 49` zeros.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Sum of multiples in a range</t>
+          <t>Smallest integer that is **not** a factor of `n!`?</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Same two pieces as any evenly spaced list: average times count. Find the first and last multiples in the range, average them, and multiply by the count you just computed.
-`sum = ((first + last)/2) x ((last - first)/r + 1)`</t>
+          <t>The next **prime** after `n`. Every integer up to `n` divides `n!`, so the first failure must need a prime bigger than `n`.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sum of the multiples of 7 between 50 and 200. First 56, last 196. Average `= (56 + 196)/2 = 126`. Count `= 21` from above. Sum `= 126 x 21 = 2,646`.</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
+          <t>After that first prime come its multiples and the primes beyond it. Do not just take "the next number after n" — that only works when it happens to be prime.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Smallest non-factor of `10!` is **11**. Next come 13, 17, 19 and 22 (`= 2 x 11`). For `12!` it is 13, not 14, since `14 = 2 x 7` and both are present.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Types of sequences</t>
+          <t>How many integers are there from `a` to `b`?</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Identify a sequence by what stays constant when you look at the differences. **Arithmetic**: constant difference between terms (5, 8, 11, 14). **Geometric**: constant ratio, each term is the last times a fixed number (5, 10, 20, 40). **Quadratic**: the differences are not constant but the differences *of the differences* are. **Cubic**: constant third difference, and so on for higher powers.
-Writing out the difference rows is the fastest diagnostic: if row one is constant it is arithmetic, if row two is constant it is quadratic, and if the ratio row is constant it is geometric.</t>
+          <t>Inclusive: `b - a + 1`. Exclusive at both ends: `b - a - 1`. Subtraction counts gaps, and there is always one more fencepost than fence.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1, 4, 9, 16, 25: differences are 3, 5, 7, 9 — not constant. Their differences are 2, 2, 2 — constant. So it is quadratic, and indeed the terms are `n^2`.</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr"/>
+          <t>"Between" on the GRE almost always means exclusive; "from … to …" and "inclusive" mean both ends count.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>From 17 to 63 inclusive: `63 - 17 + 1 = 47`. Sanity check on a tiny case: 3 to 5 inclusive is 3 numbers ✓. Strictly between: 45.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>LCM, Factorials &amp; Ranges</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>The sum formulas worth memorising</t>
+          <t>Sum of all the integers from `a` to `b`?</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Two show up often enough to be worth knowing outright:
-`1 + 2 + 3 + ... + n = n(n+1)/2`
-`1^2 + 2^2 + 3^2 + ... + n^2 = n(n+1)(2n+1)/6`
-The first is just average-times-count in disguise: the average is `(1+n)/2` and there are `n` terms.</t>
+          <t>`sum = ((a + b)/2) x (b - a + 1)` — the average of the endpoints times the count. True for any evenly spaced list.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>`1 + 2 + ... + 100 = 100 x 101/2 = 5,050`. And `1^2 + 2^2 + ... + 10^2 = 10 x 11 x 21/6 = 385`. If a question asks for `1 + 2 + ... + 50` where the list starts at 11 instead, subtract: `(50 x 51/2) - (10 x 11/2) = 1,275 - 55 = 1,220`.</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
+          <t>Evenly spaced lists are symmetric, so their average is exactly the midpoint of the first and last terms. This beats `n(n+1)/2` whenever the list does not start at 1.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Sum from 17 to 63: average `= 40`, count `= 47`, so `40 x 47 = 1,880`.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>The count is `b - a + 1`, not `a - b + 1`. Reversing the subtraction gives a negative count and nonsense.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -1875,31 +2094,30 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Sum of a geometric series</t>
+          <t>How many multiples of `r` lie between `a` and `b`?</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>For a geometric sequence with first term `a` and ratio `r`, the sum of the first `n` terms is
-`sum = a(r^n - 1)/(r - 1)`
-Unlike an arithmetic series you cannot use average-times-count, because the terms are not evenly spaced — the later terms dominate.</t>
+          <t>`count = (last - first)/r + 1`, where `first` is the smallest multiple of `r` in range and `last` the largest.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Sum of the first 20 terms of 3, 6, 12, 24, … Here `a = 3` and `r = 2`, so `sum = 3(2^20 - 1)/(2 - 1) = 3 x (1,048,576 - 1) = 3 x 1,048,575 = 3,145,725`.</t>
+          <t>Dividing by `r` converts a distance into a number of steps, and the `+1` is the same fencepost correction as counting integers.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>When `|r| &lt; 1` the terms shrink and the sum converges; an infinite geometric series then sums to `a/(1 - r)`. For example 1 + 1/2 + 1/4 + … = `1/(1 - 1/2) = 2`.</t>
-        </is>
-      </c>
+          <t>Multiples of 7 between 50 and 200: first 56, last 196, so `(196 - 56)/7 + 1 = 21`. Cross-check on the multiplier index: `7x8` to `7x28` is `28 - 8 + 1 = 21` ✓.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -1907,29 +2125,32 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Alternating series: group them in pairs</t>
+          <t>Sum of the multiples of `r` between `a` and `b`?</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>A series like `1 - 2 + 3 - 4 + ...` has no constant difference or ratio, but pairing consecutive terms turns it into one that does. Each pair collapses to the same value, so the sum becomes a simple multiplication.</t>
+          <t>Average times count: `((first + last)/2) x ((last - first)/r + 1)`.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>`1 - 2 + 3 - 4 + ... - 100`. Pair them as `(1-2) + (3-4) + ... + (99-100)`: each pair is -1 and there are 50 pairs, so the sum is **-50**. If the series stopped at 101 instead, you would have those 50 pairs plus a leftover `+101`, giving 51.</t>
+          <t>The multiples form an evenly spaced list, so the same average-times-count machinery applies.
+It works because the multiples of `r` in a range are themselves evenly spaced, with gap `r` — so the average is the midpoint of the first and last, exactly as with consecutive integers.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Check whether the last term is left unpaired. An odd number of terms always leaves one over, and forgetting it is the whole point of the question.</t>
-        </is>
-      </c>
+          <t>Multiples of 7 between 50 and 200: average `= (56 + 196)/2 = 126`, count `= 21`, sum `= 2,646`.
+Multiples of 4 between 1 and 100: first 4, last 100, count `(100-4)/4 + 1 = 25`, average 52, sum `= 1,300`.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -1937,25 +2158,30 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>When there is no formula, find the pattern</t>
+          <t>How do you tell what kind of sequence you are looking at?</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>For an unfamiliar series `a1 + a2 + ... + an`, compute the sum for `n = 1`, `n = 2`, `n = 3` and look at the results rather than the terms. The partial sums very often follow an obvious rule even when the terms do not, and that rule is the answer.</t>
+          <t>Look at what stays constant. **Arithmetic**: constant difference. **Geometric**: constant ratio. **Quadratic**: constant second difference. **Cubic**: constant third difference.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>`1/(1x2) + 1/(2x3) + 1/(3x4) + ...` Partial sums: 1/2, then 2/3, then 3/4. The pattern is `n/(n+1)`, so the sum of the first 99 terms is 99/100 — no algebra required.</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr"/>
+          <t>Write the difference rows out. If row one is constant it is arithmetic; if row two is constant it is quadratic; if the *ratio* row is constant it is geometric.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1, 4, 9, 16, 25 → differences 3, 5, 7, 9 (not constant) → their differences 2, 2, 2 (constant). Quadratic, and indeed the terms are `n^2`.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -1963,270 +2189,293 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Counting, Sequences &amp; Series</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Bounding a series to compare it</t>
+          <t>nth term of an arithmetic or geometric sequence?</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Some comparison questions give a series with no clean pattern at all. You do not need its exact value, only whether it is bigger or smaller than the other quantity. Replace every term with the smallest term to get a lower bound, then with the largest term to get an upper bound. If the other quantity sits outside that interval, you have your answer.</t>
+          <t>Arithmetic: `a_n = a_1 + (n - 1)d`. Geometric: `a_n = a_1 x r^(n-1)`.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Quantity A: `1/51 + 1/52 + ... + 1/100` (50 terms). Quantity B: 1. Every term is at most 1/51, so A is at most `50/51 &lt; 1`. Every term is at least 1/100, so A is at least `50/100 = 1/2`. A lies between 0.5 and 0.98, so B is greater.</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
+          <t>Both use `n - 1`, not `n`, because the first term has taken zero steps. That off-by-one is the whole difficulty of these formulas.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Arithmetic 5, 8, 11, …: `a_20 = 5 + 19(3) = 62`. Geometric 5, 10, 20, …: `a_8 = 5 x 2^7 = 640`. Backwards: if an arithmetic sequence has `a_1 = 4` and `a_9 = 36`, then `8d = 32`, so `d = 4`.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Repeating versus non-repeating decimals</t>
+          <t>Sum formulas for `1 + 2 + ... + n` and `1^2 + 2^2 + ... + n^2`?</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Every fraction of two integers turns into a decimal that either stops or eventually repeats forever in a fixed block — that is what makes it rational. A decimal that goes on forever *without* any repeating block cannot be written as a fraction at all; those are the irrational numbers, like `sqrt(2)` and `pi`.
-Repeating blocks are usually written with a bar over the repeating part; in plain text, write `0.333...` or say "0.3 repeating", and `0.373737...` for a two-digit block.</t>
+          <t>`n(n+1)/2` and `n(n+1)(2n+1)/6`.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>`1/3 = 0.333...` repeats, so it is rational. `1/8 = 0.125` terminates, also rational. `sqrt(2) = 1.41421356...` never settles into a block, so it is irrational and cannot be written as a ratio of integers.</t>
+          <t>The first is average-times-count in disguise: the average is `(1+n)/2` and there are `n` terms.
+The pairing proof is worth knowing: write `1 + 2 + ... + n` forwards and backwards above each other, and every column sums to `n + 1`. There are `n` columns and you have counted everything twice, hence `n(n+1)/2`.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>"Non-terminating" does not mean irrational. `1/3` never terminates but is perfectly rational, because it repeats.</t>
-        </is>
-      </c>
+          <t>`1 + 2 + ... + 100 = 100 x 101/2 = 5,050`. `1^2 + ... + 10^2 = 10 x 11 x 21/6 = 385`. For a sum starting at 11, subtract: `1,275 - 55 = 1,220`.
+The first 50 **even** numbers: `2 + 4 + ... + 100 = 2(1 + 2 + ... + 50) = 2 x 1,275 = 2,550`. Factoring the 2 out first is nearly always the quickest route.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Does a fraction terminate?</t>
+          <t>Sum of the first `n` terms of a geometric series?</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Reduce the fraction to lowest terms, then prime factorize the denominator. If the only primes left are 2s and 5s, the decimal terminates; if anything else survives, it repeats. The reason is that our decimal system is base 10 = `2 x 5`, so only denominators built from 2s and 5s can be rewritten as a power of 10.</t>
+          <t>`sum = a(r^n - 1)/(r - 1)`, with `a` the first term and `r` the ratio. If `|r| &lt; 1`, an infinite series sums to `a/(1 - r)`.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>`7/40`: `40 = 2^3 x 5`, only 2s and 5s, so it terminates (`0.175`). `7/30`: `30 = 2 x 3 x 5` contains a 3, so it repeats (`0.2333...`). `6/30` looks like it repeats, but reduce it first: `6/30 = 1/5 = 0.2`, which terminates.</t>
+          <t>Average-times-count fails here because the terms are not evenly spaced — the later terms dominate.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Always reduce first. The un-reduced denominator can contain primes that cancel away.</t>
-        </is>
-      </c>
+          <t>First 20 terms of 3, 6, 12, 24, …: `3(2^20 - 1)/1 = 3 x 1,048,575 = 3,145,725`. Infinite case: `1 + 1/2 + 1/4 + ... = 1/(1 - 1/2) = 2`.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Turning a repeating decimal into a fraction</t>
+          <t>Sum of `1 - 2 + 3 - 4 + ...`?</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Set `x` equal to the decimal, multiply both sides by `10^n` where `n` is the length of the repeating block, then subtract the original equation. The infinite tails are identical so they cancel, leaving a plain equation you can solve.
-The shortcut it produces: a block of `n` repeating digits sits over `n` nines. `0.444... = 4/9`, `0.373737... = 37/99`, `0.123123... = 123/999`.</t>
+          <t>Group it in **pairs**. Each pair collapses to the same value, turning the series into a multiplication.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Convert `0.373737...` to a fraction. Let `x = 0.3737...`; the block is 2 digits, so multiply by 100: `100x = 37.3737...`. Subtract the first from the second: `99x = 37`, so `x = 37/99`.</t>
+          <t>The series has no constant difference or ratio, but pairing consecutive terms creates one that does.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>If the decimal has a non-repeating head, such as `0.1666...`, multiply first to push the head past the point: `10x = 1.666...` and `100x = 16.66...`, so `90x = 15` and `x = 1/6`.</t>
+          <t>`1 - 2 + 3 - 4 + ... - 100`: pairs `(1-2), (3-4), ...` each give -1, and there are 50 pairs, so **-50**. Stopping at 101 instead leaves those 50 pairs plus `+101`, giving 51.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Check whether the final term is left unpaired — an odd number of terms always leaves one over, and that is the point of the question.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Smallest multiplier that makes a fraction an integer</t>
+          <t>A series with no formula and no obvious pattern — what next?</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Reduce `a/b` to lowest terms; the answer is then simply `b`, the denominator. Once the fraction is reduced, the numerator has nothing left in common with the denominator, so nothing smaller than `b` can clear it.</t>
+          <t>Compute the **partial sums** for `n = 1, 2, 3` and look at those instead of the terms. The sums often follow an obvious rule even when the terms do not.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Smallest positive integer that turns `14/21` into an integer? Reduce first: `14/21 = 2/3`, so the answer is **3**, not 21. And `3 x (2/3) = 2`, an integer.</t>
+          <t>This is how telescoping series give themselves away.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Skipping the reduction step gives a number that works but is not the smallest — which is exactly the wrong answer choice they will offer you.</t>
-        </is>
-      </c>
+          <t>`1/(1x2) + 1/(2x3) + 1/(3x4) + ...` has partial sums 1/2, 2/3, 3/4 — clearly `n/(n+1)`. So the first 99 terms sum to 99/100, with no algebra.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Proportions and cross-multiplication</t>
+          <t>Comparing a messy series against another quantity?</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>A proportion is one fraction set equal to another, usually with a single unknown. Cross-multiply — numerator of one times denominator of the other — and solve. The skill is in setting it up so that the same kind of quantity sits in the same position on both sides.
-Keep units aligned: if the left side is km over minutes, the right side must also be km over minutes.</t>
+          <t>**Bound it.** Replace every term with the smallest term for a lower bound, then with the largest for an upper bound. If the other quantity falls outside that interval, you are done.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>A man runs 4 km in 30 minutes. How far in 45 minutes at the same rate? Set up `4/30 = a/45`. Cross-multiply: `30a = 4 x 45 = 180`, so `a = 6 km`.</t>
+          <t>You never needed the exact value, only which side of the other quantity it lies on.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Check the answer makes sense in direction. More time should mean more distance; if your answer went down, you set the proportion up upside down.</t>
-        </is>
-      </c>
+          <t>A: `1/51 + 1/52 + ... + 1/100` (50 terms). B: 1. Every term is at most 1/51, so A ≤ `50/51 &lt; 1`; every term is at least 1/100, so A ≥ 1/2. A is between 0.5 and 0.98, so **B is greater**.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Simple interest</t>
+          <t>Arithmetic mean — definition and the trick that matters?</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Simple interest is paid on the original principal only, never on interest already earned. The interest itself is `prt`, so the final amount is
-`A = p(1 + rt)`
-where `p` is the principal, `r` the annual rate as a decimal and `t` the time in years. Because the interest per year never changes, the balance grows in a straight line.</t>
+          <t>`mean = sum / count`, so `sum = mean x count`. Most mean questions are really about the **sum**.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>$300 at 4% simple interest for 5 years: interest `= 300 x 0.04 x 5 = $60`, so `A = $360`. Each year adds exactly $12.</t>
+          <t>When a question changes a list — adds a value, removes one, or reports a new average — convert every average into its total first, adjust the totals, then convert back.
+For an evenly spaced list the mean also equals the median, which is a big shortcut.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Convert the rate to a decimal (`4% → 0.04`) and the time to years (`18 months → 1.5`) before substituting.</t>
+          <t>Five numbers average 12, so their sum is 60. Add a sixth number, 18: the new sum is 78 and the new mean is `78/6 = 13`. What value would pull the average of the five up to 15? The sum would need to be 90, so the new number must be 30.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>The average of two averages is only valid when the groups are the same size — otherwise you need a weighted average.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Compound interest</t>
+          <t>Median, mode and range — definitions?</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Compound interest pays interest on interest, so each year's growth is applied to the new balance:
-`A = p(1 + r)^t`
-The gap between simple and compound is small at first and grows dramatically with time, which is why comparison questions love it.</t>
+          <t>**Median**: middle value of the sorted list (average the two middle ones if the count is even). **Mode**: the most frequent value. **Range**: `largest - smallest`.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>$300 at 4% compounded annually for 5 years: `A = 300(1.04)^5 ≈ 300 x 1.21665 = $365.00`, against $360 for simple interest — $5 more, from interest earning interest.</t>
+          <t>Sorting first is non-negotiable for the median, and it is the step people skip. The median ignores outliers while the mean does not, which is exactly what comparison questions probe.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>`(1.04)^5` is not `1 + 5(0.04)`. Powers do not distribute over sums, and assuming they do is the error the question is testing.</t>
-        </is>
-      </c>
+          <t>For 3, 9, 4, 4, 12: sorted it is 3, 4, 4, 9, 12 → median **4**, mode **4**, range **9**, mean **6.4**. Replace 12 with 120 and the median stays 4 while the mean jumps to 28 — the classic outlier contrast.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Sequences, Series &amp; Averages</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Compounding more than once a year</t>
+          <t>Median of an evenly spaced list, without counting to the middle?</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>If the interest compounds `n` times a year, each period gets `r/n` of the annual rate and there are `nt` periods in total:
-`A = p(1 + r/n)^(nt)`
-More frequent compounding always gives a slightly larger amount, because the interest starts earning sooner.</t>
+          <t>`median = (first + last)/2`, and it equals the mean. Works for consecutive integers, consecutive multiples, any arithmetic sequence.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>$1,000 at 12% for 2 years. Annually: `1000(1.12)^2 = $1,254.40`. Quarterly: `n = 4`, so `1000(1 + 0.03)^8 = 1000(1.03)^8 ≈ $1,266.77`. Monthly would give about $1,269.73.</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
+          <t>Evenly spaced lists are symmetric about their centre, so the midpoint of the ends is the middle value.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Median of the multiples of 7 between 50 and 200: `(56 + 196)/2 = 126`. Median of 1 to 100: `(1 + 100)/2 = 50.5`.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Only for even spacing. An arbitrary list must be sorted first.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -2234,29 +2483,32 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Compound decrease</t>
+          <t>Repeating versus non-repeating decimals — which are rational?</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Depreciation and decay use the same formula with a minus sign:
-`A = p(1 - r)^t`
-Each period removes a percentage of whatever is left, so the amount falls quickly at first and then flattens out — it never reaches zero.</t>
+          <t>Both terminating and **repeating** decimals are rational. Only a decimal that runs forever with **no** repeating block is irrational.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>A $20,000 car depreciating 15% a year for 3 years: `A = 20,000(0.85)^3 = 20,000 x 0.614 ≈ $12,282`. Note this is *not* a 45% total drop; three 15% cuts remove about 38.6% in total.</t>
+          <t>Every ratio of two integers either stops or falls into a repeating block. So `1/3 = 0.333...` is rational despite never terminating, while `sqrt(2) = 1.41421356...` never settles and cannot be written as a fraction.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>A 20% rise followed by a 20% fall does not return you to the start: `1.2 x 0.8 = 0.96`, a 4% net loss.</t>
+          <t>`1/3 = 0.333...` (rational, repeating). `1/8 = 0.125` (rational, terminating). `pi` and `sqrt(2)` (irrational).</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>"Non-terminating" does not mean irrational — that confusion is the whole question.</t>
         </is>
       </c>
     </row>
@@ -2266,28 +2518,32 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Rate times time</t>
+          <t>Will `a/b` terminate as a decimal?</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>One relationship covers speed, work and production: `amount = rate x time`. For motion it reads `distance = speed x time`; for a job it reads `work = rate x time`. Rearranging gives `rate = amount/time` and `time = amount/rate`.
-For combined-work problems, add the rates, not the times: two taps that each fill a tank in 6 and 3 hours fill at `1/6 + 1/3 = 1/2` of a tank per hour, so together they take 2 hours.</t>
+          <t>Reduce it first, then factorize the denominator. It terminates **only if the denominator's primes are 2s and 5s**.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>A printer does 20 pages a minute; a second does 30. Together their rate is 50 pages a minute, so a 400-page job takes `400/50 = 8 minutes`.</t>
+          <t>Base 10 is `2 x 5`, so only denominators built from 2s and 5s can be rewritten as a power of 10.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Average speed for a round trip is total distance over total time, not the average of the two speeds. Driving out at 30 and back at 60 averages 40, not 45.</t>
+          <t>`7/40`: `40 = 2^3 x 5` → terminates (0.175). `7/30`: `30 = 2 x 3 x 5` → repeats (0.2333…). `6/30` looks like it repeats, but reduces to `1/5 = 0.2`.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Always reduce first — the unreduced denominator can hide primes that cancel away.</t>
         </is>
       </c>
     </row>
@@ -2297,2852 +2553,4193 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Fractions, Percents &amp; Rates</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Relative speed</t>
+          <t>Turning a repeating decimal into a fraction?</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>When two things move at once, combine their speeds into a single rate before using `distance = rate x time`. Moving toward each other or apart, **add** the speeds, because both are closing or opening the gap. Moving in the same direction, **subtract**, because only the difference changes the gap.</t>
+          <t>`n` repeating digits sit over `n` nines: `0.444... = 4/9`, `0.373737... = 37/99`, `0.123123... = 123/999`.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Two cars start 300 km apart and drive toward each other at 60 and 40 km/h. Closing speed is 100 km/h, so they meet after `300/100 = 3 hours`. If instead the 60 km/h car chases the 40 km/h car from 30 km behind, the gap closes at `60 - 40 = 20 km/h`, taking `30/20 = 1.5 hours`.</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
+          <t>The mechanism: set `x` equal to the decimal, multiply by `10^n` where `n` is the block length, and subtract. The infinite tails cancel exactly.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>`x = 0.3737...`; the block is 2 digits so `100x = 37.3737...`. Subtracting gives `99x = 37`, so `x = 37/99`.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>A non-repeating head needs an extra step: for `0.1666...`, use `10x = 1.666...` and `100x = 16.66...`, so `90x = 15` and `x = 1/6`.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Exponents &amp; Roots</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Power of a power: multiply the exponents</t>
+          <t>Smallest positive integer that turns `a/b` into an integer?</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>`(a^b)^c = a^(bc)`. Raising a power to another power means repeating the multiplication `c` times, and each repetition contributes `b` copies of `a`, so you end up with `bc` of them.</t>
+          <t>`b` — but only once `a/b` is in **lowest terms**.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>`(2^3)^4 = 2^12 = 4,096`. Check the long way: `2^3 = 8`, and `8^4 = 4,096`. This is also how you compare ugly powers — `9^10` is `(3^2)^10 = 3^20`, which sits neatly beside `3^19` or `27^7 = 3^21`.</t>
+          <t>After reducing, the numerator shares nothing with the denominator, so nothing smaller than `b` can clear it.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>`(a^b)^c` is not `a^(b^c)`. `(2^3)^2 = 64` while `2^(3^2) = 2^9 = 512`. Brackets decide which one you have.</t>
+          <t>`14/21` reduces to `2/3`, so the answer is **3**, not 21. And `3 x (2/3) = 2` ✓.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Skipping the reduction gives a number that works but is not the smallest — exactly the wrong answer they will offer.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Exponents &amp; Roots</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Same exponent, different bases</t>
+          <t>Setting up a proportion?</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>`(a^b)(c^b) = (ac)^b`. When two powers share an exponent you may multiply the bases and keep the exponent once. It also runs backwards, which is usually the more useful direction: a messy base can be split into friendlier pieces.</t>
+          <t>Put the same kind of quantity in the same position on both sides, then cross-multiply.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>`4^5 x 25^5 = (4 x 25)^5 = 100^5 = 10^10`. Backwards: `6^8 = (2 x 3)^8 = 2^8 x 3^8`, which is what lets you compare it with `2^10 x 3^8`.</t>
+          <t>Keep units aligned: if the left is km over minutes, the right must be km over minutes too. Then sanity-check the direction — more time should mean more distance.
+Check whether the relationship is **direct** (more of one means more of the other, so `a/b = c/d`) or **inverse** (more of one means less of the other, so `a x b = c x d`). Workers and time are inverse: twice the workers, half the time.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Note the brackets: `(ac)^b`, not `ac^b`. Without them the exponent would only apply to `c`.</t>
-        </is>
-      </c>
+          <t>4 km in 30 minutes; how far in 45? `4/30 = a/45` → `30a = 180` → `a = 6 km`.
+Inverse case: 6 workers finish a job in 10 days; how long for 15 workers? `6 x 10 = 15 x d`, so `d = 4 days` — not `15/6 x 10`.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Exponents &amp; Roots</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Same base, multiplying: add the exponents</t>
+          <t>Ratios: what does `a : b` actually let you write down?</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>`(a^b)(a^c) = a^(b+c)`. Multiplying means putting all the copies of `a` together, so the counts add.</t>
+          <t>Introduce the multiplier `x`: the parts are `ax` and `bx`, and the whole is `(a + b)x`. Part-to-part is `a : b`; part-to-whole is `a : (a+b)`.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>`2^3 x 2^5 = 2^8 = 256`. This is the move that rescues expressions like `2^10 + 2^10`: that is not `2^20` but `2 x 2^10 = 2^11`. Adding powers is completely different from multiplying them.</t>
+          <t>The multiplier is what turns a ratio into an equation. Confusing part-to-part with part-to-whole is the most common ratio error: 2:3 means 2/5 and 3/5 of the total, not 2/3 and 3/3.
+To combine two ratios sharing a term, scale them until that term matches — `A:B = 2:3` and `B:C = 4:5` become `A:B:C = 8:12:15`.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>There is no rule for `a^b + a^c`. When you see a sum of powers, factor out the smaller one instead: `2^10 + 2^12 = 2^10(1 + 4) = 5 x 2^10`.</t>
-        </is>
-      </c>
+          <t>Boys to girls is 3:5 in a class of 40. Total parts `= 8`, so `8x = 40` and `x = 5`: 15 boys and 25 girls. Boys are `3/8` of the class, not `3/5`.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Exponents &amp; Roots</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Same base, dividing: subtract the exponents</t>
+          <t>Percents: converting, and finding "x percent of y"?</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>`(a^b)/(a^c) = a^(b-c)`. Division cancels copies of `a`, so the counts subtract. This is also where the two definitions that look strange come from: `a^0 = 1` (because `a^b/a^b = 1`) and `a^(-n) = 1/a^n` (because subtracting more than you have flips it into the denominator).</t>
+          <t>Percent means "per hundred": `x% = x/100`. "Of" means multiply, so `x% of y = (x/100) x y`. Useful ones: `1/8 = 12.5%`, `1/6 ≈ 16.7%`, `1/3 ≈ 33.3%`, `3/8 = 37.5%`, `5/8 = 62.5%`.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>`2^8/2^3 = 2^5 = 32`. And `3^4/3^7 = 3^(-3) = 1/27`. A negative exponent is not a negative number — `2^(-3)` is 1/8, comfortably positive.</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
+          <t>Percent questions become easy once you translate word by word: "is" is `=`, "of" is `x`, "what" is the variable.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>"18 is what percent of 45?" → `18 = (p/100) x 45` → `p = 40`. And 15% of 60 is `0.15 x 60 = 9`. Reversing: "12 is 30% of what?" → `12 = 0.3y` → `y = 40`.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>`x% of y` always equals `y% of x`, which can turn an awkward computation into an easy one: 8% of 50 is the same as 50% of 8, i.e. 4.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Exponents &amp; Roots</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Roots as fractional exponents</t>
+          <t>Percent change — and what happens with two changes in a row?</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>A root is a power with a fractional exponent: `sqrt(a) = a^(1/2)`, `cuberoot(a) = a^(1/3)`, and in general `n-th root of a^m = a^(m/n)`. Rewriting roots this way lets you use every exponent rule you already know, and shortcuts that were invisible in radical form become obvious.</t>
+          <t>`percent change = (new - old)/old x 100`, always over the **original**. Successive changes **multiply**: a 20% rise then a 20% fall is `1.2 x 0.8 = 0.96`, a 4% net loss.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>`sqrt(12)/sqrt(3)` looks awkward, but as `12^(1/2)/3^(1/2) = (12/3)^(1/2) = 4^(1/2) = 2` it is immediate. Similarly `sqrt(sqrt(16)) = (16^(1/2))^(1/2) = 16^(1/4) = 2`.</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
+          <t>Increases and decreases are not symmetric, because the second change is applied to a different base. A rise of 25% needs a fall of only 20% to undo it.
+Multipliers are the fast way through: +30% is `x1.3`, -15% is `x0.85`.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Price rises from 80 to 100: `(100-80)/80 = 25%` increase. Falling back from 100 to 80 is `(80-100)/100 = -20%`. Two successive 10% rises give `1.1 x 1.1 = 1.21`, a 21% increase, not 20%.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>"Increased by 300%" means the result is 4 times the original, not 3 times.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Exponents &amp; Roots</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Is the nth root rational?</t>
+          <t>Simple interest formula?</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Prime factorize the number under the root. The root is rational exactly when every exponent in that factorization is divisible by the root's index — because taking an `n`-th root divides each exponent by `n`, and you need whole numbers out the other side.
-For square roots that means every exponent must be even; for cube roots, every exponent a multiple of 3.</t>
+          <t>`A = p(1 + rt)` — interest is `prt`, added once to the principal. `r` is the annual rate as a decimal, `t` the time in years.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Is the 4th root of 24 rational? `24 = 2^3 x 3`. The exponents 3 and 1 are not multiples of 4, so no. Is `sqrt(144)` rational? `144 = 2^4 x 3^2`, both exponents even, so yes — it is `2^2 x 3 = 12`.</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
+          <t>Interest is paid on the original principal only, never on interest already earned, so the balance grows in a straight line.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>$300 at 4% for 5 years: interest `= 300 x 0.04 x 5 = $60`, so `A = $360` — exactly $12 a year.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Convert the rate to a decimal and the time to years (18 months → 1.5) before substituting.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Exponents &amp; Roots</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Simplifying radicals</t>
+          <t>Compound interest formula?</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Prime factorize what is under the root and pull out any prime whose exponent reaches the index of the root. Each group of `n` identical factors under an `n`-th root escapes as a single factor outside.
-If an exponent overshoots, split it: `sqrt(2^9) = sqrt(2^8) x sqrt(2) = 2^4 x sqrt(2)`.</t>
+          <t>`A = p(1 + r)^t`.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>`sqrt(24) = sqrt(2^3 x 3) = sqrt(2^2) x sqrt(2 x 3) = 2sqrt(6)`. And `cuberoot(24) = cuberoot(2^3 x 3) = 2 x cuberoot(3)`, because the three 2s form one complete group for a cube root.</t>
+          <t>Each period's interest is applied to the new balance, so growth is exponential rather than linear. The gap over simple interest is small at first and grows fast — which is why comparison questions love it.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>`sqrt(a + b)` is not `sqrt(a) + sqrt(b)`. Roots distribute over multiplication and division only — `sqrt(9 + 16) = 5`, not `3 + 4`.</t>
+          <t>$300 at 4% compounded annually for 5 years: `300(1.04)^5 ≈ $365.00`, against $360 simple — $5 of interest earning interest.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>`(1.04)^5` is not `1 + 5(0.04)`. Powers do not distribute over sums.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Exponents &amp; Roots</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Radicals in the denominator</t>
+          <t>Compound interest when it compounds more than once a year?</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>A fraction with a root on the bottom is considered unsimplified and is harder to compare or estimate. Multiply top and bottom by that root to move it upstairs — you are multiplying by 1, so the value does not change.
-When the denominator is a sum like `1 + sqrt(2)`, multiply by its conjugate `1 - sqrt(2)` instead, and the difference-of-squares identity clears the root.</t>
+          <t>`A = p(1 + r/n)^(nt)` — divide the rate by `n`, multiply the periods by `n`.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>`3/sqrt(2) = (3 x sqrt(2))/(sqrt(2) x sqrt(2)) = 3sqrt(2)/2 ≈ 2.12`, which you can now estimate at a glance. With a conjugate: `1/(1 + sqrt(2)) = (1 - sqrt(2))/((1)^2 - (sqrt(2))^2) = (1 - sqrt(2))/(-1) = sqrt(2) - 1`.</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
+          <t>More frequent compounding always yields slightly more, because interest starts earning sooner.
+Comparison questions usually only need the direction: for the same nominal rate, more frequent compounding always wins, and the gap widens with time. There is a ceiling, though — compounding infinitely often multiplies by `e^(rt)`, only slightly above monthly.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>$1,000 at 12% for 2 years. Annually: `1000(1.12)^2 = $1,254.40`. Quarterly: `1000(1.03)^8 ≈ $1,266.77`. Monthly: about $1,269.73.
+A rate quoted as "12% compounded quarterly" is really 3% four times, which is an effective annual rate of `1.03^4 - 1 ≈ 12.55%`.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Exponents &amp; Roots</t>
+          <t>Fractions, Ratios &amp; Percents</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Even exponents under even roots need absolute values</t>
+          <t>Formula for something that shrinks by a percentage each period?</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>`sqrt(x^2)` is **not** `x` — it is `|x|`. The square root symbol always returns the non-negative root, so if `x` were negative the plain answer would have the wrong sign. The same applies to any even power under any even root.
-Odd roots have no such problem: `cuberoot(x^3) = x` even when `x` is negative, because cube roots can return negatives.</t>
+          <t>`A = p(1 - r)^t`.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>If `x = -5`, then `sqrt(x^2) = sqrt(25) = 5 = |x|`, not -5. So an equation like `sqrt(x^2) = 3` has two solutions, `x = 3` and `x = -3`, while `x^3 = 27` has only one.</t>
+          <t>Each period removes a percentage of whatever remains, so the amount falls quickly at first and then flattens — it never quite reaches zero.
+Halving is the case to recognise: `r = 0.5` gives `p(0.5)^t`, so the quantity halves every period — and after `t` periods, `t` halvings.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>In a quantitative comparison, "`x^2 = 16`" means `x` could be 4 or -4. Any question that squares away a variable's sign is usually heading for answer D.</t>
-        </is>
-      </c>
+          <t>A $20,000 car depreciating 15% a year for 3 years: `20,000(0.85)^3 ≈ $12,282`. Note that is a 38.6% total drop, not 45%.
+A population falling 10% a year takes about 7 years to halve: `0.9^7 ≈ 0.478`. And a 50% fall followed by a 50% rise leaves you at `0.5 x 1.5 = 0.75` — down 25%, not back where you started.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Polynomials &amp; Quadratics</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Degree of a polynomial</t>
+          <t>The one formula behind speed, work and production?</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Within each term, add up the exponents of every variable; the biggest of those totals is the degree of the whole polynomial. A single term with several variables counts them all together, which is what people miss.</t>
+          <t>`amount = rate x time`. Distance = speed x time; work = rate x time. For combined work, **add the rates, never the times**.</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>In `(2x^2)(4y^3) = 8x^2y^3` the degree is `2 + 3 = 5`. In `x^3 + 5x^2y^2 - 7`, the term degrees are 3, 4 and 0, so the polynomial has degree 4.</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
+          <t>Rearranging gives `rate = amount/time` and `time = amount/rate`. Two taps filling a tank in 6 and 3 hours work at `1/6 + 1/3 = 1/2` of a tank per hour, so together they take 2 hours.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>One printer does 20 pages a minute, another 30. Combined rate 50 per minute, so a 400-page job takes `400/50 = 8 minutes`.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Average speed is total distance over total time, not the average of the speeds. Out at 30 and back at 60 averages **40**, not 45.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Polynomials &amp; Quadratics</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>What counts as a polynomial</t>
+          <t>Two objects moving at once — what do you do with their speeds?</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>A polynomial is a sum of terms made only of numbers and variables raised to whole-number powers. That rules out negative exponents (`x^-1`, i.e. variables in a denominator), fractional exponents (roots of variables) and absolute values.
-The point of the definition is that polynomials are smooth and predictable, which is what lets the factoring rules below always work.</t>
+          <t>Combine them into one rate. Toward each other or apart: **add**. Same direction: **subtract**.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>`3x^2 - 5x + 7` is a polynomial. `3/x + 2` is not (that is `3x^-1`). `sqrt(x) + 1` is not (that is `x^(1/2)`). `|x| + 4` is not. But `3/4 x^2` is fine — fractional *coefficients* are allowed, only fractional *exponents* are not.</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
+          <t>Only the rate at which the gap changes matters. Two cars approaching each other close the gap at the sum of their speeds; a chase closes it at the difference.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>300 km apart, driving toward each other at 60 and 40 km/h: closing speed 100, so they meet after 3 hours. If instead the 60 chases the 40 from 30 km back, the gap closes at 20 km/h, taking 1.5 hours.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Polynomials &amp; Quadratics</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Linear equations</t>
+          <t>`(a^b)^c` = ?</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>A linear equation is a polynomial equation of degree 1: every variable appears to the first power only. Graphed on the plane it is a straight line, which is where the name comes from, and it has exactly one solution unless the variable cancels out entirely.</t>
+          <t>`a^(bc)` — multiply the exponents.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>`3x + 7 = 22` is linear, giving `x = 5`. `y = 2x - 3` is linear in two variables and draws a straight line. `x^2 + 3x = 4` is not linear — it is quadratic, degree 2.</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr"/>
+          <t>Raising a power to a power repeats the multiplication `c` times, each contributing `b` copies of `a`.
+This is the main tool for comparing powers with different bases: rewrite both as powers of the same base and then simply compare exponents.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>`(2^3)^4 = 2^12 = 4,096`, and the long way `8^4` agrees. This is also how you compare ugly powers: `9^10 = (3^2)^10 = 3^20`, which sits neatly beside `27^7 = 3^21`.
+Which is bigger, `4^30` or `8^20`? `4^30 = 2^60` and `8^20 = 2^60` — they are equal.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>`(a^b)^c` is not `a^(b^c)`. `(2^3)^2 = 64` but `2^(3^2) = 512`.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Polynomials &amp; Quadratics</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>The three quadratic identities</t>
+          <t>`(a^b)(c^b)` = ?</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>These three are worth recognising instantly in both directions:
-`a^2 + 2ab + b^2 = (a + b)^2`
-`a^2 - 2ab + b^2 = (a - b)^2`
-`a^2 - b^2 = (a + b)(a - b)`
-The third — the difference of squares — is the one that turns awkward arithmetic into mental arithmetic.</t>
+          <t>`(ac)^b` — same exponent, so multiply the bases and keep the exponent once.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>`97 x 103 = (100 - 3)(100 + 3) = 100^2 - 3^2 = 10,000 - 9 = 9,991`. And if a question says `x + y = 10` and `x - y = 4`, then `x^2 - y^2 = 10 x 4 = 40` without ever finding `x` or `y`.</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr"/>
+          <t>Running it backwards is usually more useful: a messy base splits into friendlier pieces.
+It is also how you handle a power of a fraction: `(a/b)^n = a^n/b^n`, so `(2/3)^4 = 16/81`.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>`4^5 x 25^5 = 100^5 = 10^10`. Backwards: `6^8 = (2 x 3)^8 = 2^8 x 3^8`, which is what lets you compare it with `2^10 x 3^8`.
+`2^10 x 5^10 = 10^10`, so a question about `2^10 x 5^10 x 3` is really asking about `3 x 10^10` — a 1 followed by ten zeros, tripled.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Mind the brackets: `(ac)^b`, not `ac^b`.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Polynomials &amp; Quadratics</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Spotting an identity to simplify</t>
+          <t>`(a^b)(a^c)` = ?</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Before grinding through algebra, scan the expression for the shapes above. A trinomial whose first and last terms are perfect squares and whose middle term is twice the product of their roots is a perfect square trinomial, and collapses into one bracket. A difference of two squares always splits into conjugates.</t>
+          <t>`a^(b+c)` — same base, so **add** the exponents.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>`x^2 + 10x + 25 = (x + 5)^2`, because 25 is `5^2` and `10x` is `2 x 5 x x`. `4x^2 - 9 = (2x + 3)(2x - 3)`. And a fraction like `(x^2 - 9)/(x + 3)` simplifies to `x - 3` once you factor the top.</t>
+          <t>Multiplying gathers all the copies of `a` together, so the counts add.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Check the middle term before declaring a perfect square. `x^2 + 7x + 25` is not `(x+5)^2`, because that would need `10x`.</t>
+          <t>`2^3 x 2^5 = 2^8 = 256`. Contrast with a sum: `2^10 + 2^10 = 2 x 2^10 = 2^11`, not `2^20`.
+Useful in reverse for comparisons: `3^11` versus `9^5 = 3^10` — same base, so `3^11` is three times larger.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>There is no rule for `a^b + a^c`. Factor out the smaller: `2^10 + 2^12 = 2^10(1 + 4) = 5 x 2^10`.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Polynomials &amp; Quadratics</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Find the domain before you simplify</t>
+          <t>`(a^b)/(a^c)` = ?</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>When you cancel a factor from the top and bottom of a fraction, you are quietly dividing by that factor — which is only legal if it is not zero. The restriction it imposes stays with the expression even after the factor has vanished from sight, so work out the domain from the **original** expression.</t>
+          <t>`a^(b-c)` — same base, so **subtract**. This is also where `a^0 = 1` and `a^(-n) = 1/a^n` come from.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>`(x^2 - 25)/((x+5)(x-5))`. Cancelling gives 1, but the domain still excludes both `x = 5` and `x = -5`, since either would have made the original denominator zero. Looking only at the simplified answer would lose both restrictions.</t>
+          <t>Division cancels copies of `a`. Subtracting more than you have flips the leftover into the denominator, which is exactly what a negative exponent means.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>This is exactly how a graph ends up with a hole in it. The simplified function is defined there; the original one is not.</t>
-        </is>
-      </c>
+          <t>`2^8/2^3 = 2^5 = 32`. `3^4/3^7 = 3^(-3) = 1/27`. Note `2^(-3) = 1/8` is positive — a negative exponent is not a negative number.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Polynomials &amp; Quadratics</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Absolute-value equations split into two</t>
+          <t>Rewriting a root as an exponent?</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Rearrange until the equation reads `|expression1| = expression2`, then solve it twice: once with `expression1 = expression2` and once with `expression1 = -expression2`. The absolute value hides the sign of what is inside, so both possibilities have to be chased.</t>
+          <t>`nth root of a^m = a^(m/n)`. So `sqrt(a) = a^(1/2)` and `cuberoot(a) = a^(1/3)`.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>`|4x + 9| = 21`. First: `4x + 9 = 21`, so `x = 3`. Second: `4x + 9 = -21`, so `x = -7.5`. Both check out in the original equation.</t>
+          <t>Once roots are exponents, every exponent rule applies to them, and shortcuts that were invisible in radical form appear.
+A negative fractional exponent combines both ideas: `a^(-1/2) = 1/sqrt(a)`. And `(a^(1/2))^2 = a`, which is why squaring undoes a square root.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Isolate the absolute value before splitting — `2|x| + 3 = 11` must become `|x| = 4` first. And if the right-hand side is negative, there are no solutions at all, since an absolute value can never be negative.</t>
-        </is>
-      </c>
+          <t>`sqrt(12)/sqrt(3)` is awkward, but `12^(1/2)/3^(1/2) = (12/3)^(1/2) = 2` is immediate. Likewise `sqrt(sqrt(16)) = 16^(1/4) = 2`.
+`8^(2/3)` means "cube root, then square": `cuberoot(8) = 2`, and `2^2 = 4`. Doing the root first keeps the numbers small.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Polynomials &amp; Quadratics</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>How many solutions does a quadratic have?</t>
+          <t>Is the `n`th root of a number rational?</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>For `ax^2 + bx + c = 0`, compute the discriminant `b^2 - 4ac`. Positive means two distinct real solutions, zero means one (a repeated root), negative means none. You do not need the solutions themselves to answer "how many".</t>
+          <t>Yes exactly when **every exponent in its prime factorization is divisible by `n`**. Square roots need all even exponents; cube roots need multiples of 3.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>`x^2 - 4x - 6 = 0`: discriminant `= 16 + 24 = 40 &gt; 0`, so two solutions. `x^2 - 4x + 4 = 0`: discriminant `= 16 - 16 = 0`, so one solution (`x = 2`). `x^2 + x + 5 = 0`: discriminant `= 1 - 20 = -19 &lt; 0`, so no real solutions.</t>
+          <t>Taking an `n`th root divides each exponent by `n`, and you need whole numbers out the other side.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Rearrange to `= 0` before reading off `a`, `b` and `c`, and keep the signs: in `x^2 - 4x - 6`, `c` is -6, not 6.</t>
-        </is>
-      </c>
+          <t>4th root of 24? `24 = 2^3 x 3`, and 3 and 1 are not multiples of 4 → irrational. `sqrt(144)`? `144 = 2^4 x 3^2`, both even → rational, equal to `2^2 x 3 = 12`.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Polynomials &amp; Quadratics</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Completing the square</t>
+          <t>Simplifying a radical like `sqrt(24)`?</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>When a quadratic does not factor neatly, you can force a perfect square. Take the coefficient of `x`, halve it, square it, and add that to both sides. The left side then folds into a single squared bracket that you can undo with a square root.</t>
+          <t>Prime factorize underneath and pull out any prime whose exponent reaches the root's index. `sqrt(24) = sqrt(2^2 x 6) = 2sqrt(6)`.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>`x^2 - 4x - 6 = 0`. Half of -4 is -2, and `(-2)^2 = 4`, so add 4 to both sides: `x^2 - 4x + 4 - 6 = 4`, which is `(x-2)^2 - 6 = 4`, so `(x-2)^2 = 10` and `x = 2 ± sqrt(10)`.</t>
+          <t>Each complete group of `n` identical factors escapes an `n`th root as a single factor. If an exponent overshoots, split it: `sqrt(2^9) = sqrt(2^8) x sqrt(2) = 2^4 sqrt(2)`.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>If the `x^2` term has a coefficient, divide the whole equation through by it first — completing the square only works when the leading coefficient is 1.</t>
+          <t>`cuberoot(24) = cuberoot(2^3 x 3) = 2 cuberoot(3)`, because the three 2s form one complete group for a cube root.</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>`sqrt(a + b)` is not `sqrt(a) + sqrt(b)`: `sqrt(9 + 16) = 5`, not 7. Roots distribute over multiplication and division only.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Inequalities &amp; Functions</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Multiplying or dividing by a negative flips the sign</t>
+          <t>Getting a radical out of a denominator?</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Inequalities behave like equations for adding and subtracting, but multiplying or dividing both sides by a negative number reverses the direction of the sign. Picture the number line: negating reflects every number through zero, so whatever was on the left ends up on the right.</t>
+          <t>Multiply top and bottom by that radical. For a denominator like `1 + sqrt(2)`, multiply by its **conjugate** `1 - sqrt(2)`.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>`-2x &gt; 6`. Divide by -2 and flip: `x &lt; -3`. Test it: `x = -4` gives `-2(-4) = 8 &gt; 6` ✓, while `x = 0` gives `0 &gt; 6` ✗.</t>
+          <t>You are multiplying by 1, so the value is unchanged — but the expression becomes estimable. The conjugate works because the difference of squares kills the root.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>The trap is dividing by a *variable* whose sign you do not know. From `ax &gt; a` you cannot conclude `x &gt; 1` unless you are told `a &gt; 0`.</t>
-        </is>
-      </c>
+          <t>`3/sqrt(2) = 3sqrt(2)/2 ≈ 2.12`. And `1/(1 + sqrt(2)) = (1 - sqrt(2))/(1 - 2) = sqrt(2) - 1`.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Inequalities &amp; Functions</t>
+          <t>Rates, Exponents &amp; Roots</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Adding and subtracting inequalities</t>
+          <t>`sqrt(x^2)` = ?</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Two inequalities pointing the same way can always be added: if `a &gt; b` and `c &gt; d`, then `a + c &gt; b + d`. Subtracting is only safe when they point in **opposite** directions, and the result keeps the sign of the one you subtract *from*.
-Concretely, from `a &gt; b` and `c &lt; d` you may conclude `a - c &gt; b - d`. The intuition: subtracting a smaller thing leaves you with more.</t>
+          <t>`|x|`, **not** `x`. The radical sign always returns the non-negative root. The same applies to any even power under any even root.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Given `5 &lt; x &lt; 9` and `1 &lt; y &lt; 4`, what is the range of `x - y`? Flip the second to `-4 &lt; -y &lt; -1` and add: `1 &lt; x - y &lt; 8`.</t>
+          <t>Odd roots have no such problem: `cuberoot(x^3) = x` even for negative `x`, because cube roots can return negatives.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Never subtract two same-direction inequalities. From `x &gt; 2` and `y &gt; 1` you cannot say `x - y &gt; 1`: take `x = 3, y = 10`.</t>
+          <t>With `x = -5`: `sqrt(x^2) = sqrt(25) = 5 = |x|`. So `sqrt(x^2) = 3` has two solutions, `x = ±3`, while `x^3 = 27` has one.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>In a comparison, "`x^2 = 16`" means `x` could be 4 **or** -4. Any question that squares away a sign is usually heading for D.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Inequalities &amp; Functions</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Absolute values in inequalities</t>
+          <t>Degree of a polynomial — how is it measured?</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Isolate the absolute value on the left, then split into two cases exactly as with equations — but when you negate the right-hand side, the inequality sign flips as well.
-The two shapes are worth memorising as pictures. `|x| &lt; a` means `-a &lt; x &lt; a`, a single band around zero. `|x| &gt; a` means `x &gt; a` **or** `x &lt; -a`, two pieces heading outwards.</t>
+          <t>Add the exponents **within each term**; the largest of those totals is the degree.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>`|2x - 6| &lt; 4` becomes `-4 &lt; 2x - 6 &lt; 4`, so `2 &lt; 2x &lt; 10`, giving `1 &lt; x &lt; 5`. By contrast `|2x - 6| &gt; 4` gives `2x - 6 &gt; 4` or `2x - 6 &lt; -4`, i.e. `x &gt; 5` or `x &lt; 1`.</t>
+          <t>A single term with several variables counts them all together, which is the part people miss.
+Degree tells you what to expect: degree 1 graphs as a line with one solution, degree 2 as a parabola with up to two, and in general a polynomial of degree `n` has at most `n` real roots and at most `n - 1` turning points.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>`|x - 3| &lt; 5` is best read as "x is less than 5 away from 3", which immediately gives `-2 &lt; x &lt; 8`. Reading absolute value as distance prevents most sign errors.</t>
-        </is>
-      </c>
+          <t>`(2x^2)(4y^3) = 8x^2y^3` has degree `2 + 3 = 5`. In `x^3 + 5x^2y^2 - 7` the term degrees are 3, 4 and 0, so the polynomial has degree **4**.
+`(x + 2)(x - 3)(x + 5)` has degree 3 without expanding — just count the brackets.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Inequalities &amp; Functions</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Sign charts for factored inequalities</t>
+          <t>What disqualifies an expression from being a polynomial?</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>An inequality like `(x + 3)(x - 2) &gt; 0` has two critical values, -3 and 2, but the answer is not simply "x between them" or "x outside them" — you have to check. Mark the critical values on a line, then test one value in each of the three regions and see whether the product is positive or negative.
-For a product of two factors: positive outside the roots, negative between them (when the leading coefficient is positive).</t>
+          <t>Negative exponents (variables in a denominator), fractional exponents (roots of variables), and absolute values.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>`(x + 3)(x - 2) &gt; 0`. Test `x = -4`: `(-1)(-6) = +6` ✓. Test `x = 0`: `(3)(-2) = -6` ✗. Test `x = 3`: `(6)(1) = +6` ✓. So the solution is `x &lt; -3` or `x &gt; 2`.</t>
+          <t>A polynomial is a sum of terms made only of numbers and variables raised to whole-number powers. That restriction is what makes the factoring rules always work.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Always move everything to one side first. Solving `(x+3)(x-2) &gt; 6` by setting each factor against 6 is meaningless; expand, subtract 6, refactor, then test.</t>
-        </is>
-      </c>
+          <t>`3x^2 - 5x + 7` ✓. `3/x + 2` ✗ (that is `3x^-1`). `sqrt(x) + 1` ✗. `|x| + 4` ✗. But `(3/4)x^2` ✓ — fractional *coefficients* are fine, only fractional *exponents* are not.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Inequalities &amp; Functions</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Functions with an expression inside</t>
+          <t>What is a linear equation?</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>When a function is defined as `f(something) = ...`, the rule tells you what happens to whatever the "something" evaluates to. To find `f(7)`, set the inside expression equal to 7, solve for `x`, and substitute that `x` into the right-hand side.</t>
+          <t>A polynomial equation of degree 1 — every variable to the first power only. It graphs as a straight line and has exactly one solution unless the variable cancels out.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>`f(x + 3) = x^2 + x`. What is `f(7)`? Set `x + 3 = 7`, so `x = 4`. Then the right side is `4^2 + 4 = 20`, so `f(7) = 20`. Substituting 7 directly for `x` would have given 56, the wrong answer the question is fishing for.</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
+          <t>Recognising degree tells you what tools apply: linear means isolate and solve, degree 2 means factor, discriminant or the quadratic formula.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>`3x + 7 = 22` → `x = 5`. `y = 2x - 3` is linear in two variables. `x^2 + 3x = 4` is not linear.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Inequalities &amp; Functions</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Functions defined in terms of themselves</t>
+          <t>Two equations, two unknowns — how do you solve them?</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>A recursive definition tells you how to get from one input to the next rather than giving values outright. Read it as a step rule, then walk from the value you are given to the value you want.</t>
+          <t>**Substitution** (solve one for a variable, put it into the other) or **elimination** (scale one equation so a variable cancels when you add or subtract).</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>`f(x + 1) = 10 f(x)`, and `f(3) = 5`. What is `f(6)`? Each step up multiplies by 10: `f(4) = 50`, `f(5) = 500`, `f(6) = 5,000`. Three steps, so equivalently `f(6) = 5 x 10^3`.</t>
+          <t>Elimination is usually faster when coefficients line up; substitution is better when one variable is already isolated.
+Watch what the question actually asks: it often wants `x + y` or `x - y`, which you can get by adding or subtracting the equations directly — no need to find `x` and `y` at all.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Count the steps, not the numbers. From `f(3)` to `f(6)` is three steps, not six.</t>
+          <t>`2x + 3y = 16` and `x - y = 2`. Substituting `x = y + 2` gives `2y + 4 + 3y = 16`, so `y = 2.4` and `x = 4.4`. But if the question only wanted `3x + 2y`, adding the two equations as they stand gets there faster.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Two equations that are multiples of each other have infinitely many solutions; two with the same slope and different constants have none.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Inequalities &amp; Functions</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Finding the range of a function</t>
+          <t>Expanding brackets, and factoring `x^2 + bx + c`?</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>The range is the set of outputs the function can produce. A reliable method: set `y = f(x)`, rearrange to express `x` in terms of `y`, and then ask what values of `y` are legal in that new expression. Whatever `y` cannot be is missing from the range.</t>
+          <t>Expand with FOIL: `(x + p)(x + q) = x^2 + (p+q)x + pq`. To factor, find two numbers that **multiply to `c` and add to `b`**.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>`y = (3 - x)/(x - 2)`. Multiply out: `y(x - 2) = 3 - x`, so `yx + x = 3 + 2y`, giving `x = (3 + 2y)/(y + 1)`. That is undefined at `y = -1`, so the range of the original function is every real number except -1.</t>
+          <t>Factoring is FOIL run backwards, and the multiply-to/add-to search is quick because you only test factor pairs of `c`. If the `x^2` has a coefficient, factor it out first or test pairs on `ac`.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Do not confuse range with domain. Here the *domain* excludes `x = 2` (the original denominator) and the *range* excludes `y = -1`.</t>
+          <t>`x^2 + 7x + 12`: which pair multiplies to 12 and adds to 7? 3 and 4, so it is `(x+3)(x+4)`. `x^2 - 5x + 6` → -2 and -3 → `(x-2)(x-3)`.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Signs are where it goes wrong: a positive `c` with a negative `b` means **both** numbers are negative.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Inequalities &amp; Functions</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Even functions</t>
+          <t>The three quadratic identities?</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>A function is even when `f(-x) = f(x)`: feeding in the opposite input gives the same output. For polynomials that happens exactly when every power of `x` is even (a constant counts as `x^0`). Their graphs are mirror images across the y-axis.</t>
+          <t>`a^2 + 2ab + b^2 = (a + b)^2`
+`a^2 - 2ab + b^2 = (a - b)^2`
+`a^2 - b^2 = (a + b)(a - b)`</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>`f(x) = x^2 + 3` is even: `f(-2) = 7 = f(2)`. `cos(x)` and `|x|` are even too. But `f(x) = x^2 + x` is not, because the `x` term is odd-powered: `f(-2) = 2` while `f(2) = 6`.</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr"/>
+          <t>The third — difference of squares — is the workhorse, turning awkward arithmetic into mental arithmetic and simplifying fractions in one step.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>`97 x 103 = (100-3)(100+3) = 10,000 - 9 = 9,991`. Given `x + y = 10` and `x - y = 4`, then `x^2 - y^2 = 40` without ever finding `x` or `y`.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Inequalities &amp; Functions</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Odd functions</t>
+          <t>How do you spot that an expression is one of the identities?</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>A function is odd when `f(-x) = -f(x)`: flipping the input flips the sign of the output. For polynomials that means every power of `x` is odd and there is no constant term. Their graphs have 180° rotational symmetry about the origin.</t>
+          <t>First and last terms are perfect squares, and the middle term is **twice** the product of their roots → perfect square trinomial. Two squares with a minus between → difference of squares.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>`f(x) = x^3 - x` is odd: `f(-2) = -6` and `f(2) = 6`. Adding a constant breaks it — `x^3 + 1` is neither even nor odd, which is the usual state of affairs. Only `f(x) = 0` manages to be both.</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr"/>
+          <t>Scanning for these shapes before grinding through algebra saves the most time of any habit in this section.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>`x^2 + 10x + 25 = (x+5)^2` (25 is `5^2`, and `10x = 2 x 5 x x`). `4x^2 - 9 = (2x+3)(2x-3)`. `(x^2 - 9)/(x + 3)` simplifies to `x - 3`.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Check the middle term first: `x^2 + 7x + 25` is **not** `(x+5)^2`, which would need `10x`.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Lines, Parabolas &amp; Circles</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>What the intercepts tell you about a line</t>
+          <t>The quadratic formula?</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>The signs of a line's two intercepts are decided by its slope and whether it passes through the origin, and questions exploit that constantly.
-A line through the origin has both intercepts equal to 0, whatever its slope. A horizontal line (slope 0) has only a y-intercept, which can sit anywhere. For a line **not** through the origin: a positive slope forces one intercept positive and the other negative, so their **product is negative**; a negative slope puts both intercepts on the same side, so their **product is positive**.</t>
+          <t>For `ax^2 + bx + c = 0`:
+`x = (-b ± sqrt(b^2 - 4ac)) / 2a`</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>`y = 2x - 6` (positive slope): y-intercept -6, x-intercept 3, product -18 — negative, as predicted. `y = -2x + 6` (negative slope): y-intercept 6, x-intercept 3, product 18 — positive.</t>
+          <t>It always works, so it is the fallback when factoring fails. The quantity under the root is the discriminant, so the formula also tells you the number of solutions.
+Rearrange to `= 0` first and keep the signs: in `x^2 - 4x - 6`, `c` is -6.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>A vertical line has no slope at all (undefined, not zero) and no y-intercept unless it *is* the y-axis.</t>
-        </is>
-      </c>
+          <t>`2x^2 + 3x - 2 = 0`: `x = (-3 ± sqrt(9 + 16))/4 = (-3 ± 5)/4`, giving `x = 1/2` and `x = -2`. Factoring confirms it: `(2x - 1)(x + 2)`.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Lines, Parabolas &amp; Circles</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Slopes of perpendicular lines</t>
+          <t>How many solutions does a quadratic have?</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Perpendicular lines have slopes that are negative reciprocals: if one has slope `m`, the other has slope `-1/m`, and their product is always -1. Parallel lines, by contrast, have equal slopes.</t>
+          <t>Check the discriminant `b^2 - 4ac`: **positive** → 2 solutions, **zero** → 1, **negative** → none.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>A line with slope 2/3 is perpendicular to one with slope -3/2, and `(2/3)(-3/2) = -1` ✓. So the line perpendicular to `y = 4x + 1` through the origin is `y = -x/4`.</t>
+          <t>You do not need the solutions themselves to answer "how many", which is exactly what the question usually wants.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Horizontal and vertical lines are perpendicular to each other, but the rule fails numerically because `-1/0` is undefined. Treat that pair as a special case.</t>
-        </is>
-      </c>
+          <t>`x^2 - 4x - 6`: `16 + 24 = 40 &gt; 0` → two. `x^2 - 4x + 4`: `16 - 16 = 0` → one (`x = 2`). `x^2 + x + 5`: `1 - 20 &lt; 0` → none.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Lines, Parabolas &amp; Circles</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Parabolas from perfect squares</t>
+          <t>Completing the square — what do you add?</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>A quadratic that is a perfect square, like `y = (x - 3)^2`, touches the x-axis at exactly one point rather than crossing it. That single point is both the root and the vertex — the minimum of the curve if it opens upward, the maximum if it opens downward.
-This is the graphical face of "discriminant = 0, one solution".</t>
+          <t>Half the coefficient of `x`, squared — add it to **both** sides. `x^2 + bx` becomes a perfect square once you add `(b/2)^2`.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>`y = (x - 3)^2` has its only root at `x = 3`, and the vertex sits at `(3, 0)`. `y = -(x + 2)^2` opens downward with its maximum at `(-2, 0)`.</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr"/>
+          <t>It forces a quadratic that will not factor into a single squared bracket you can undo with a root. It is also how you find a parabola's vertex.</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>`x^2 - 4x - 6 = 0`. Half of -4 is -2, squared is 4: `(x^2 - 4x + 4) - 6 = 4`, so `(x-2)^2 = 10` and `x = 2 ± sqrt(10)`.</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Divide through by the leading coefficient first — completing the square needs `x^2` to stand alone.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Lines, Parabolas &amp; Circles</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Horizontal shifts of a parabola</t>
+          <t>When you cancel a factor from a fraction, what must you record first?</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Changing `x` inside the bracket slides the curve sideways, and it moves the **opposite** way to the sign you see. `y = (x - h)^2` shifts `h` units **right**; `y = (x + h)^2` shifts `h` units **left**.
-The reason is that the vertex sits wherever the bracket equals zero: in `(x - 3)^2` that is `x = +3`.</t>
+          <t>The **domain of the original expression**. Cancelling `(x - 5)` quietly divides by it, so `x = 5` stays excluded even though the factor has vanished.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>`y = (x - 4)^2` is the basic parabola moved 4 right, with vertex `(4, 0)`. `y = (x + 4)^2` is moved 4 left, with vertex `(-4, 0)`.</t>
+          <t>The restriction belongs to the original expression, not the simplified one, so work the domain out before you simplify. This is exactly how a graph ends up with a hole in it.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>This inside-the-bracket sign flip is the single most common graphing error. Solve "bracket = 0" every time rather than trusting the sign.</t>
-        </is>
-      </c>
+          <t>`(x^2 - 25)/((x+5)(x-5))` simplifies to 1, but the domain still excludes **both** `x = 5` and `x = -5`. Reading the simplified form alone would lose both.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Lines, Parabolas &amp; Circles</t>
+          <t>Equations &amp; Quadratics</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Vertical shifts of a parabola</t>
+          <t>`|expression| = something` — how do you solve it?</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Changing the constant *outside* the square moves the curve up or down, and this time the direction matches the sign. `y = x^2 + k` shifts `k` up; `y = x^2 - k` shifts `k` down.</t>
+          <t>Isolate the absolute value, then split into two equations: `expression = something` and `expression = -(something)`.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>`y = x^2 + 3` has its vertex at `(0, 3)` and never touches the x-axis. `y = x^2 - 3` has its vertex at `(0, -3)` and crosses at `x = ±sqrt(3)`. Combining both kinds of shift, `y = (x - 2)^2 + 5` has vertex `(2, 5)`.</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr"/>
+          <t>The bars hide the sign of what is inside, so both possibilities must be chased and both checked.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>`|4x + 9| = 21` → `4x + 9 = 21` gives `x = 3`; `4x + 9 = -21` gives `x = -7.5`. Both check out.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Isolate first: `2|x| + 3 = 11` must become `|x| = 4`. And if the right side is negative there are **no** solutions.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Lines, Parabolas &amp; Circles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Graphing a quadratic by completing the square</t>
+          <t>The one rule that makes inequalities different from equations?</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Any quadratic can be rewritten as `y = (x - h)^2 + k`, and in that vertex form the graph is simply the basic parabola moved `h` right and `k` up. Completing the square is therefore also a graphing tool: it converts an unreadable expression into a vertex you can plot immediately.</t>
+          <t>Multiplying or dividing both sides by a **negative** number flips the inequality sign.</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>`y = x^2 - 4x - 6`. Half of -4 is -2, squared is 4, so `y = (x^2 - 4x + 4) - 4 - 6 = (x - 2)^2 - 10`. The vertex is `(2, -10)`, the minimum value is -10, and the y-intercept is still -6 (set `x = 0`).</t>
+          <t>Negating reflects every number through zero on the number line, so whatever was on the left ends up on the right. Adding and subtracting are safe.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Whatever you add inside the bracket must be subtracted outside it, or you have changed the function.</t>
+          <t>`-2x &gt; 6` → divide by -2 and flip → `x &lt; -3`. Test: `x = -4` gives `8 &gt; 6` ✓; `x = 0` gives `0 &gt; 6` ✗.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>The real trap is dividing by a **variable** of unknown sign. From `ax &gt; a` you cannot conclude `x &gt; 1` unless you know `a &gt; 0`.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Lines, Parabolas &amp; Circles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>The equation of a circle</t>
+          <t>Can you add or subtract two inequalities?</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>A circle of radius `r` centred at `(h, k)` is the set of points at distance `r` from the centre, which the distance formula turns into
-`(x - h)^2 + (y - k)^2 = r^2`
-Note the same inside-the-bracket sign flip as parabolas: `(x - 3)` means the centre is at `x = +3`. And the right-hand side is `r^2`, not `r`.</t>
+          <t>Add freely when they point the **same** way. Subtract only when they point **opposite** ways, and the result keeps the sign of the one you subtract from.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>`(x - 3)^2 + (y + 2)^2 = 25` is a circle centred at `(3, -2)` with radius 5. A circle centred at the origin simplifies to `x^2 + y^2 = r^2`.</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr"/>
+          <t>From `a &gt; b` and `c &lt; d` you may conclude `a - c &gt; b - d` — subtracting a smaller thing leaves you with more. The safest habit is to flip the second inequality and add.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Given `5 &lt; x &lt; 9` and `1 &lt; y &lt; 4`, find the range of `x - y`. Flip the second to `-4 &lt; -y &lt; -1` and add: `1 &lt; x - y &lt; 8`.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Never subtract two same-direction inequalities: from `x &gt; 2` and `y &gt; 1` you cannot say `x - y &gt; 1` — take `x = 3, y = 10`.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Lines, Parabolas &amp; Circles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Recognising a circle from its equation</t>
+          <t>`|x| &lt; a` and `|x| &gt; a` — what do they look like on the line?</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>If an equation contains both `x^2` and `y^2` added together, it is an ellipse of some kind. It is specifically a **circle** when the coefficients of `x^2` and `y^2` are equal — equal coefficients mean the curve stretches by the same amount in both directions.</t>
+          <t>`|x| &lt; a` is one band: `-a &lt; x &lt; a`. `|x| &gt; a` is two pieces heading outwards: `x &gt; a` **or** `x &lt; -a`. When you negate the right-hand side, the sign flips too.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>`3x^2 + 3y^2 = 27` is a circle: divide by 3 to get `x^2 + y^2 = 9`, radius 3. `4x^2 + 9y^2 = 36` is an ellipse, since 4 ≠ 9. And `x^2 - y^2 = 9` is neither — a minus sign makes it a hyperbola.</t>
+          <t>Reading the bars as distance prevents most sign errors: `|x - 3| &lt; 5` says "x is less than 5 away from 3".</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Equal coefficients are required, not coefficients of 1. Divide through before reading off the radius.</t>
-        </is>
-      </c>
+          <t>`|2x - 6| &lt; 4` → `-4 &lt; 2x - 6 &lt; 4` → `1 &lt; x &lt; 5`. But `|2x - 6| &gt; 4` → `x &gt; 5` **or** `x &lt; 1`.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Reflections, Rotations &amp; Angles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Reflecting across the axes and the origin</t>
+          <t>`(x + 3)(x - 2) &gt; 0` — what is the solution set?</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Reflecting a point across an axis flips the sign of the **other** coordinate — the one measuring distance from that axis. Across the x-axis, `(x, y)` becomes `(x, -y)`; across the y-axis it becomes `(-x, y)`. Reflecting through the origin flips both: `(x, y)` becomes `(-x, -y)`.
-Remember which sign changes by asking what stays the same: reflecting in the x-axis keeps you at the same horizontal position, so `x` is untouched.</t>
+          <t>`x &lt; -3` **or** `x &gt; 2`. Mark the critical values on a line and **test a value in each of the three regions** — do not guess from the signs.</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>`(2, 3)` reflected in the x-axis is `(2, -3)`; in the y-axis it is `(-2, 3)`; through the origin it is `(-2, -3)`. Reflecting in both axes one after the other gives the same result as reflecting through the origin.</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr"/>
+          <t>For a product of two factors with a positive leading coefficient: positive outside the roots, negative between them.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Test `x = -4`: `(-1)(-6) = +6` ✓. Test `x = 0`: `(3)(-2) = -6` ✗. Test `x = 3`: `(6)(1) = +6` ✓. So the outside regions win.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Move everything to one side first. Solving `(x+3)(x-2) &gt; 6` by setting each factor against 6 is meaningless — expand, subtract 6, refactor, then test.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Reflections, Rotations &amp; Angles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Reflecting across the vertical line x = k</t>
+          <t>`f(x + 3) = x^2 + x`. What is `f(7)`?</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>The y-coordinate is unchanged and the x-coordinate lands as far on the other side of `k` as it started on this side:
-`(x, y) → (2k - x, y)`
-Rather than memorise it, compute the distance to the line and step that far again: from `x` to `k` is `k - x`, so the image is at `k + (k - x) = 2k - x`.</t>
+          <t>**20.** Set the inside expression equal to 7: `x + 3 = 7`, so `x = 4`, and then evaluate the right-hand side at `x = 4`: `16 + 4 = 20`.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Reflect `(2, 3)` across `x = 5`. The point is 3 to the left of the line, so the image is 3 to the right, at `x = 8`: `(8, 3)`. The formula agrees: `2(5) - 2 = 8`.</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr"/>
+          <t>The rule describes what happens to whatever the inside expression evaluates to, so you must solve for the `x` that produces the input you want.
+The same care is needed for composite functions: `f(g(x))` means run `g` first, then feed its output into `f`. Work from the inside out.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Substituting 7 directly for `x` would give 56 — the wrong answer the question is fishing for.
+With `f(x) = 2x + 1` and `g(x) = x^2`: `f(g(3)) = f(9) = 19`, but `g(f(3)) = g(7) = 49`. Order matters.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Reflections, Rotations &amp; Angles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Reflecting across the horizontal line y = k</t>
+          <t>A function defined in terms of itself — how do you use it?</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>The mirror image of the previous rule: the x-coordinate stays put and the y-coordinate reflects through `k`.
-`(x, y) → (x, 2k - y)`</t>
+          <t>Read it as a **step rule** and walk from the value you are given to the value you want.</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Reflect `(2, 3)` across `y = 1`. The point is 2 above the line, so the image is 2 below, at `y = -1`: `(2, -1)`. The formula: `2(1) - 3 = -1` ✓. Note `y = 0` recovers the x-axis rule, `(x, -y)`.</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr"/>
+          <t>Recursive definitions tell you how to move from one input to the next rather than giving values outright.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>`f(x + 1) = 10 f(x)` with `f(3) = 5`. Each step multiplies by 10: `f(4) = 50`, `f(5) = 500`, `f(6) = 5,000` — three steps, so `5 x 10^3`.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Count steps, not numbers: from `f(3)` to `f(6)` is three steps, not six.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Reflections, Rotations &amp; Angles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Reflecting across the line y = x</t>
+          <t>How do you find the range of a function?</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Swap the coordinates: `(x, y)` becomes `(y, x)`. The line `y = x` is the diagonal where the two coordinates are equal, and reflecting in it exchanges the roles of horizontal and vertical.
-This is also why the graph of an inverse function is the reflection of the original in `y = x`.</t>
+          <t>Set `y = f(x)`, rearrange to get `x` in terms of `y`, and ask which `y` values are legal. Whatever `y` cannot be is missing from the range.</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>`(2, 3)` reflected in `y = x` is `(3, 2)`. Reflecting in `y = -x` instead gives `(-y, -x)`, so `(2, 3)` would become `(-3, -2)`.</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr"/>
+          <t>Solving for `x` converts a question about outputs into a question about a domain, which you already know how to answer.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>`y = (3 - x)/(x - 2)` → `y(x-2) = 3-x` → `x(y+1) = 3+2y` → `x = (3+2y)/(y+1)`, undefined at `y = -1`. So the range is every real number except **-1**.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Do not confuse the two: here the *domain* excludes `x = 2` and the *range* excludes `y = -1`.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Reflections, Rotations &amp; Angles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Rotating 90° anticlockwise about the origin</t>
+          <t>What makes a function even?</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>`(x, y) → (-y, x)`. Swap the coordinates and then negate the new first one.
-You can always check a rotation rule with an easy point instead of trusting memory: `(1, 0)` sits on the positive x-axis, and a quarter turn anticlockwise should carry it to `(0, 1)` on the positive y-axis — which the rule does.</t>
+          <t>`f(-x) = f(x)`. For polynomials that means every power of `x` is **even** (a constant counts as `x^0`). The graph is symmetric about the y-axis.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>`(2, 3)` rotated 90° anticlockwise becomes `(-3, 2)`. Sketch it: the point moves from the first quadrant into the second, which is what an anticlockwise quarter turn should do.</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr"/>
+          <t>Feeding in the opposite input gives the same output, so the two halves of the graph mirror each other.</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>`f(x) = x^2 + 3` is even: `f(-2) = 7 = f(2)`. `f(x) = x^2 + x` is not, because of the odd-powered term: `f(-2) = 2` but `f(2) = 6`.</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Reflections, Rotations &amp; Angles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Rotating 90° clockwise about the origin</t>
+          <t>What makes a function odd?</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>`(x, y) → (y, -x)`. Swap the coordinates and negate the new second one — the mirror of the anticlockwise rule.</t>
+          <t>`f(-x) = -f(x)`. For polynomials that means every power is **odd** and there is no constant term. The graph has 180° rotational symmetry about the origin.</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>`(2, 3)` rotated 90° clockwise becomes `(3, -2)`, moving from the first quadrant into the fourth. Check with `(1, 0)`: it should land on `(0, -1)`, and it does. Note that three anticlockwise turns equal one clockwise turn.</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr"/>
+          <t>Flipping the input flips the sign of the output.
+A quick test that avoids algebra: if the graph looks the same after turning the page 180°, it is odd; if it looks the same after folding along the y-axis, it is even.</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>`f(x) = x^3 - x` is odd: `f(-2) = -6`, `f(2) = 6`. Adding a constant breaks it — `x^3 + 1` is neither. Only `f(x) = 0` is both even and odd.
+For any odd function `f(0) = 0`, because `f(-0) = -f(0)` forces it. That single fact answers many "which could be odd" questions immediately.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Reflections, Rotations &amp; Angles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Rotating 180° about the origin</t>
+          <t>Slope of a line, and the equation of a line?</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>`(x, y) → (-x, -y)`, which is identical to reflecting through the origin. Half a turn sends every point to the opposite side, and the direction of rotation no longer matters.</t>
+          <t>`slope = (y2 - y1)/(x2 - x1)` = rise over run. Slope-intercept form: `y = mx + b`, where `m` is the slope and `b` the y-intercept.</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>`(2, 3)` rotated 180° becomes `(-2, -3)`, moving from the first quadrant to the third. A 270° anticlockwise rotation is the same as 90° clockwise, so `(2, 3)` would become `(3, -2)`.</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr"/>
+          <t>A positive slope rises left to right, a negative one falls, zero is horizontal, and a vertical line has **undefined** slope (the run is 0). Parallel lines share a slope.
+To find a line through two points: compute `m`, then substitute one point into `y = mx + b` to get `b`.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Through `(2, 3)` and `(6, 11)`: `m = (11-3)/(6-2) = 2`. Then `3 = 2(2) + b` gives `b = -1`, so `y = 2x - 1`.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Keep the points in the same order top and bottom. `(y2 - y1)/(x1 - x2)` flips the sign.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Reflections, Rotations &amp; Angles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Complementary and supplementary angles</t>
+          <t>Distance between two points in the plane?</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Two angles are **complementary** if they add to 90° and **supplementary** if they add to 180°. Supplementary pairs turn up constantly because angles on a straight line always sum to 180°, and so do co-interior angles between parallel lines.
-The alphabet trick: C comes before S, and 90 comes before 180.</t>
+          <t>`d = sqrt((x2 - x1)^2 + (y2 - y1)^2)` — Pythagoras on the horizontal and vertical gaps.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>The complement of 35° is 55°; its supplement is 145°. In a right triangle the two non-right angles are always complementary, since all three must total 180°.</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr"/>
+          <t>The two points are opposite corners of a right triangle whose legs are the coordinate differences, so the distance is its hypotenuse.</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>From `(1, 2)` to `(4, 6)`: legs 3 and 4, so `d = 5`. Recognising the 3-4-5 saves the square root entirely.</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Squaring removes signs, so the order of the points does not matter here — unlike in the slope formula.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Reflections, Rotations &amp; Angles</t>
+          <t>Inequalities, Functions &amp; Coordinate Basics</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Interior angles of a polygon</t>
+          <t>Midpoint of a segment?</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>For a polygon with `n` sides the interior angles add up to `(n - 2) x 180°`. Any polygon can be cut into `n - 2` triangles by drawing diagonals from one vertex, and each triangle contributes 180°.
-For a **regular** polygon each interior angle is that total divided by `n`.</t>
+          <t>`((x1 + x2)/2, (y1 + y2)/2)` — average each coordinate separately.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>A hexagon has `(6 - 2) x 180 = 720°` in total, so a regular hexagon has interior angles of `720/6 = 120°` each. A pentagon totals 540°, giving 108° per angle when regular.</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr"/>
+          <t>The midpoint is the average point, which is also why a question giving you one endpoint and the midpoint lets you solve for the other endpoint.
+A line's midpoint is also the centre of the circle that has that line as a diameter, which is how coordinate-geometry questions link the two formulas.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Midpoint of `(1, 2)` and `(7, 10)` is `(4, 6)`. Backwards: if `(4, 6)` is the midpoint and one endpoint is `(1, 2)`, the other satisfies `(1 + x)/2 = 4`, so it is `(7, 10)`.
+If `(2,1)` and `(8,9)` are the ends of a diameter, the centre is `(5,5)` and the radius is half the distance, `= 5`, so the circle is `(x-5)^2 + (y-5)^2 = 25`.</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Reflections, Rotations &amp; Angles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Exterior angles always total 360°</t>
+          <t>What do the signs of a line's two intercepts tell you?</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Whatever the number of sides, one exterior angle at each vertex always sums to 360°. Walking once around the polygon turns you through one full revolution, and the amount you turn at each corner is exactly the exterior angle.
-For a regular polygon, each exterior angle is `360/n` — often a faster route to the interior angle, which is its supplement.</t>
+          <t>Through the origin: both are 0. Not through the origin — **positive slope → intercepts have opposite signs** (product negative); **negative slope → same signs** (product positive). Slope 0 has only a y-intercept.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>A regular hexagon: each exterior angle is `360/6 = 60°`, so each interior angle is `180 - 60 = 120°`, matching the other formula. If a question says a regular polygon has exterior angles of 24°, then `n = 360/24 = 15` sides.</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr"/>
+          <t>A rising line that misses the origin has to cross one axis on each side of it; a falling line crosses both on the same side. Questions test this without ever giving you an equation.</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>`y = 2x - 6`: intercepts -6 and 3, product -18 (negative) ✓. `y = -2x + 6`: intercepts 6 and 3, product 18 (positive) ✓.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>A vertical line has **undefined** slope, not zero, and no y-intercept unless it is the y-axis itself.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Regular polygons</t>
+          <t>Slopes of perpendicular lines?</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>A polygon is regular when all its sides are equal **and** all its angles are equal. Equilateral triangles and squares are the familiar cases. Regularity is what lets you divide the angle total by `n` to get a single angle, and it is also the condition behind several maximum-area results later on.</t>
+          <t>Negative reciprocals: if one is `m`, the other is `-1/m`, and their product is **-1**. (Parallel lines have equal slopes.)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>A regular octagon has 8 equal sides and 8 equal angles of `(8-2) x 180/8 = 135°` each. A rhombus has equal sides but unequal angles, and a rectangle has equal angles but unequal sides — neither is regular; only the square is both.</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr"/>
+          <t>Turning a line 90° swaps rise and run and reverses one of the signs.</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Slope 2/3 is perpendicular to -3/2, and `(2/3)(-3/2) = -1` ✓. So the perpendicular to `y = 4x + 1` through the origin is `y = -x/4`.</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Horizontal and vertical lines are perpendicular but break the formula, since `-1/0` is undefined. Treat that pair as a special case.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>The quadrilateral family</t>
+          <t>A quadratic that is a perfect square — what does its graph do?</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>They nest inside each other, and knowing the hierarchy answers a lot of "must be true" questions:
-- **Parallelogram**: two pairs of parallel sides. Opposite sides and opposite angles are equal; diagonals bisect each other.
-- **Rhombus**: a parallelogram with all four sides equal.
-- **Rectangle**: a parallelogram with all four angles 90°.
-- **Square**: both a rhombus and a rectangle.
-- **Trapezoid**: exactly one pair of parallel sides, so it is not a parallelogram at all.</t>
+          <t>It **touches** the x-axis at exactly one point instead of crossing. That point is both the only root and the vertex.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Every square is a rectangle, but most rectangles are not squares. So "a quadrilateral with four equal sides" could be a square or a non-square rhombus — enough ambiguity to make a comparison question answer D.</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
+          <t>This is the graphical face of "discriminant = 0, one solution".
+It also tells you the sign of the whole expression: `(x - 3)^2` is never negative, so `y = (x-3)^2 + 4` is always at least 4 — a favourite way to hide a minimum value in a comparison.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>`y = (x - 3)^2` has its only root and its minimum at `(3, 0)`. `y = -(x + 2)^2` opens downward with its maximum at `(-2, 0)`.
+`y = x^2 - 6x + 9 = (x-3)^2` touches the axis at `x = 3`; its discriminant is `36 - 36 = 0` ✓.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>What a trapezoid does and does not guarantee</t>
+          <t>`y = (x - h)^2` and `y = (x + h)^2` — which way do they move?</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>In a trapezoid all four sides and all four angles can be different; the only structural rule is that the two angles on the same leg (between the parallel sides) add to 180°, because they are co-interior angles across parallel lines.
-So do not assume symmetry. Only an *isosceles* trapezoid has equal legs and equal base angles, and the question has to tell you that.</t>
+          <t>Opposite to the sign you see: `(x - h)^2` shifts `h` **right**, `(x + h)^2` shifts `h` **left**.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>A trapezoid with parallel sides top and bottom and a base angle of 70° has an angle of 110° directly above it on the same leg. The other leg could carry 50° and 130°, a completely different pair.</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr"/>
+          <t>The vertex sits where the bracket equals zero, so in `(x - 3)^2` that is `x = +3`. Solving "bracket = 0" is more reliable than remembering the rule.</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>`y = (x - 4)^2` has vertex `(4, 0)`; `y = (x + 4)^2` has vertex `(-4, 0)`.</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>This inside-the-bracket sign flip is the single most common graphing error.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Inscribed and circumscribed</t>
+          <t>`y = x^2 + k` and `y = x^2 - k` — which way do they move?</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>**Inscribed** means drawn inside; **circumscribed** means drawn around the outside. In both cases the touching condition matters: every vertex of the inner shape must sit on the outer shape.
-So a square inscribed in a circle has all four corners on the circle, and its diagonal is the circle's diameter. A circle inscribed in a square touches all four sides, and its diameter equals the square's side.</t>
+          <t>The way the sign says: `+k` shifts **up**, `-k` shifts **down**. Outside the square, the direction matches.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>A square inscribed in a circle of radius 5: the diagonal is the diameter, 10, so the side is `10/sqrt(2) = 5sqrt(2)` and the area is 50. A circle inscribed in a square of side 10 has radius 5 and area `25pi`.</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
+          <t>Combine both kinds of shift and you can place any parabola: `y = (x - h)^2 + k` has vertex `(h, k)`.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>`y = x^2 + 3` has vertex `(0, 3)` and never meets the x-axis. `y = x^2 - 3` has vertex `(0, -3)` and crosses at `±sqrt(3)`. `y = (x - 2)^2 + 5` has vertex `(2, 5)`.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Bigger angles face bigger sides</t>
+          <t>How do you find a parabola's vertex from an untidy quadratic?</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>In any triangle, the largest angle is opposite the longest side and the smallest angle is opposite the shortest side. The ordering runs both ways, so knowing the order of the angles tells you the order of the sides and vice versa.</t>
+          <t>Complete the square into **vertex form** `y = (x - h)^2 + k`; the vertex is `(h, k)`. (Or use `h = -b/2a`.)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>A triangle with angles 30°, 60°, 90° has its shortest side opposite the 30° and its longest (the hypotenuse) opposite the 90°. If a question says `angle A &gt; angle B`, you may conclude that side `a` (opposite A) is longer than side `b` — often all a comparison question needs.</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr"/>
+          <t>Vertex form is just the basic parabola shifted `h` right and `k` up, so completing the square doubles as a graphing tool: it converts an unreadable expression into a point you can plot.</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>`y = x^2 - 4x - 6` → `(x^2 - 4x + 4) - 4 - 6` → `(x - 2)^2 - 10`. Vertex `(2, -10)`, minimum value -10, y-intercept -6.</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Whatever you add inside the bracket must be subtracted outside it, or you have changed the function.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>The triangle inequality</t>
+          <t>Equation of a circle?</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Any two sides of a triangle must together exceed the third. Applied to all three pairs, this pins the missing side into a range: it must be greater than the difference of the other two and less than their sum.</t>
+          <t>`(x - h)^2 + (y - k)^2 = r^2`, centre `(h, k)`, radius `r`.</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Two sides are 7 and 10. The third side `x` satisfies `10 - 7 &lt; x &lt; 10 + 7`, so `3 &lt; x &lt; 17`. If `x` must also be an integer, there are 13 possibilities (4 through 16).</t>
+          <t>It is the distance formula rearranged: every point on the circle is `r` away from the centre. Note the same inside-the-bracket sign flip as parabolas, and that the right-hand side is `r^2`, not `r`.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>The inequality is strict. A "triangle" with sides 3, 7 and 10 is a flat line, not a triangle.</t>
-        </is>
-      </c>
+          <t>`(x - 3)^2 + (y + 2)^2 = 25` is centred at `(3, -2)` with radius **5**. Centred at the origin it simplifies to `x^2 + y^2 = r^2`.</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>When two triangles are congruent</t>
+          <t>Does an equation describe a circle?</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Congruent means identical in size and shape. Four combinations of three pieces of information are enough to guarantee it: **SSS** (three sides), **SAS** (two sides and the angle *between* them), **ASA** (two angles and the side between them) and **AAS** (two angles and a side not between them).
-The notable exception is **SSA** — two sides and an angle not between them — which does not determine a triangle; there are usually two different triangles that fit.</t>
+          <t>It needs `x^2` and `y^2` added together **with equal coefficients**. Equal coefficients → circle; unequal → ellipse; a minus sign → hyperbola.</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Given two triangles with sides 5, 7 and the 40° angle between them, they are congruent by SAS. But given sides 5 and 7 with a 40° angle opposite the 5, two different triangles satisfy the description, so nothing is guaranteed.</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr"/>
+          <t>Equal coefficients mean the curve stretches by the same amount in both directions, which is what makes it round.</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>`3x^2 + 3y^2 = 27` → divide by 3 → `x^2 + y^2 = 9`, a circle of radius 3. `4x^2 + 9y^2 = 36` is an ellipse. `x^2 - y^2 = 9` is neither.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Equal coefficients are required, not coefficients of 1 — divide through before reading off the radius.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Similar triangles</t>
+          <t>Reflecting a point across an axis, or the origin?</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Similar triangles have the same shape at a different scale: equal angles, and all corresponding lengths in one fixed ratio. Two equal angles are enough to prove similarity (the third follows automatically), which is usually how the GRE sets it up.
-Every length scales by the same factor — sides, heights, perimeters. Areas scale by the **square** of that factor.</t>
+          <t>Across the x-axis: `(x, -y)`. Across the y-axis: `(-x, y)`. Through the origin: `(-x, -y)`. The coordinate that flips is the one measuring distance from that axis.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Two triangles with angles 40°, 60°, 80°; the first has its 40°-side of length 6, the second 9, a ratio of 3:2. If the first has area 20, the second has area `20 x (3/2)^2 = 45`, not 30.</t>
+          <t>Ask what stays the same: reflecting in the x-axis keeps your horizontal position, so `x` is untouched.
+The same rules apply to whole shapes: reflect each vertex and rejoin them. Reflection preserves lengths and angles, so the image is congruent to the original.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Match corresponding sides by the angles they sit opposite, not by the order they are written in.</t>
-        </is>
-      </c>
+          <t>`(2, 3)` → x-axis: `(2, -3)`; y-axis: `(-2, 3)`; origin: `(-2, -3)`. Reflecting in both axes in turn is the same as reflecting through the origin.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>The 30-60-90 triangle</t>
+          <t>Reflecting `(x, y)` across the vertical line `x = k`?</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Its sides are always in the ratio `1 : sqrt(3) : 2`. The shortest side (`x`) faces the 30° angle, the hypotenuse (`2x`) faces the 90°, and the middle side (`x sqrt(3)`) faces the 60°. It is exactly half of an equilateral triangle cut down the middle.</t>
+          <t>`(2k - x, y)` — `y` unchanged.</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>A 30-60-90 triangle with hypotenuse 10 has a short side of 5 and a long leg of `5sqrt(3) ≈ 8.66`. This also gives the height of an equilateral triangle of side 10: `5sqrt(3)`.</t>
+          <t>Rather than memorising it, step the distance twice: from `x` to `k` is `k - x`, so the image sits at `k + (k - x) = 2k - x`.</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Match sides to angles, not to position in the picture. Given the *long leg* as 6, the short side is `6/sqrt(3) = 2sqrt(3)`, not 3.</t>
-        </is>
-      </c>
+          <t>Reflect `(2, 3)` across `x = 5`. The point is 3 left of the line, so the image is 3 right: `(8, 3)`. Formula agrees: `2(5) - 2 = 8`.
+Another: reflect `(-1, 4)` across `x = 2`. It is 3 units left, so the image is 3 right, at `(5, 4)` — and `2(2) - (-1) = 5` ✓.</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>The 45-45-90 triangle</t>
+          <t>Reflecting `(x, y)` across the horizontal line `y = k`?</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>An isosceles right triangle: two equal legs and a hypotenuse `sqrt(2)` times as long, ratio `1 : 1 : sqrt(2)`. It is a square cut along its diagonal, which is why the diagonal of a square with side `s` is `s sqrt(2)`.</t>
+          <t>`(x, 2k - y)` — `x` unchanged.</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Legs of 5 give a hypotenuse of `5sqrt(2) ≈ 7.07`. Backwards: a hypotenuse of 10 gives legs of `10/sqrt(2) = 5sqrt(2) ≈ 7.07`. So a square with diagonal 10 has side `5sqrt(2)` and area 50.</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
+          <t>The mirror image of the previous rule; setting `k = 0` recovers the x-axis rule `(x, -y)`.</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Reflect `(2, 3)` across `y = 1`. The point is 2 above, so the image is 2 below: `(2, -1)`. Formula: `2(1) - 3 = -1` ✓.
+Another: reflect `(6, -2)` across `y = 3`. It is 5 below, so the image is 5 above, at `(6, 8)` — and `2(3) - (-2) = 8` ✓.</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Lines, Parabolas &amp; Circles</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Splitting a triangle into special right triangles</t>
+          <t>Reflecting `(x, y)` across the line `y = x`?</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>When a triangle has awkward angles, drop a perpendicular from a vertex to the opposite side and look for the two special triangles inside it. An angle of 105° splits into 45 + 60, and 75° into 45 + 30 — and suddenly the whole figure is computable with known ratios.</t>
+          <t>Swap the coordinates: `(y, x)`.</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>A triangle with angles 30°, 105°, 45° and one known side. Drop the height from the 105° vertex: it splits into a 30-60-90 and a 45-45-90 sharing that height. Find the height from the known side, use each ratio to get the two base pieces, and add the two areas.</t>
+          <t>`y = x` is the diagonal where the coordinates are equal, so reflecting in it exchanges the roles of horizontal and vertical. This is also why an inverse function's graph is the original reflected in `y = x`.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>The perpendicular must land inside the triangle for the areas to add. For an obtuse triangle it may fall outside, in which case you subtract instead.</t>
-        </is>
-      </c>
+          <t>`(2, 3)` → `(3, 2)`. Across `y = -x` instead it becomes `(-y, -x)`, so `(2, 3)` → `(-3, -2)`.
+So the point `(0, 5)` on the y-axis lands on `(5, 0)` on the x-axis, and any point already on `y = x` stays put.</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Polygons &amp; Triangles</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Pythagorean triples worth memorising</t>
+          <t>Rotating `(x, y)` 90° anticlockwise about the origin?</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Four sets of whole numbers satisfy `a^2 + b^2 = c^2` often enough to be worth knowing by sight: **3-4-5**, **5-12-13**, **8-15-17** and **7-24-25**. Every multiple of a triple is also a triple, so 6-8-10 and 9-12-15 come free.
-Recognising one saves you a square-root calculation, and recognising a *near*-miss saves you from assuming a right angle that is not there.</t>
+          <t>`(-y, x)` — swap, then negate the new first coordinate.</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>A right triangle with legs 8 and 15 has hypotenuse 17 — no calculation needed. Legs of 9 and 12 give 15, since that is `3 x (3-4-5)`. And if a triangle has sides 5, 12 and 14, it is *not* right-angled, however familiar the 5 and 12 look.</t>
+          <t>Check any rotation rule with an easy point instead of trusting memory: `(1, 0)` sits on the positive x-axis and a quarter turn anticlockwise must take it to `(0, 1)`, which this rule does.
+Rotations preserve distance from the origin, so a point 5 units out stays 5 units out — a quick sanity check on any answer.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>The largest number must be the hypotenuse. Sides 3, 4 and 5 make a right triangle; sides 3, 5 and a hypotenuse of 4 are impossible.</t>
-        </is>
-      </c>
+          <t>`(2, 3)` → `(-3, 2)`, moving from the first quadrant into the second — exactly what an anticlockwise quarter turn should do.</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Area of an equilateral triangle</t>
+          <t>Rotating `(x, y)` 90° clockwise about the origin?</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>For side length `s`, the area is
-`area = (sqrt(3) x s^2)/4`
-It follows from the 30-60-90 ratios: the height of an equilateral triangle is `s sqrt(3)/2`, and area is half base times height.</t>
+          <t>`(y, -x)` — swap, then negate the new second coordinate.</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>An equilateral triangle of side 6 has area `(sqrt(3) x 36)/4 = 9sqrt(3) ≈ 15.6`. Doubling the side to 12 quadruples the area to `36sqrt(3)`, because area depends on `s^2`.</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr"/>
+          <t>The mirror of the anticlockwise rule. Three anticlockwise turns equal one clockwise turn, which is a handy check for 270° questions.
+Clockwise by 90° is the same as anticlockwise by 270°, and doing either four times returns you to the start. If a question rotates by 450°, subtract 360° first.</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>`(2, 3)` → `(3, -2)`, first quadrant to fourth. Test with `(1, 0)`: it should land on `(0, -1)` ✓.
+Rotating `(0, 4)` clockwise gives `(4, 0)`: the point travels from the positive y-axis to the positive x-axis ✓.</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Area of a parallelogram</t>
+          <t>Rotating `(x, y)` 180° about the origin?</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>`area = base x height`, where the height is the **perpendicular** distance between the two parallel sides — not the length of the slanted side. A parallelogram is a rectangle that has been pushed over, and pushing it over does not change base or height.</t>
+          <t>`(-x, -y)` — identical to reflecting through the origin, and the direction of rotation no longer matters.</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>A parallelogram with base 10 and slant side 6 leaning at 30° has height `6 x sin(30°) = 3`, so its area is 30, not 60. If the question gives you the height directly as 4, the area is simply 40.</t>
+          <t>Half a turn sends every point to the diametrically opposite side.
+Because it equals reflection through the origin, a 180° rotation is the only rotation that is also a reflection — which is why questions can describe the same transformation in two ways.</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Using the slanted side as the height is the classic error, and it always overestimates.</t>
-        </is>
-      </c>
+          <t>`(2, 3)` → `(-2, -3)`, first quadrant to third. A 270° anticlockwise turn equals 90° clockwise, so it would give `(3, -2)`.
+A shape with 180° rotational symmetry, such as a parallelogram, maps onto itself — its centre is the point you rotate about.</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Area of a trapezoid</t>
+          <t>Complementary and supplementary angles?</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>`area = ((base1 + base2)/2) x height`: the average of the two parallel sides times the perpendicular distance between them. You are really finding the width of the "average" rectangle.</t>
+          <t>**Complementary** add to 90°, **supplementary** add to 180°. C before S, 90 before 180.</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>A trapezoid with parallel sides 8 and 12 and height 5 has area `((8 + 12)/2) x 5 = 10 x 5 = 50`. If the two bases were equal it would be a parallelogram, and the formula would collapse to base times height.</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr"/>
+          <t>Supplementary pairs appear constantly because angles on a straight line total 180°. In any right triangle the two non-right angles are complementary.
+Two more facts close most diagram questions: angles on a straight line sum to 180°, and angles around a point sum to 360°. Vertical (opposite) angles are always equal.</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>The complement of 35° is 55°; its supplement is 145°.
+If two angles on a line are `3x` and `2x`, then `5x = 180`, so they are 108° and 72°. In a right triangle with one angle 35°, the third is 55°.</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Area of a regular polygon</t>
+          <t>Two parallel lines cut by a transversal — which angles are equal?</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>With `n` sides of length `s` and apothem `a` (the perpendicular distance from the centre to the middle of a side):
-`area = (n x s x a)/2`
-The polygon splits into `n` identical triangles, each with base `s` and height `a`. Since `n x s` is the perimeter, this is also "half perimeter times apothem".</t>
+          <t>Only **two** values appear, and every angle is one or the other. Corresponding, alternate interior and alternate exterior angles are **equal**; co-interior (same-side) angles are **supplementary**. Vertical (opposite) angles are always equal, parallel or not.</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>A regular hexagon of side 6 has apothem `3sqrt(3) ≈ 5.196`, so its area is `(6 x 6 x 5.196)/2 ≈ 93.5`. Cross-check with six equilateral triangles of side 6: `6 x 9sqrt(3) = 54sqrt(3) ≈ 93.5` ✓.</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr"/>
+          <t>Rather than memorising names, look at the picture: all the "acute-looking" angles are equal to each other, all the "obtuse-looking" ones are equal to each other, and one of each pair adds to 180°.</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>If one angle is 70°, then every angle in the figure is 70° or 110°. Angles around a point total 360°, and angles on a line total 180° — those two facts close most diagram questions.</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>For a fixed perimeter, regular is biggest</t>
+          <t>Sum of the interior angles of an `n`-sided polygon?</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Among all shapes with the same perimeter and the same number of sides, the regular one encloses the most area, and the further from regular the shape gets, the smaller its area. Pushing a square into a long thin rectangle keeps the perimeter but loses area fast.
-Across different numbers of sides the same logic continues: more sides means more area for the same perimeter, with the circle as the winner.</t>
+          <t>`(n - 2) x 180°`. For a **regular** polygon, divide that by `n` for one angle.</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Perimeter 40: a 10 x 10 square gives area 100; a 15 x 5 rectangle gives 75; a 19 x 1 rectangle gives 19. A circle with circumference 40 has radius `40/(2pi) ≈ 6.37` and area ≈ 127, beating every polygon.</t>
+          <t>Diagonals from a single vertex cut the polygon into `n - 2` triangles, each worth 180°.
+The formula also runs backwards: given the angle total, `n = total/180 + 2`. And for a *regular* polygon each interior angle is `180 - 360/n`, which is often the faster route.</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>This is about a *fixed perimeter*. Two shapes with the same area can have wildly different perimeters, and the comparison reverses.</t>
-        </is>
-      </c>
+          <t>Hexagon: `(6-2) x 180 = 720°`, so a regular hexagon has angles of `720/6 = 120°`. A pentagon totals 540°, giving 108° each.
+A polygon whose interior angles sum to 1,080° has `1080/180 + 2 = 8` sides. A regular decagon has angles of `180 - 36 = 144°`.</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>A regular hexagon inscribed in a circle</t>
+          <t>Sum of the exterior angles of any polygon?</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>For a regular hexagon inscribed in a circle, the side equals the radius: `s = r`. The hexagon splits into six equilateral triangles meeting at the centre, each with all sides equal to the radius.
-The pattern around it is worth knowing: with fewer sides the side is longer than the radius (a square gives `s = r sqrt(2)`), and with more sides the side is shorter.</t>
+          <t>Always **360°**, whatever the number of sides. For a regular polygon each exterior angle is `360/n`.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>A regular hexagon inscribed in a circle of radius 6 has sides of 6, perimeter 36, and area `6 x (sqrt(3) x 36/4) = 54sqrt(3) ≈ 93.5`. The circle's area is `36pi ≈ 113`, so the hexagon fills about 83% of it.</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr"/>
+          <t>Walking once round the polygon turns you through one full revolution, and at each corner you turn by the exterior angle.</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Regular hexagon: each exterior angle is `360/6 = 60°`, so each interior angle is `180 - 60 = 120°` ✓. If a regular polygon has exterior angles of 24°, it has `360/24 = 15` sides.
+A regular polygon with interior angles of 150° has exterior angles of 30°, so it has 12 sides.</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Cylinder volume and surface area</t>
+          <t>What makes a polygon regular?</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>`volume = pi r^2 h` — the circular base area times the height.
-`surface area = 2 pi r^2 + 2 pi r h` — the two circular ends plus the curved side, which unrolls into a rectangle of height `h` and width equal to the circumference `2 pi r`.</t>
+          <t>All sides equal **and** all angles equal. Both conditions are required.</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>A cylinder with radius 3 and height 10: volume `= pi x 9 x 10 = 90pi ≈ 283`. Surface area `= 2pi(9) + 2pi(3)(10) = 18pi + 60pi = 78pi ≈ 245`.</t>
+          <t>Regularity is what lets you divide the angle total by `n`, and it is the condition behind the maximum-area results later.
+For a regular polygon everything follows from `n`: each interior angle is `180 - 360/n`, each exterior angle is `360/n`, and the number of diagonals is `n(n-3)/2`.</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Doubling the radius quadruples the volume but doubling the height only doubles it — radius appears squared, so questions that change the radius have outsized effects.</t>
-        </is>
-      </c>
+          <t>A regular octagon has angles of 135°. A rhombus has equal sides but unequal angles; a rectangle has equal angles but unequal sides — neither is regular. Only the square is both.
+A hexagon has `6(3)/2 = 9` diagonals; a pentagon has 5.</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>For a fixed volume, regular means less surface area</t>
+          <t>The quadrilateral family — how do they nest?</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>The three-dimensional partner of the perimeter rule: for a given volume, the more regular (more compact) the solid, the smaller its surface area. Stretch a solid into a long thin shape and the surface area climbs while the volume stays put. The sphere is the extreme winner; among boxes, the cube is.</t>
+          <t>- **Parallelogram**: two pairs of parallel sides; opposite sides and angles equal; diagonals bisect each other.
+- **Rhombus**: parallelogram with four equal sides.
+- **Rectangle**: parallelogram with four right angles.
+- **Square**: both a rhombus and a rectangle.
+- **Trapezoid**: exactly one pair of parallel sides, so not a parallelogram.</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Volume 64: a 4 x 4 x 4 cube has surface area 96. A 16 x 2 x 2 box has the same volume but surface area `2(32 + 32 + 4) = 136`. A sphere of volume 64 has surface area about 77.</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr"/>
+          <t>The hierarchy answers "must be true" questions directly: every square is a rectangle, but most rectangles are not squares.</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>"A quadrilateral with four equal sides" could be a square or a non-square rhombus — ambiguous enough to make a comparison question answer D.</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>The longest diagonal of a shape</t>
+          <t>What does a trapezoid actually guarantee?</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>The longest diagonal joins the two furthest-apart points, which in a box means travelling across the width, the depth **and** the height at once — a corner to its diametrically opposite corner. It is the answer to "what is the longest rod that fits inside".</t>
+          <t>Only that the two angles on the same leg add to **180°**. All four sides and all four angles can otherwise be different.</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>In a rectangular room, the longest straight line is not along the floor but from one bottom corner up to the opposite top corner. A face diagonal of a 3 x 4 x 12 box is only 5, while the true longest diagonal is 13.</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr"/>
+          <t>Those co-interior angles are supplementary because the other two sides are parallel. Symmetry is not implied — only an *isosceles* trapezoid has equal legs and equal base angles, and the question must say so.</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>A base angle of 70° forces 110° directly above it on the same leg. The other leg could carry 50° and 130°, a completely different pair.</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Diagonal of a rectangular solid</t>
+          <t>Inscribed versus circumscribed?</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>`diagonal = sqrt(length^2 + width^2 + depth^2)`
-It is Pythagoras applied twice: once across the base to get the floor diagonal, then again vertically using that diagonal and the height.</t>
+          <t>**Inscribed** is drawn inside, **circumscribed** is drawn around — and in both cases every vertex of the inner shape must touch the outer shape.</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>A 3 x 4 x 12 box: `sqrt(9 + 16 + 144) = sqrt(169) = 13`. For a cube of side `s` the formula collapses to `s sqrt(3)`, so a cube of side 5 has longest diagonal `5sqrt(3) ≈ 8.66`.</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr"/>
+          <t>The touching condition is what turns the words into measurements: a square inscribed in a circle has its **diagonal** equal to the diameter; a circle inscribed in a square has its **diameter** equal to the side.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Square inscribed in a circle of radius 5: diagonal 10, so side `10/sqrt(2) = 5sqrt(2)` and area 50. Circle inscribed in a square of side 10: radius 5, area `25pi`.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Area, Volume &amp; Solids</t>
+          <t>Rotations, Angles &amp; Polygons</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Fitting boxes inside boxes</t>
+          <t>In a triangle, how do angles and opposite sides relate?</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>If the small box's dimensions divide exactly into the big box's, you may simply divide the volumes. If they do **not** divide exactly, that shortcut overcounts, because the leftover slivers cannot be reassembled. Instead work out how many fit along each dimension, round each down, and multiply.</t>
+          <t>Largest angle faces the longest side, smallest angle faces the shortest side — and the ordering works both ways.</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>How many 2 x 2 x 2 cubes fit in a 10 x 10 x 10 box? Everything divides evenly: `1000/8 = 125`, and `5 x 5 x 5 = 125` agrees. Now try 3 x 3 x 3 cubes in the same box: volume division suggests `1000/27 ≈ 37`, but per dimension you fit only `10/3 → 3`, so the true answer is `3 x 3 x 3 = 27`.</t>
+          <t>Knowing the order of the angles gives you the order of the sides for free, which is often all a comparison question needs.
+Two immediate corollaries: equal angles face equal sides (so an isosceles triangle's base angles are equal), and in a right triangle the hypotenuse is always the longest side because 90° is the largest angle.</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>You may also be allowed to rotate the small box. If the dimensions differ, test the orientations — one of them often fits noticeably more.</t>
-        </is>
-      </c>
+          <t>In a 30-60-90 triangle the shortest side faces the 30° and the hypotenuse faces the 90°. If `angle A &gt; angle B`, then side `a` (opposite A) is longer than side `b`.
+A triangle with angles 50°, 60°, 70° has its sides in that same order of size, so the side opposite the 50° is the shortest.</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Averages, Mixtures &amp; Spread</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Mixtures as weighted averages</t>
+          <t>Given two sides of a triangle, what can the third be?</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Mixing two solutions is a weighted average: the concentration of the result sits between the two originals, pulled toward whichever contributes more volume.
-If mixture A is `a%` strong with volume `x`, and mixture B is `b%` strong with volume `y`, the final concentration is
-`(ax + by)/(x + y)`
-The numerator is the total amount of the important substance; the denominator is the total volume.</t>
+          <t>Strictly between their **difference** and their **sum**: `|a - b| &lt; c &lt; a + b`. Any two sides must together exceed the third.</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>30 litres of 20% acid mixed with 10 litres of 60% acid: `(0.20 x 30 + 0.60 x 10)/40 = (6 + 6)/40 = 12/40 = 30%`. Note the answer is much closer to 20% than to 60%, because there is three times as much of the weak solution.</t>
+          <t>Applied to all three pairs, the triangle inequality pins the missing side into a range — and questions usually ask for the number of integer possibilities.</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>The result must always lie strictly between the two concentrations. If your answer falls outside that range, you have made an arithmetic slip.</t>
+          <t>Sides 7 and 10: `3 &lt; x &lt; 17`, so an integer third side has **13** possibilities (4 through 16).</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>The inequality is strict. Sides 3, 7 and 10 make a flat line, not a triangle.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Averages, Mixtures &amp; Spread</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>The mixture ratio shortcut</t>
+          <t>What proves two triangles congruent?</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>When you know the target concentration and need the **ratio** of the two mixtures, you do not need algebra. Take the distance from each starting concentration to the target, and swap them:
-`volume of A : volume of B = |z - b| : |z - a|`
-where `z` is the target. The mixture further from the target contributes less, so its distance becomes the *other* one's share.</t>
+          <t>**SSS**, **SAS** (angle *between* the sides), **ASA**, or **AAS**. Notably **SSA does not work** — two different triangles usually fit.</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Mix 20% acid with 60% acid to get 30%. Distances: from 20 to 30 is 10, from 60 to 30 is 30. Swapping gives `A : B = 30 : 10 = 3 : 1`. Check with the weighted average: `(0.2 x 3 + 0.6 x 1)/4 = 1.2/4 = 30%` ✓.</t>
+          <t>Congruent means identical in size and shape, so three well-chosen pieces pin it down. The exception matters: with two sides and a non-included angle, the third side can swing to two positions.</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Take care which distance goes with which mixture. The one nearer the target must get the larger share — sanity-check your ratio against that.</t>
-        </is>
-      </c>
+          <t>Two triangles with sides 5 and 7 and the 40° angle between them are congruent by SAS. With the 40° opposite the 5 instead, nothing is guaranteed.</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Averages, Mixtures &amp; Spread</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Median of an evenly spaced list</t>
+          <t>What do similar triangles give you?</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>For any evenly spaced list, the median equals the mean, and both equal the midpoint of the first and last terms:
-`median = (first + last)/2`
-You never have to count to the middle. This works for consecutive integers, consecutive multiples, or any arithmetic sequence.</t>
+          <t>Equal angles and all corresponding lengths in one fixed ratio. **Two** equal angles are enough to prove similarity. Lengths scale by `k`; **areas scale by `k^2`**.</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Median of the multiples of 7 between 50 and 200: the first is 56 and the last is 196, so the median is `(56 + 196)/2 = 126`. Median of the integers 1 to 100: `(1 + 100)/2 = 50.5`.</t>
+          <t>Similar means same shape, different scale — every length (sides, heights, perimeters) uses the same factor, but area uses its square. That squared factor is the part questions target.</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>This holds only when the spacing is even. For an arbitrary list you must sort it and find the middle value (or average the two middle values when the count is even).</t>
+          <t>Two triangles with angles 40-60-80; the first has its 40°-side of length 6, the second 9, a ratio of 3:2. If the first has area 20, the second has area `20 x (3/2)^2 = 45`, not 30.</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Match sides by the angles they face, not by the order they are written.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Averages, Mixtures &amp; Spread</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Quartiles and measures of position</t>
+          <t>Pythagorean theorem?</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Quartiles cut an ordered list into four parts: Q1 has a quarter of the data below it, Q2 is the median, Q3 has three quarters below it. The point that trips people up is that the quartile *values* are boundary markers, not members of the quarters — a value sitting exactly on Q1 is not counted inside the first or the second quarter.
-The same logic applies to deciles and percentiles: they are dividing lines, and a data point equal to the line belongs to neither side.</t>
+          <t>`a^2 + b^2 = c^2`, with `c` the hypotenuse — right triangles only.</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>For the list 1, 2, 3, 4, 5, 6, 7, 8 the median Q2 is 4.5 with four values each side; Q1 is 2.5 and Q3 is 6.5. So "how many values are in the third quarter" means those strictly between Q2 and Q3, namely 5 and 6.</t>
+          <t>It is also the converse: if the three sides satisfy it, the triangle *is* right-angled. And it is the engine behind the distance formula and the diagonal of a box.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Different textbooks compute quartiles slightly differently. On the GRE the interquartile range `Q3 - Q1` is what usually matters, and it is robust to those differences.</t>
+          <t>Legs 6 and 8: `36 + 64 = 100`, so `c = 10`. Backwards, hypotenuse 13 with one leg 5: `b^2 = 169 - 25 = 144`, so `b = 12`.</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>The hypotenuse is always the longest side and always faces the right angle. Plugging it in as a leg is the standard error.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Averages, Mixtures &amp; Spread</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Variance</t>
+          <t>The 30-60-90 triangle — side ratios?</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Variance measures how spread out a list is. Take each term's distance from the mean, square it so that positives and negatives do not cancel, add those up, and divide by how many terms there are.
-`variance = sum of (term - mean)^2 / N`
-Squaring is what makes outliers count heavily: a term twice as far from the mean contributes four times as much.</t>
+          <t>`1 : sqrt(3) : 2`. The short side (`x`) faces 30°, the hypotenuse (`2x`) faces 90°, the middle side (`x sqrt(3)`) faces 60°.</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>For 2, 4, 6 the mean is 4. Differences are -2, 0, 2; squares are 4, 0, 4; the total is 8; divide by 3 to get a variance of `8/3 ≈ 2.67`.</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr"/>
+          <t>It is half an equilateral triangle cut down the middle, which is also where the height of an equilateral triangle comes from.</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Hypotenuse 10 → short side 5, long leg `5sqrt(3) ≈ 8.66`. So an equilateral triangle of side 10 has height `5sqrt(3)`.</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Match sides to angles, not to their position in the picture. Given the **long leg** as 6, the short side is `6/sqrt(3) = 2sqrt(3)`, not 3.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Averages, Mixtures &amp; Spread</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Standard deviation step by step</t>
+          <t>The 45-45-90 triangle — side ratios?</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Standard deviation is the square root of the variance, which brings the measure back into the same units as the data. The procedure:
-1. Find the mean.
-2. Subtract the mean from each term.
-3. Square each difference.
-4. Add the squares.
-5. Divide by `N`.
-6. Take the square root.</t>
+          <t>`1 : 1 : sqrt(2)`. Two equal legs, hypotenuse `sqrt(2)` times as long.</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>For 2, 4, 6: mean 4; differences -2, 0, 2; squares 4, 0, 4; sum 8; divide by 3 → 2.67; square root → **1.63**. For 1, 4, 7 the same procedure gives `sqrt(6) ≈ 2.45` — the same mean but more spread, hence a larger SD.</t>
+          <t>It is a square cut along its diagonal, which is why a square of side `s` has diagonal `s sqrt(2)`.
+It appears whenever a square's diagonal shows up, and in isosceles right triangles hidden inside larger figures.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Most GRE questions only need you to *compare* standard deviations, which you can often do by eye: the list whose values sit further from the mean has the larger SD, regardless of the arithmetic.</t>
-        </is>
-      </c>
+          <t>Legs 5 → hypotenuse `5sqrt(2) ≈ 7.07`. Backwards: hypotenuse 10 → legs `10/sqrt(2) = 5sqrt(2)`. So a square with diagonal 10 has area 50.
+A square of side 8 has diagonal `8sqrt(2) ≈ 11.3`. A 45-45-90 triangle with hypotenuse `6sqrt(2)` has legs of 6 and area 18.</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Averages, Mixtures &amp; Spread</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Population versus sample standard deviation</t>
+          <t>A triangle with awkward angles like 30-105-45 — what do you do?</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>The two differ only in the divisor. Population SD divides by `N`; sample SD divides by `N - 1`. Dividing by a smaller number makes the sample SD slightly larger, which compensates for a sample tending to understate the spread of the population it came from.</t>
+          <t>Drop a perpendicular to split it into two special right triangles. 105° splits into 45 + 60; 75° splits into 45 + 30.</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>For 2, 4, 6 the population SD is `sqrt(8/3) ≈ 1.63` and the sample SD is `sqrt(8/2) = 2`. The GRE means population SD unless it explicitly says "sample".</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr"/>
+          <t>Once the figure is two known triangles you can use their ratios on both halves and add the areas. Look for angles that decompose into 30/45/60.</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>For 30-105-45 with one side given, the height from the 105° vertex creates a 30-60-90 and a 45-45-90 sharing that height. Find the height, use each ratio for its base piece, then add the two areas.</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>The perpendicular must land inside the triangle for the areas to add. In an obtuse triangle it may fall outside, and you subtract instead.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Averages, Mixtures &amp; Spread</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>What transformations do to standard deviation</t>
+          <t>Pythagorean triples worth recognising?</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Apply the same change to every term in a list and the spread reacts predictably. **Adding or subtracting** a constant shifts everything together and leaves the standard deviation unchanged. **Multiplying or dividing** by a constant scales the SD by that same factor (by its absolute value, since SD is never negative).
-The mean, by contrast, changes under both operations.</t>
+          <t>**3-4-5**, **5-12-13**, **8-15-17**, **7-24-25** — and every multiple of them (6-8-10, 9-12-15, …).</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>The list 2, 4, 6 has SD ≈ 1.63. Add 100 to each term to get 102, 104, 106: the SD is still 1.63, though the mean jumps from 4 to 104. Multiply the original by 3 to get 6, 12, 18: the SD triples to ≈ 4.90.</t>
+          <t>Recognition saves a square root, and recognising a near-miss saves you from assuming a right angle that is not there.</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Variance scales by the *square* of the factor, so multiplying by 3 multiplies the variance by 9 while multiplying the SD by 3.</t>
+          <t>Legs 8 and 15 → hypotenuse 17 instantly. Legs 9 and 12 → 15, since that is `3 x (3-4-5)`. But sides 5, 12 and 14 are **not** right-angled, however familiar the 5 and 12 look.</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>The largest number must be the hypotenuse.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Averages, Mixtures &amp; Spread</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Standardizing a list</t>
+          <t>Area of a triangle?</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Standardizing rewrites each value as the number of standard deviations it sits from the mean — its z-score. Two steps: subtract the mean from every value, then divide each result by the standard deviation. The new list always has mean 0 and standard deviation 1.
-`z = (value - mean)/SD`
-This is what lets you compare positions across different scales.</t>
+          <t>`area = (1/2) x base x height`, where the height is **perpendicular** to the chosen base.</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>The list 2, 8 has mean 5 and population SD 3. Standardized it becomes `(2-5)/3 = -1` and `(8-5)/3 = 1`, i.e. -1 and 1. So a score of 8 is "one standard deviation above the mean".</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr"/>
+          <t>Any side can be the base, as long as you use the height perpendicular to *that* side. In a right triangle the two legs are base and height already.</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Base 10, height 6 → area 30. A right triangle with legs 6 and 8 has area 24 (the hypotenuse never enters). Two triangles with the same base and the same height have equal areas, however different they look.</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>In an obtuse triangle the height can fall outside the triangle — it is still the perpendicular distance, not a side.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Averages, Mixtures &amp; Spread</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>The normal distribution percentages</t>
+          <t>Area and perimeter of a rectangle and a square?</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>The bell curve is symmetric about the mean, and the GRE expects you to know how the area splits. Within 1 SD of the mean lies about **68%** of the data (34% each side). The band between 1 and 2 SDs holds about **28%** (14% each side). Beyond 2 SDs lies about **4%** (2% each side).
-Cumulatively: about 68% within one SD, about 96% within two. Each half of the curve holds 50%, so `34 + 14 + 2 = 50` on each side — a useful check when you are reconstructing the picture.</t>
+          <t>Rectangle: `area = lw`, `perimeter = 2(l + w)`. Square of side `s`: `area = s^2`, `perimeter = 4s`, `diagonal = s sqrt(2)`.</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Test scores are normally distributed with mean 500 and SD 100. Between 400 and 600 lie 68% of scores. Above 700 (two SDs up) lie 2%. Between 600 and 700 lie 14%. And a score of 700 is at roughly the 98th percentile, since `50 + 34 + 14 = 98`.</t>
+          <t>The pairing that questions exploit: a fixed perimeter leaves the area free to vary wildly, and a fixed area leaves the perimeter free — the square is the extreme in both cases.</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Practise drawing the curve with 2 / 14 / 34 / 34 / 14 / 2 written under the sections. Almost every normal-distribution question is answered by reading numbers off that sketch.</t>
-        </is>
-      </c>
+          <t>Perimeter 40: a 10x10 square has area 100, a 15x5 rectangle 75, a 19x1 rectangle just 19. Conversely, area 36 can be a 6x6 square (perimeter 24) or a 36x1 rectangle (perimeter 74).</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Sets &amp; Counting</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Sets versus lists</t>
+          <t>Area of an equilateral triangle of side `s`?</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>A **set** is an unordered collection with no duplicates, written in braces `{2, 5, 9}`, and it may be infinite. Its size is written `|S|`. A **list** is ordered, may repeat values, and is always finite.
-The distinction decides which counting tool applies: questions about sets lead to combinations and inclusion–exclusion, questions about lists lead to permutations.</t>
+          <t>`(sqrt(3) x s^2)/4`.</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>`{1, 2, 3}` and `{3, 2, 1}` are the same set; the lists (1, 2, 3) and (3, 2, 1) are different. `{1, 1, 2}` is really just `{1, 2}` with two elements, whereas the list (1, 1, 2) genuinely has three entries.</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr"/>
+          <t>It follows from the 30-60-90 ratios: the height is `s sqrt(3)/2`, and area is half base times height.
+Because it depends on `s^2`, the ratio of the areas of two equilateral triangles is the square of the ratio of their sides. And six of them make a regular hexagon, which is how hexagon areas are computed.</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Side 6 → `(sqrt(3) x 36)/4 = 9sqrt(3) ≈ 15.6`. Doubling the side to 12 **quadruples** the area, since it depends on `s^2`.
+Given an area of `25sqrt(3)`, solve `(sqrt(3)s^2)/4 = 25sqrt(3)` → `s^2 = 100` → `s = 10`. A regular hexagon of side 10 then has area `6 x 25sqrt(3) = 150sqrt(3)`.</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Sets &amp; Counting</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Inclusion–exclusion for two sets</t>
+          <t>Area of a parallelogram?</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Add the two group sizes and subtract the overlap, which you have otherwise counted twice:
-`|A or B| = |A| + |B| - |A and B|`
-Rearranged, it also finds the overlap when you know the total, which is the more common exam form.</t>
+          <t>`base x height`, where the height is the **perpendicular** distance between the parallel sides — not the slanted side.</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>In a class of 30, 18 take French and 15 take Spanish, and everyone takes at least one. How many take both? `30 = 18 + 15 - both`, so `both = 3`. If instead 4 students took neither, the equation becomes `30 - 4 = 18 + 15 - both`, giving 7.</t>
+          <t>A parallelogram is a rectangle pushed over, and pushing it over changes neither base nor height.</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Read carefully whether the total includes people in *neither* group. Those have to be removed before the formula applies.</t>
+          <t>Base 10 with a slant side of 6 leaning at 30°: height `= 6 sin(30°) = 3`, so the area is **30**, not 60.</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Using the slanted side as the height always overestimates — it is the most common area error.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Sets &amp; Counting</t>
+          <t>Triangles &amp; Area</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Inclusion–exclusion for three sets</t>
+          <t>Area of a trapezoid?</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>With three groups the formula extends by adding back the triple overlap, which the pairwise subtractions removed once too often:
-`|A or B or C| = |A| + |B| + |C| - |A and B| - |B and C| - |A and C| + |A and B and C|`
-There is a second version, used when a question tells you how many are in **exactly** two groups rather than at least two:
-`total = |A| + |B| + |C| - (exactly two) - 2 x (all three)`
-Which one you need depends entirely on the wording, so identify that first.</t>
+          <t>`((base1 + base2)/2) x height` — the average of the parallel sides times the distance between them.</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>40 students, 20 play football, 18 basketball, 16 tennis, 8 play football and basketball, 6 basketball and tennis, 5 football and tennis, and 3 play all three. Then `20+18+16-8-6-5+3 = 38` play at least one, so 2 play none.</t>
+          <t>You are finding the width of the "average" rectangle. If the two bases were equal it would be a parallelogram, and the formula collapses to base times height.
+It also runs backwards to find a missing base or height, which is the usual exam form: substitute what you know and solve.</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>"8 play football and basketball" normally means *at least* those two, including anyone who also plays tennis. If the question says "only football and basketball", use the second formula.</t>
-        </is>
-      </c>
+          <t>Parallel sides 8 and 12, height 5 → `10 x 5 = 50`.
+A trapezoid of area 60 with bases 7 and 13 has height `60 = 10h`, so `h = 6`.</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Sets &amp; Counting</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>The multiplication principle</t>
+          <t>Circumference and area of a circle?</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>If one choice has `a` options and an independent second choice has `b` options, the pair has `a x b` possible outcomes. Extend it to as many stages as you like by multiplying them all together — this is the backbone of every counting question.</t>
+          <t>`circumference = 2 pi r = pi d`, `area = pi r^2`. Radius is half the diameter.</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>A menu with 4 starters and 3 mains offers `4 x 3 = 12` two-course meals. Add 2 desserts and it becomes `4 x 3 x 2 = 24`. Likewise a 4-digit PIN using digits 0-9 with repeats allowed has `10^4 = 10,000` possibilities.</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr"/>
+          <t>Nearly every circle question is "find `r` first". Whatever you are given — area, circumference, a chord, an inscribed square — convert it to the radius and the rest follows.
+Scaling: doubling the radius doubles the circumference but **quadruples** the area.</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Radius 6: circumference `12pi ≈ 37.7`, area `36pi ≈ 113`. Given an area of `49pi`, the radius is 7 and the circumference is `14pi`.</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Read whether you are given radius or diameter. Using `d` where the formula wants `r` doubles or quadruples the answer.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Sets &amp; Counting</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>AND means multiply, OR means add</t>
+          <t>Arc length and sector area for a central angle of `n` degrees?</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Decide whether the stages happen **together** or **instead** of each other. If both must happen (this *and* that), multiply. If exactly one happens (this *or* that, but not both), add the possibilities.
-Most complex counting questions are a tree of these two operations, so label each branch before computing.</t>
+          <t>Take that fraction of the whole circle:
+`arc = (n/360) x 2 pi r` and `sector area = (n/360) x pi r^2`.</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Travel from A to B by 3 roads then B to C by 4 roads: both legs are needed, so `3 x 4 = 12` routes. But if you can travel to C by one of 3 roads **or** by one of 4 different roads, that is `3 + 4 = 7` routes.</t>
+          <t>A sector is a slice of pizza: the central angle tells you what fraction of the full 360° you have, and both the boundary and the area scale by that same fraction.</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>If "or" allows both to happen, adding double-counts the overlap — go back to inclusion–exclusion.</t>
+          <t>Radius 6, central angle 60°: that is `1/6` of the circle, so the arc is `(1/6)(12pi) = 2pi` and the sector area is `(1/6)(36pi) = 6pi`. Backwards: an arc of `3pi` on a radius-6 circle is `3pi/12pi = 1/4` of the circle, so the angle is 90°.</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Arc length is a distance and sector area is an area — do not use one where the other is asked.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Sets &amp; Counting</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Optional choices, and "at least one"</t>
+          <t>Inscribed angles, and the angle in a semicircle?</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Something that may be taken or left is a two-way choice: in or out. Give every optional item a factor of 2 and multiply as usual. For `n` optional extras that is `2^n` combinations, including the case where you take none.
-To enforce "at least one", count everything and subtract the single case where nothing was chosen.</t>
+          <t>An inscribed angle is **half** the central angle standing on the same arc. So an angle inscribed in a semicircle (standing on a diameter) is always **90°**.</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>4 ice-cream flavours and 4 optional toppings: `4 x 2 x 2 x 2 x 2 = 64` combinations. If at least one topping is compulsory, remove the 4 no-topping cases: `64 - 4 = 60`.</t>
+          <t>The semicircle case is the one the GRE uses most: any triangle with the diameter as one side and its third vertex on the circle is right-angled at that vertex.</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>This "count all, subtract the bad case" move is the standard answer to any "at least one" question, and it is almost always faster than counting the good cases directly.</t>
-        </is>
-      </c>
+          <t>A central angle of 80° gives an inscribed angle of 40° on the same arc. And if `AB` is a diameter and `C` is anywhere else on the circle, `angle ACB = 90°`, so `AC^2 + BC^2 = AB^2`.</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Sets &amp; Counting</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Combinations: choosing r from n</t>
+          <t>Area of a regular polygon?</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>When order does **not** matter, the number of ways to choose `r` items from `n` is
-`nCr = n!/(r!(n - r)!)`
-The `r!` on the bottom divides out all the orderings of the same chosen group, which is exactly what "order does not matter" means.</t>
+          <t>`area = (n x s x a)/2`, where `a` is the **apothem** — the perpendicular distance from the centre to the middle of a side. Since `n x s` is the perimeter, this is "half perimeter times apothem".</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>How many 3-person committees from 10 people? `10C3 = 10!/(3!7!) = (10 x 9 x 8)/(3 x 2 x 1) = 120`. Note the useful symmetry `nCr = nC(n-r)`: choosing 3 to include is the same as choosing 7 to exclude.</t>
+          <t>The polygon splits into `n` identical triangles, each with base `s` and height `a`.</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>The giveaway word is "committee", "group", "handshake" or "selection" — anything where swapping two members changes nothing.</t>
-        </is>
-      </c>
+          <t>Regular hexagon of side 6: apothem `3sqrt(3) ≈ 5.196`, so area `= (6 x 6 x 5.196)/2 ≈ 93.5`. Cross-check with six equilateral triangles: `6 x 9sqrt(3) = 54sqrt(3) ≈ 93.5` ✓.</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Sets &amp; Counting</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Permutations: arranging r from n</t>
+          <t>A regular hexagon inscribed in a circle — how do side and radius compare?</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>When order **does** matter, the count is
-`nPr = n!/(n - r)!`
-It is the combination count times `r!`, since each chosen group can be arranged in `r!` ways.</t>
+          <t>`s = r`, exactly. Fewer sides → `s &gt; r` (a square gives `s = r sqrt(2)`); more sides → `s &lt; r`.</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>How many ways to award gold, silver and bronze among 10 runners? `10P3 = 10!/7! = 10 x 9 x 8 = 720`, six times the 120 committees above — because each group of three can be arranged on the podium in `3! = 6` ways.</t>
+          <t>The hexagon splits into six equilateral triangles meeting at the centre, each with every side equal to the radius.
+It makes several figures computable at a glance: the hexagon's perimeter is `6r`, its area is six equilateral triangles of side `r`, and its longest diagonal is the circle's diameter `2r`.</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Words like "ranking", "order", "podium", "president and treasurer" or "password" signal permutations.</t>
-        </is>
-      </c>
+          <t>Hexagon in a circle of radius 6: sides 6, perimeter 36, area `54sqrt(3) ≈ 93.5`. The circle's area is `36pi ≈ 113`, so the hexagon fills about 83% of it.</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Sets &amp; Counting</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Permutations by the slot method</t>
+          <t>Same perimeter, different shapes — which has the most area?</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Rather than recall the formula, draw a blank for each position and fill in how many options it has, then multiply. Each item used up reduces the choices for the next slot by one.</t>
+          <t>The most **regular** one, and the further from regular, the less area. Across different side counts, more sides is better, with the circle the overall winner.</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>How many ways to arrange the letters of ABCDE? Five slots: `5 x 4 x 3 x 2 x 1 = 120`, which matches `5P5 = 5!/0! = 120`. Choosing only the first three letters: `5 x 4 x 3 = 60 = 5P3`.</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr"/>
+          <t>Stretching a shape while keeping its perimeter loses area fast, which is what makes these comparison questions answerable without computing anything.</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Perimeter 40: a 10x10 square gives 100, a 15x5 rectangle 75, a 19x1 rectangle 19. A circle of circumference 40 has area ≈127, beating every polygon.</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>This is about a **fixed perimeter**. With a fixed area the comparison reverses.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Sets &amp; Counting</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Permutations with restrictions</t>
+          <t>Volume and surface area of a rectangular solid and a cube?</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Handle the restricted positions first, then fill in the rest with the slot method. If a restriction splits into separate scenarios, count each scenario fully and **add** them; if the restrictions apply simultaneously, **multiply** the stage counts.
-Two standard tricks: to keep items together, glue them into one block and arrange the blocks (then multiply by the arrangements inside the block); to keep items apart, count everything and subtract the arrangements where they are together.</t>
+          <t>Box: `volume = lwh`, `surface area = 2(lw + lh + wh)`. Cube of side `s`: `volume = s^3`, `surface area = 6s^2`.</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>How many 4-digit numbers can be made from 1-7 with no repeats if the number must be even? The last slot must be 2, 4 or 6 → 3 options; the remaining three slots take any of the leftover 6 digits: `6 x 5 x 4 = 120`. Total `3 x 120 = 360`.</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr"/>
+          <t>A box has three pairs of identical faces, which is where the 2 and the three products come from. For a cube all six faces match.
+Scaling: double every edge and the volume goes up **8 times**, the surface area **4 times**.</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>A 3x4x5 box: volume 60, surface area `2(12 + 15 + 20) = 94`. A cube of side 4: volume 64, surface area 96.</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Advanced Counting &amp; Probability</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Arrangements with repeated items</t>
+          <t>Volume and surface area of a cylinder?</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Arranging `n` items where some are identical gives fewer distinct results than `n!`, because swapping two identical items changes nothing. Divide by the factorial of each repeat count:
-`arrangements = n!/(a! b! ...)`
-where `a`, `b`, … are how many times each repeated item appears.</t>
+          <t>`volume = pi r^2 h`. `surface area = 2 pi r^2 + 2 pi r h` — two circular ends plus the curved side.</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>How many arrangements of the letters in BANANA? `n = 6`, with three As and two Ns, so `6!/(3! 2!) = 720/12 = 60`. For a word with no repeats, like ABCDEF, the division disappears and you get the full `6! = 720`.</t>
+          <t>The curved side unrolls into a rectangle of height `h` and width equal to the circumference `2 pi r`, which is where the second term comes from.</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Divide by the factorial of each repeat *separately*; do not add the repeat counts together first. Three As and two Ns means `3! x 2! = 12`, not `5! = 120`.</t>
+          <t>Radius 3, height 10: volume `= 90pi ≈ 283`; surface area `= 18pi + 60pi = 78pi ≈ 245`.</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Radius appears squared in the volume, so changing it has an outsized effect: doubling `r` quadruples the volume, while doubling `h` only doubles it.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Advanced Counting &amp; Probability</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Repeats plus restrictions</t>
+          <t>Same volume, different shapes — which has the least surface area?</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Combine the two ideas: split the problem into the sections the restriction creates, count each with the repeats formula, then multiply the sections together (or add, if they are alternative scenarios).</t>
+          <t>The most **regular** one. Elongate a solid and the surface area climbs while the volume stays put. The sphere wins overall; among boxes, the cube.</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>How many arrangements of TEXTBOOK have all vowels first and all consonants last? The vowels are E, O, O → `3!/2! = 3` arrangements. The consonants are T, X, T, B, K → `5!/2! = 60`. The two blocks are both required, so multiply: `3 x 60 = 180`.</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr"/>
+          <t>The three-dimensional partner of the perimeter rule, and it is tested the same way — as a comparison you answer by reasoning, not calculating.</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Volume 64: a 4x4x4 cube has surface area 96; a 16x2x2 box has the same volume but surface area `2(32 + 32 + 4) = 136`. A sphere of volume 64 has about 77.</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Advanced Counting &amp; Probability</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Turning a word problem into a counting problem</t>
+          <t>What is the longest straight line that fits inside a box?</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Most counting questions are one of the standard types wearing a disguise. Before calculating, answer three questions: how many items are there, how many are being chosen or arranged, and does order matter? Add a fourth if needed: are repeats allowed?
-Order matters → permutation. Order does not → combination. Repeats allowed → plain multiplication (`n^r`). Identical items in a fixed arrangement → divide by the repeat factorials.</t>
+          <t>The **space diagonal** — corner to diametrically opposite corner, crossing length, width and height at once. Not a face diagonal.</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>"How many ways can 5 books be placed on a shelf if 2 are identical?" Items: 5, all being arranged, order matters, with one repeat of 2 → `5!/2! = 60`. "How many 3-topping pizzas from 8 toppings?" Choosing 3 of 8, order irrelevant, no repeats → `8C3 = 56`.</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr"/>
+          <t>This is the "longest rod that fits" question. The two furthest-apart points of a box are opposite corners, so both the width and the depth get "diagonalled".</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>In a room, the longest line runs from a bottom corner to the opposite top corner. In a 3x4x12 box the best face diagonal is only 5, while the true longest is 13.</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Advanced Counting &amp; Probability</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Circular arrangements</t>
+          <t>Formula for the diagonal of a rectangular solid?</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Seating `n` people around a circle gives `(n - 1)!` arrangements rather than `n!`. A circle has no fixed starting point, so rotating everyone by one seat produces the same arrangement — which means each distinct seating has been counted `n` times, and `n!/n = (n - 1)!`.
-The practical method: fix one person in place, then arrange the remaining `n - 1` around them.</t>
+          <t>`d = sqrt(l^2 + w^2 + h^2)`. For a cube of side `s` it collapses to `s sqrt(3)`.</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>5 people in a row: `5! = 120`. The same 5 around a round table: `4! = 24`. If the seats are numbered — or if the arrangement can be flipped over, as with a bracelet — the count changes again, so read the question carefully.</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr"/>
+          <t>Pythagoras applied twice: once across the base to get the floor diagonal, then again vertically using that diagonal and the height.
+It is also the 3-D distance formula: the diagonal is the distance between opposite corners, exactly as `sqrt(dx^2 + dy^2 + dz^2)` measures distance in space.</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>3x4x12 box: `sqrt(9 + 16 + 144) = sqrt(169) = 13`. Cube of side 5: `5sqrt(3) ≈ 8.66`.
+A 6x6x7 box: `sqrt(36 + 36 + 49) = sqrt(121) = 11`. And "will a 12-inch rod fit in a 4x6x9 box?" → `sqrt(16+36+81) = sqrt(133) ≈ 11.5`, so no.</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Advanced Counting &amp; Probability</t>
+          <t>Circles &amp; Solids</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>When is nCr largest?</t>
+          <t>How many small boxes fit inside a big one?</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>For a fixed `n`, the number of combinations peaks when `r` is half of `n`. Choosing about half the items gives the most possible groups, and the counts fall away symmetrically toward `r = 0` and `r = n`, which each have exactly one.
-If `n` is odd there is no exact half, so two neighbouring values of `r` tie for the maximum.</t>
+          <t>Divide **per dimension** and round each down, then multiply. Dividing the volumes only works when every dimension divides exactly.</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>With `n = 6`, the counts run 1, 6, 15, 20, 15, 6, 1 — the maximum is 20 at `r = 3`. With `n = 7` they run 1, 7, 21, 35, 35, 21, 7, 1, so `r = 3` and `r = 4` tie at 35.</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr"/>
+          <t>Volume division silently assumes the leftover slivers can be reassembled, which they cannot.</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>2x2x2 cubes into a 10x10x10 box: everything divides, so `1000/8 = 125`, matching `5 x 5 x 5`. But 3x3x3 cubes: volume division suggests 37, while per dimension you fit `10/3 → 3`, giving `3 x 3 x 3 = 27`.</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>You may be allowed to rotate the small box. When the dimensions differ, test the orientations — one often fits noticeably more.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Advanced Counting &amp; Probability</t>
+          <t>Statistics &amp; Data</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Probability that both A and B happen</t>
+          <t>Mixing two solutions — what is the concentration of the result?</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>For **independent** events — where one happening does not change the odds of the other — multiply:
-`P(A and B) = P(A) x P(B)`
-If the events are not independent, use the conditional version `P(A) x P(B given A)`.</t>
+          <t>A weighted average: `(ax + by)/(x + y)`, where mixture A is `a%` strong with volume `x` and B is `b%` with volume `y`.</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Two fair coin flips both landing heads: `1/2 x 1/2 = 1/4`. But drawing two aces from a deck *without replacement* is not independent: `4/52 x 3/51 = 1/221`, not `(4/52)^2`.</t>
+          <t>The numerator is the total amount of the important substance, the denominator the total volume. The result is pulled toward whichever mixture contributes more volume.</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>"Without replacement" is the flag for dependence. The second probability must account for what the first draw removed.</t>
+          <t>30 litres of 20% acid with 10 litres of 60%: `(6 + 6)/40 = 30%`. Much closer to 20% than 60%, because there is three times as much of the weak one.</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>The answer must lie strictly **between** the two concentrations. Outside that range means an arithmetic slip.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Advanced Counting &amp; Probability</t>
+          <t>Statistics &amp; Data</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Probability that A or B happens</t>
+          <t>What ratio of two mixtures gives a target concentration?</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>`P(A or B) = P(A) + P(B) - P(A and B)`. It is inclusion–exclusion again: adding the two probabilities double-counts the outcomes where both occur, so subtract that overlap once.</t>
+          <t>Alligation: take each mixture's distance from the target and **swap them**. `A : B = |z - b| : |z - a|`.</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Rolling a die, `P(even) = 3/6` and `P(greater than 3) = 3/6`. The overlap (4 or 6) is `2/6`. So `P(even or greater than 3) = 3/6 + 3/6 - 2/6 = 4/6 = 2/3` — matching the list 2, 4, 5, 6.</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr"/>
+          <t>The mixture further from the target contributes less, so its distance becomes the *other* one's share. No algebra needed.</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Mix 20% and 60% acid to get 30%. Distances 10 and 30, swapped gives `A : B = 30 : 10 = 3 : 1`. Check: `(0.2 x 3 + 0.6 x 1)/4 = 30%` ✓.</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Sanity-check which way round it goes: the mixture **nearer** the target must get the larger share.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Advanced Counting &amp; Probability</t>
+          <t>Statistics &amp; Data</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Independent versus mutually exclusive</t>
+          <t>Quartiles — what exactly is Q1, and what sits "inside" a quarter?</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>These sound similar and mean opposite things. **Independent** events do not affect each other's chances, so `P(A and B) = P(A) x P(B)`. **Mutually exclusive** events cannot both happen, so `P(A and B) = 0` and `P(A or B) = P(A) + P(B)`.
-A consequence worth remembering: for mutually exclusive events `P(A) + P(B) &lt;= 1`, because probabilities summing past 1 would force an overlap.</t>
+          <t>Quartiles cut an ordered list into four parts: Q1 has a quarter below it, Q2 is the median, Q3 has three quarters below. The quartile **values are boundaries, not members** — a value sitting exactly on Q1 belongs to neither neighbouring quarter.</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Two coin flips are independent (both can be heads). Drawing one card that is both a king and a queen is mutually exclusive. Note that two events with non-zero probability cannot be both independent and mutually exclusive — if they cannot co-occur, knowing one happened tells you a great deal about the other.</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr"/>
+          <t>The same holds for deciles and percentiles: they are dividing lines. The interquartile range `Q3 - Q1` is what the GRE usually wants, and it is robust to the small definitional differences between textbooks.</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>For 1, 2, 3, 4, 5, 6, 7, 8: Q2 = 4.5, Q1 = 2.5, Q3 = 6.5, so the interquartile range is 4. "The third quarter" means the values strictly between Q2 and Q3 — 5 and 6.</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Advanced Counting &amp; Probability</t>
+          <t>Statistics &amp; Data</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Conditional probability</t>
+          <t>Variance — how is it built?</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>`P(A | B) = P(A and B)/P(B)` — the chance of A *given that* B has happened. Conditioning on B shrinks the world to just the outcomes where B occurred, so you re-scale by dividing by `P(B)`.</t>
+          <t>`variance = sum of (term - mean)^2 / N`. Distance from the mean, squared, averaged.</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Roll a die; what is the probability it is a 2 given that it is even? `P(2 and even) = 1/6`, `P(even) = 1/2`, so `P(2 | even) = (1/6)/(1/2) = 1/3`. That matches intuition: among 2, 4, 6, one of the three is a 2.</t>
+          <t>Squaring stops positives and negatives cancelling, and it makes outliers count heavily — a term twice as far from the mean contributes four times as much.
+Variance is in *squared* units, which is why standard deviation — its square root — is the figure actually quoted. A variance of 0 means every value is identical.</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>`P(A | B)` and `P(B | A)` are different numbers. The probability of being even given a roll of 2 is 1, not 1/3.</t>
-        </is>
-      </c>
+          <t>For 2, 4, 6: mean 4; differences -2, 0, 2; squares 4, 0, 4; total 8; `8/3 ≈ 2.67`.
+For 10, 10, 10 the variance is 0. For 8, 10, 12 the mean is 10, the squared differences are 4, 0, 4, and the variance is 8/3 — the same as for 2, 4, 6, since only the spread matters, not the location.</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Statistics &amp; Data</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Standard deviation — the procedure?</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>The square root of the variance: (1) find the mean, (2) subtract it from each term, (3) square the differences, (4) add them, (5) divide by `N`, (6) square root.</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Taking the root brings the measure back into the units of the data, which is why SD rather than variance is what questions quote.</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>2, 4, 6 → variance 2.67 → SD ≈ **1.63**. The list 1, 4, 7 has the same mean but more spread, giving `sqrt(6) ≈ 2.45`.</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Most GRE questions only ask you to **compare** SDs, which you can often do by eye: the list whose values sit further from the mean wins, no arithmetic needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Statistics &amp; Data</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Population versus sample standard deviation?</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Population divides by `N`; sample divides by `N - 1`. The sample version is slightly larger.</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Dividing by a smaller number compensates for a sample tending to understate the spread of the population it came from. The GRE means population SD unless it says "sample".
+The intuition for `N - 1`: a sample's own mean sits closer to its points than the true population mean does, so the squared differences come out slightly too small, and the smaller divisor corrects for it.</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>For 2, 4, 6: population SD `= sqrt(8/3) ≈ 1.63`; sample SD `= sqrt(8/2) = 2`.
+The gap shrinks as the sample grows: with `N = 100` the two divisors differ by 1%, which is why the distinction rarely changes a comparison answer.</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Statistics &amp; Data</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Add 10 to every value, or multiply every value by 3 — what happens to the SD?</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Adding or subtracting a constant: **no change**. Multiplying or dividing: the SD is multiplied or divided by the same factor.</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Adding shifts the whole list without changing the gaps; multiplying stretches the gaps. The mean, by contrast, changes under both.</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>2, 4, 6 has SD ≈ 1.63. Adding 100 gives 102, 104, 106 — SD still 1.63, mean now 104. Multiplying by 3 gives 6, 12, 18 — SD ≈ 4.90.</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Variance scales by the **square** of the factor: multiplying the list by 3 multiplies the variance by 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Statistics &amp; Data</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Standardizing a list (z-scores)?</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>`z = (value - mean)/SD`. Subtract the mean from every value, then divide by the SD. The new list always has mean 0 and SD 1.</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>A z-score says how many standard deviations a value sits from the mean, which is what lets you compare positions across different scales.</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>The list 2, 8 has mean 5 and population SD 3, so it standardizes to -1 and 1. A score of 8 is "one standard deviation above the mean".</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Statistics &amp; Data</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>The normal distribution — what percentages should you be able to draw?</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>**2 / 14 / 34 / 34 / 14 / 2**. So about 68% lies within 1 SD of the mean, about 96% within 2 SDs, and about 4% beyond 2 SDs.</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>The curve is symmetric, so each half holds 50%: `34 + 14 + 2 = 50` is the check you use when reconstructing the sketch from memory.</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Scores are normal with mean 500, SD 100. Between 400 and 600: 68%. Above 700: 2%. Between 600 and 700: 14%. A score of 700 is roughly the 98th percentile, since `50 + 34 + 14 = 98`.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Draw the curve and write the six numbers under it before answering. Almost every normal-distribution question is then just reading off the sketch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Statistics &amp; Data</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Data interpretation questions — what should you do before calculating?</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Read the **axes, units and footnotes** first: what exactly is being measured, in what units, and is the chart showing an amount or a percentage of something.</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>The arithmetic in a DI set is easy; the traps are in the reading. Percentages of different bases cannot be added or compared directly, and "percent" versus "percentage points" are different questions.
+A set of questions shares one chart, so the time spent understanding it pays back three times. Estimate first — answer choices are usually far apart.</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>A bar chart shows revenue in **thousands** and a pie chart shows each region's **share**. "Which region grew most?" is about the bars; "which had the largest share?" is about the pie — and a region can gain share while its revenue falls, if the total fell faster.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>A percentage increase from 5% to 10% is a rise of 5 percentage **points** but a 100% **increase**.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Set versus list — what is the difference?</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>A **set** is unordered with no duplicates, written `{2, 5, 9}`, and can be infinite; its size is `|S|`. A **list** is ordered, allows duplicates, and is finite.</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>The distinction decides which tool applies: sets lead to combinations and inclusion–exclusion, lists lead to permutations.</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>`{1, 2, 3}` and `{3, 2, 1}` are the same set, but the lists (1, 2, 3) and (3, 2, 1) differ. `{1, 1, 2}` is just `{1, 2}` with two elements, while the list (1, 1, 2) has three entries.</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Inclusion–exclusion for two groups?</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>`|A or B| = |A| + |B| - |A and B|` — add the two, subtract the overlap you counted twice.</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>The rearranged form is the one exams use: knowing the total and both groups gives you the overlap.</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>30 students, 18 take French, 15 Spanish, everyone takes at least one. `30 = 18 + 15 - both` → **3** take both. If 4 took neither, use `30 - 4 = 18 + 15 - both` → 7.</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Check whether the total includes people in **neither** group — remove them before applying the formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Inclusion–exclusion for three groups?</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>`|A or B or C| = |A| + |B| + |C| - |A and B| - |B and C| - |A and C| + |A and B and C|`
+If instead you are told how many are in **exactly** two groups:
+`total = |A| + |B| + |C| - (exactly two) - 2 x (all three)`</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>The pairwise subtractions remove the triple overlap once too often, so the standard version adds it back. Which formula you need depends entirely on the wording, so settle that first.</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>40 students: 20 football, 18 basketball, 16 tennis, 8 football+basketball, 6 basketball+tennis, 5 football+tennis, 3 all three. `20+18+16-8-6-5+3 = 38` play at least one, so 2 play none.</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>"8 play football and basketball" normally means *at least* those two, including anyone who also plays tennis. "Only football and basketball" is the other formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Several independent choices in a row — how many outcomes?</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Multiply the options at each stage: `a x b x c ...`</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>The multiplication principle is the backbone of every counting question; extend it to as many stages as you like.
+It also covers repeats: choosing from `n` options `r` times **with** repetition gives `n^r`, because every stage still has all `n` options available.</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>4 starters and 3 mains → 12 meals; add 2 desserts → 24. A 4-digit PIN from 10 digits with repeats allowed → `10^4 = 10,000`.
+A 3-letter code from 26 letters with repeats allowed: `26^3 = 17,576`. Without repeats: `26 x 25 x 24 = 15,600`.</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>When do you add possibilities, and when do you multiply?</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>**AND → multiply** (both stages happen). **OR → add** (one or the other, not both).</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Label each branch of the problem before computing; most complex counting questions are just a tree of these two operations.</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>A to B by 3 roads then B to C by 4 roads: both legs needed → `3 x 4 = 12` routes. But if you may go to C by one of 3 roads **or** one of 4 others → `3 + 4 = 7`.</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>If "or" allows both to happen, adding double-counts — go back to inclusion–exclusion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Optional extras, and "at least one" — how do you count them?</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Each optional item is a two-way choice (in or out), so `n` options give `2^n` combinations. For "at least one", count everything and **subtract the case where nothing was chosen**.</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Count-all-then-subtract-the-bad-case is the standard move for "at least" questions, and it is almost always faster than counting the good cases.</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>4 ice-cream flavours with 4 optional toppings: `4 x 2 x 2 x 2 x 2 = 64`. If at least one topping is compulsory, remove the 4 no-topping cases: **60**.</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Choosing `r` from `n` where order does **not** matter?</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>`nCr = n!/(r!(n - r)!)`</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>The `r!` divides out the orderings of the same chosen group — which is exactly what "order does not matter" means. Note the symmetry `nCr = nC(n-r)`: choosing 3 to include is choosing 7 to exclude.</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>3-person committees from 10 people: `10C3 = (10 x 9 x 8)/(3 x 2 x 1) = 120`.</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>The giveaway words are committee, group, handshake, selection — anything where swapping two members changes nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Choosing `r` from `n` where order **does** matter?</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>`nPr = n!/(n - r)!` — which is `nCr` times `r!`.</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Each chosen group can be arranged in `r!` ways, so permutations always outnumber combinations by that factor.
+The relationship is worth holding onto: `nPr = nCr x r!`. Whenever you can count the groups, multiply by `r!` to get the ordered count.</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Gold, silver, bronze among 10 runners: `10P3 = 10 x 9 x 8 = 720`, six times the 120 committees, because each trio can stand on the podium in `3! = 6` orders.
+Arranging 2 of 5 books on a shelf: `5P2 = 20`. Choosing 2 of 5 to take on holiday: `5C2 = 10` — exactly half, since each pair has `2! = 2` orders.</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Ranking, order, podium, "president and treasurer", password → permutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Counting arrangements without any formula?</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>The **slot method**: draw a blank for each position, write how many options it has, multiply. Each item used reduces the next slot by one.</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>It is the formula in disguise, but far harder to misapply — and it extends naturally to restricted positions.
+The slot method is also the only practical approach once restrictions appear, because you can fill the constrained slots first and let the rest follow.</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Arranging ABCDE: `5 x 4 x 3 x 2 x 1 = 120`, matching `5P5`. Taking only the first three letters: `5 x 4 x 3 = 60 = 5P3`.
+How many 3-digit numbers have no repeated digits? The first slot cannot be 0, so `9 x 9 x 8 = 648`.</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Arrangements with a restriction on some positions?</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Fill the **restricted slots first**, then the rest by the slot method. Separate scenarios are **added**; simultaneous stages are **multiplied**.</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Two standard tricks: to keep items **together**, glue them into one block and arrange the blocks (then multiply by the arrangements inside the block); to keep items **apart**, count everything and subtract the arrangements where they are together.</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>4-digit numbers from 1–7, no repeats, must be even. The last slot must be 2, 4 or 6 → 3 options; the other three slots take the remaining digits → `6 x 5 x 4 = 120`. Total `3 x 120 = 360`.</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Sets &amp; Counting</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Arranging `n` items when some are identical?</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>`n!/(a! b! ...)`, dividing by the factorial of each repeat count.</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Swapping two identical items produces no new arrangement, so the plain `n!` overcounts by exactly those internal orderings.</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>BANANA: `n = 6` with three As and two Ns → `6!/(3! 2!) = 720/12 = 60`. A word with no repeats, like ABCDEF, keeps the full `6! = 720`.</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Divide by each repeat's factorial **separately**: three As and two Ns means `3! x 2! = 12`, not `5!`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>Advanced Counting &amp; Probability</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>"At least one" via the complement</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>Questions asking for the probability of "at least one" are almost always faster backwards: compute the probability that it never happens and subtract from 1.
-`P(at least one) = 1 - P(none)`
-Counting the direct way means adding the cases for exactly one, exactly two, exactly three … whereas the complement is a single multiplication.</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>Flip a coin 4 times; what is the probability of at least one head? `P(no heads) = (1/2)^4 = 1/16`, so the answer is `15/16`. The direct route would have needed four separate cases.</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>The complement of "at least one" is "none", not "exactly one". Likewise the complement of "at least two" is "zero or one" — both of which you must subtract.</t>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Counting Strategy &amp; Probability</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Repeats **and** restrictions together?</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Split the problem into the sections the restriction creates, count each with the repeats formula, then multiply the sections (or add, if they are alternatives).</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Handle one constraint at a time and the hardest-looking counting questions become two small ones.</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Arrangements of TEXTBOOK with all vowels first and all consonants last. Vowels E, O, O → `3!/2! = 3`. Consonants T, X, T, B, K → `5!/2! = 60`. Both blocks are required, so `3 x 60 = 180`.</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Counting Strategy &amp; Probability</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>An unfamiliar counting question — what do you ask yourself first?</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Three questions: **how many items**, **how many are being chosen or arranged**, and **does order matter**? Then a fourth: are repeats allowed?
+Order matters → permutation. Order does not → combination. Repeats allowed → plain multiplication (`n^r`). Identical items → divide by the repeat factorials.</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Nearly every counting question is one of the standard types in disguise. Answering those three questions names the type, and then the formula is mechanical.</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>"5 books on a shelf, 2 identical" → arranging 5, order matters, one repeat of 2 → `5!/2! = 60`. "3-topping pizzas from 8 toppings" → choosing 3 of 8, order irrelevant → `8C3 = 56`.</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Counting Strategy &amp; Probability</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Seating `n` people around a **circular** table?</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>`(n - 1)!`, not `n!`.</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>A circle has no fixed starting point, so rotating everyone one seat gives the same arrangement — each distinct seating was counted `n` times, and `n!/n = (n-1)!`. In practice: fix one person, then arrange the rest around them.</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>5 people in a row: `5! = 120`. The same 5 around a table: `4! = 24`.</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Numbered seats make it a row again, and a flippable arrangement (a bracelet) halves the count. Read the setup carefully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Counting Strategy &amp; Probability</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>For a fixed `n`, which `r` makes `nCr` largest?</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>`r = n/2`. If `n` is odd, the two values either side of the middle tie.</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Choosing about half the items gives the most possible groups; the counts fall away symmetrically toward `r = 0` and `r = n`, which each have exactly one.</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>`n = 6`: counts run 1, 6, 15, **20**, 15, 6, 1 — maximum at `r = 3`. `n = 7`: 1, 7, 21, **35**, **35**, 21, 7, 1 — `r = 3` and `r = 4` tie.</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Counting Strategy &amp; Probability</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Basic probability of an event?</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>`P(E) = favourable outcomes / total outcomes`, always between 0 and 1. All the outcomes you count must be **equally likely**.</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Most probability questions are really counting questions wearing a hat — build the numerator and denominator with the counting tools you already have.
+`P(not E) = 1 - P(E)` is the other half of the toolkit.</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>One card from a deck: `P(king) = 4/52 = 1/13`. Two dice: `P(sum of 7) = 6/36 = 1/6`, since 6 of the 36 equally likely pairs total 7. Choosing 2 people from 10 of whom 4 are women, `P(both women) = 4C2 / 10C2 = 6/45 = 2/15`.</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Equally likely matters. The sums of two dice are **not** equally likely — 7 comes up six times as often as 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Counting Strategy &amp; Probability</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Probability that A **and** B both happen?</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>For **independent** events, `P(A and B) = P(A) x P(B)`. If they are not independent, use `P(A) x P(B given A)`.</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Independence means one event does not change the odds of the other. "Without replacement" is the standard flag that it fails.
+For three or more independent events, keep multiplying. For dependent ones, each factor is conditioned on everything before it.</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Two coin flips both heads: `1/2 x 1/2 = 1/4`. Two aces drawn without replacement: `4/52 x 3/51 = 1/221`, **not** `(4/52)^2`.
+Three heads in a row: `(1/2)^3 = 1/8`. Three aces without replacement: `4/52 x 3/51 x 2/50 = 1/5,525`.</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Counting Strategy &amp; Probability</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Probability that A **or** B happens?</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>`P(A or B) = P(A) + P(B) - P(A and B)` — inclusion–exclusion again.</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Adding the two probabilities double-counts the outcomes where both occur, so the overlap comes off once.
+When the events are mutually exclusive the overlap is 0, so the formula collapses to plain addition — which is why "or" questions about outcomes that cannot co-occur feel so much easier.</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>One die: `P(even) = 3/6`, `P(&gt;3) = 3/6`, overlap {4, 6} `= 2/6`. So `P(even or &gt;3) = 3/6 + 3/6 - 2/6 = 2/3`, matching the list 2, 4, 5, 6.
+Drawing a king **or** a queen: mutually exclusive, so `4/52 + 4/52 = 2/13`. Drawing a king **or** a heart: they overlap in the king of hearts, so `4/52 + 13/52 - 1/52 = 4/13`.</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Counting Strategy &amp; Probability</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Independent versus mutually exclusive — what is the difference?</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>**Independent**: neither affects the other, so `P(A and B) = P(A)P(B)`. **Mutually exclusive**: they cannot both happen, so `P(A and B) = 0` and `P(A or B) = P(A) + P(B)`.</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>They sound similar and mean opposite things. A consequence worth remembering: for mutually exclusive events `P(A) + P(B) &lt;= 1`, since probabilities summing past 1 would force an overlap.</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Two coin flips are independent (both can be heads). One card being both a king and a queen is mutually exclusive. Two events with non-zero probability can never be both — if they cannot co-occur, knowing one happened tells you a great deal about the other.</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Counting Strategy &amp; Probability</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Conditional probability `P(A | B)`?</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>`P(A | B) = P(A and B) / P(B)` — the probability of A **given that** B happened.</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Conditioning on B shrinks the world to the outcomes where B occurred, so you rescale by dividing by `P(B)`.</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Roll a die: what is `P(2 | even)`? `P(2 and even) = 1/6`, `P(even) = 1/2`, so `(1/6)/(1/2) = 1/3` — matching the intuition that among 2, 4, 6 exactly one is a 2.</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>`P(A | B)` and `P(B | A)` are different numbers: the probability of being even **given** a roll of 2 is 1, not 1/3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Counting Strategy &amp; Probability</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Probability of "at least one" — what is the fast route?</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>The complement: `P(at least one) = 1 - P(none)`.</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Counting directly means adding the cases for exactly one, exactly two, exactly three … The complement is a single multiplication.</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Four coin flips, at least one head: `P(no heads) = (1/2)^4 = 1/16`, so the answer is **15/16**. Rolling two dice, at least one 6: `1 - (5/6)^2 = 11/36`.</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>The complement of "at least one" is "none" — and the complement of "at least two" is "zero or one", so both cases must come off.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F163"/>
+  <autoFilter ref="A1:G189"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>